--- a/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
+++ b/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\trans\BNVFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BE2D7A-CB76-4484-8BD2-B88F54442BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E48301-624A-49FA-9B6F-497A605A3B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31245" yWindow="3165" windowWidth="18165" windowHeight="12285" activeTab="2" xr2:uid="{9F7C64E4-EC04-4C16-8383-3C9CBB105721}"/>
+    <workbookView xWindow="37650" yWindow="2730" windowWidth="26565" windowHeight="11490" activeTab="1" xr2:uid="{9F7C64E4-EC04-4C16-8383-3C9CBB105721}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="71">
   <si>
     <t>battery electric vehicle</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>motorbikes</t>
-  </si>
-  <si>
-    <t>Fuel Economy (freight ton*miles/BTU)</t>
   </si>
   <si>
     <t>freight</t>
@@ -329,9 +326,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="0.0000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -408,7 +406,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -466,12 +464,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,7 +609,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="171" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -728,61 +722,10 @@
             <v>4.9212368633330004E-3</v>
           </cell>
         </row>
-        <row r="44">
-          <cell r="C44">
-            <v>6.5798820574477688E-4</v>
-          </cell>
-          <cell r="D44">
-            <v>1.5847326557973324E-4</v>
-          </cell>
-          <cell r="E44">
-            <v>1.0509496345551802E-4</v>
-          </cell>
-          <cell r="F44">
-            <v>1.0380732234767244E-4</v>
-          </cell>
-          <cell r="G44">
-            <v>0</v>
-          </cell>
-          <cell r="H44">
-            <v>1.3340249848135008E-4</v>
-          </cell>
-          <cell r="I44">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="C45">
-            <v>6.2149365057914963E-2</v>
-          </cell>
-          <cell r="D45">
-            <v>0</v>
-          </cell>
-          <cell r="E45">
-            <v>9.9265992802289229E-3</v>
-          </cell>
-          <cell r="F45">
-            <v>1.0558702581861411E-2</v>
-          </cell>
-          <cell r="G45">
-            <v>0</v>
-          </cell>
-          <cell r="H45">
-            <v>1.2426694100178716E-2</v>
-          </cell>
-          <cell r="I45">
-            <v>0</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="12">
         <row r="18">
           <cell r="D18">
-            <v>7.0063905313000519E-5</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19">
             <v>7.0063905313000519E-5</v>
           </cell>
         </row>
@@ -811,29 +754,6 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="24">
-          <cell r="C24">
-            <v>0</v>
-          </cell>
-          <cell r="D24">
-            <v>0</v>
-          </cell>
-          <cell r="E24">
-            <v>0</v>
-          </cell>
-          <cell r="F24">
-            <v>2.992789097910166E-2</v>
-          </cell>
-          <cell r="G24">
-            <v>0</v>
-          </cell>
-          <cell r="H24">
-            <v>0</v>
-          </cell>
-          <cell r="I24">
-            <v>0</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="14">
         <row r="22">
@@ -856,29 +776,6 @@
             <v>0</v>
           </cell>
           <cell r="I22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="C23">
-            <v>1.0021251453207708E-3</v>
-          </cell>
-          <cell r="D23">
-            <v>0</v>
-          </cell>
-          <cell r="E23">
-            <v>0</v>
-          </cell>
-          <cell r="F23">
-            <v>1.6108650602655154E-2</v>
-          </cell>
-          <cell r="G23">
-            <v>0</v>
-          </cell>
-          <cell r="H23">
-            <v>0</v>
-          </cell>
-          <cell r="I23">
             <v>0</v>
           </cell>
         </row>
@@ -1194,40 +1091,40 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1247,7 +1144,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -2045,7 +1942,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -2843,7 +2740,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -3641,7 +3538,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -4439,7 +4336,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -5237,7 +5134,7 @@
   <sheetData>
     <row r="1" spans="1:36">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -6126,7 +6023,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -6308,7 +6205,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>0</v>
@@ -6490,21 +6387,21 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18">
         <f>'US-LDVs-psgr'!B5</f>
@@ -6521,7 +6418,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="14">
         <f>'US-LDVs-frgt'!B5</f>
@@ -6538,7 +6435,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="14">
         <f t="shared" ref="B20:D21" si="0">B18/$B18</f>
@@ -6555,7 +6452,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" s="14">
         <f t="shared" si="0"/>
@@ -6572,27 +6469,27 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D23" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <f>'US-HDVs-psgr'!B2</f>
@@ -6617,7 +6514,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="14">
         <f>'US-HDVs-frgt'!B2</f>
@@ -6642,7 +6539,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26" s="14">
         <f t="shared" ref="B26:C27" si="1">B24/$D24</f>
@@ -6667,7 +6564,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27" s="14">
         <f t="shared" si="1"/>
@@ -6692,21 +6589,21 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <f>'US-aircraft-psgr'!B2</f>
@@ -6723,7 +6620,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="14">
         <f>'US-aircraft-frgt'!B2</f>
@@ -6740,7 +6637,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B32" s="14">
         <f>B31/C31</f>
@@ -6757,21 +6654,21 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="14">
         <f>'US-rail-psgr'!B2</f>
@@ -6788,7 +6685,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="14">
         <f>'US-rail-frgt'!B2</f>
@@ -6805,7 +6702,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B37" s="14">
         <f t="shared" ref="B37:D38" si="3">B35/$C35</f>
@@ -6822,7 +6719,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B38" s="14">
         <f t="shared" si="3"/>
@@ -6839,21 +6736,21 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="14">
         <f>'US-ships-psgr'!B2</f>
@@ -6870,7 +6767,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="14">
         <f>'US-ships-frgt'!B2</f>
@@ -6887,7 +6784,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="14">
         <f>B41/$C41</f>
@@ -6904,7 +6801,7 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="14">
         <f>B42/$C42</f>
@@ -6939,18 +6836,18 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="C1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
         <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>0</v>
@@ -7017,7 +6914,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>0</v>
@@ -7084,7 +6981,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>0</v>
@@ -7153,15 +7050,15 @@
         <v>1.0591751203291366E-2</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>0</v>
@@ -7228,7 +7125,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>0</v>
@@ -7295,7 +7192,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>0</v>
@@ -7362,7 +7259,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>0</v>
@@ -7429,7 +7326,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>0</v>
@@ -7496,7 +7393,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>0</v>
@@ -7563,7 +7460,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>0</v>
@@ -7630,7 +7527,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>0</v>
@@ -7697,7 +7594,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>0</v>
@@ -7787,12 +7684,12 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -7800,7 +7697,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="22" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7808,7 +7705,7 @@
         <v>32415.35</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7816,7 +7713,7 @@
         <v>1.60934</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7824,7 +7721,7 @@
         <v>1.4</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7834,29 +7731,29 @@
     </row>
     <row r="11" spans="1:4">
       <c r="B11" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11">
         <v>24.1</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12">
         <v>14.1</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="22">
         <v>2020</v>
@@ -7864,26 +7761,26 @@
     </row>
     <row r="15" spans="1:4">
       <c r="B15" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="30">
         <f>C11/$A$5</f>
         <v>14.975082953260344</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="30">
         <f>C12/$A$5</f>
         <v>8.7613555867622743</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:33">
@@ -7893,26 +7790,26 @@
     </row>
     <row r="19" spans="1:33">
       <c r="B19" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="31">
         <f>C15/$A$4</f>
         <v>4.6197505050108497E-4</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:33">
       <c r="B20" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="31">
         <f>C16/$A$4</f>
         <v>2.7028415817698326E-4</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:33">
@@ -7922,50 +7819,50 @@
     </row>
     <row r="23" spans="1:33">
       <c r="B23" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" s="31">
         <f>C19*$A$6</f>
         <v>6.4676507070151896E-4</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:33">
       <c r="B24" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="31">
         <f>C20*$A$6</f>
         <v>3.7839782144777654E-4</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:33" ht="15" thickBot="1"/>
     <row r="26" spans="1:33" ht="15" thickBot="1">
       <c r="B26" s="22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C26" s="32">
         <f>AVERAGE(C23:C24)</f>
         <v>5.1258144607464772E-4</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:33">
       <c r="A29" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="14"/>
     </row>
     <row r="30" spans="1:33">
       <c r="B30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30">
         <v>2020</v>
@@ -8844,7 +8741,7 @@
     </row>
     <row r="40" spans="2:33">
       <c r="B40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -9242,7 +9139,7 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -9606,7 +9503,7 @@
         <f>'SK_fuel econ'!$C$26*INDEX('SK_fuel econ'!$C$40:$AG$40,MATCH(B1,'SK_fuel econ'!$C$39:$AG$39,0))</f>
         <v>5.1258144607464772E-4</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="35">
         <f>'SK_fuel econ'!$C$26*INDEX('SK_fuel econ'!$C$40:$AG$40,MATCH(C1,'SK_fuel econ'!$C$39:$AG$39,0))</f>
         <v>5.309809855528363E-4</v>
       </c>
@@ -10269,7 +10166,7 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -10371,127 +10268,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.6660150128553506E-4</v>
+        <v>1.154922998361878E-3</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.753275478747539E-4</v>
+        <v>1.1700413439870092E-3</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.8416782146305747E-4</v>
+        <v>1.1853575940393318E-3</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.9312381732177929E-4</v>
+        <v>1.2008743391569534E-3</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.0219705029587716E-4</v>
+        <v>1.2165942038903398E-3</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.1138905506015868E-4</v>
+        <v>1.2325198471462397E-3</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.2070138637886111E-4</v>
+        <v>1.24865396263742E-3</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3013561936862868E-4</v>
+        <v>1.2649992793382892E-3</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3969334976493298E-4</v>
+        <v>1.2815585619464841E-3</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.4937619419198048E-4</v>
+        <v>1.2983346113504999E-3</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.591857904361536E-4</v>
+        <v>1.3153302651034411E-3</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.6912379772303067E-4</v>
+        <v>1.3325483979029738E-3</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.7919189699803264E-4</v>
+        <v>1.3499919220775608E-3</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.8939179121074337E-4</v>
+        <v>1.3676637880790626E-3</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.9972520560295203E-4</v>
+        <v>1.3855669849817851E-3</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.1019388800046555E-4</v>
+        <v>1.4037045409880618E-3</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.2079960910874151E-4</v>
+        <v>1.4220795239404528E-3</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.3154416281239056E-4</v>
+        <v>1.4406950418406491E-3</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.4242936647859986E-4</v>
+        <v>1.4595542433751699E-3</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.5345706126452802E-4</v>
+        <v>1.4786603184479418E-3</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.6462911242872432E-4</v>
+        <v>1.4980164987198476E-3</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.7594740964662421E-4</v>
+        <v>1.517626058155341E-3</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.87413867330175E-4</v>
+        <v>1.5374923135762144E-3</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.9903042495164526E-4</v>
+        <v>1.5576186252226161E-3</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.1079904737167321E-4</v>
+        <v>1.5780083973214124E-3</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.2272172517160965E-4</v>
+        <v>1.598665078661989E-3</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.3480047499021075E-4</v>
+        <v>1.6195921631795894E-3</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.4703733986473853E-4</v>
+        <v>1.6407931905462908E-3</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5943438957652697E-4</v>
+        <v>1.6622717467697143E-3</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7199372100107079E-4</v>
+        <v>1.6840314647995746E-3</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8471745846269768E-4</v>
+        <v>1.7060760251421667E-3</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -10501,127 +10398,127 @@
       </c>
       <c r="B3" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5806212262176831E-4</v>
+        <v>2.4137215532560945E-4</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5765204633288012E-4</v>
+        <v>2.4074593953111626E-4</v>
       </c>
       <c r="D3" s="21">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5724303394570296E-4</v>
+        <v>2.4012134839055527E-4</v>
       </c>
       <c r="E3" s="21">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5683508270005083E-4</v>
+        <v>2.3949837768892515E-4</v>
       </c>
       <c r="F3" s="21">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5642818984289866E-4</v>
+        <v>2.3887702322216E-4</v>
       </c>
       <c r="G3" s="21">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5602235262836389E-4</v>
+        <v>2.3825728079710092E-4</v>
       </c>
       <c r="H3" s="21">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5561756831768784E-4</v>
+        <v>2.3763914623146774E-4</v>
       </c>
       <c r="I3" s="21">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5521383417921731E-4</v>
+        <v>2.3702261535383078E-4</v>
       </c>
       <c r="J3" s="21">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5481114748838609E-4</v>
+        <v>2.3640768400358275E-4</v>
       </c>
       <c r="K3" s="21">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5440950552769655E-4</v>
+        <v>2.3579434803091065E-4</v>
       </c>
       <c r="L3" s="21">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5400890558670132E-4</v>
+        <v>2.351826032967677E-4</v>
       </c>
       <c r="M3" s="21">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5360934496198511E-4</v>
+        <v>2.3457244567284547E-4</v>
       </c>
       <c r="N3" s="21">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5321082095714626E-4</v>
+        <v>2.3396387104154606E-4</v>
       </c>
       <c r="O3" s="21">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5281333088277871E-4</v>
+        <v>2.333568752959542E-4</v>
       </c>
       <c r="P3" s="21">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5241687205645379E-4</v>
+        <v>2.3275145433980965E-4</v>
       </c>
       <c r="Q3" s="21">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.520214418027021E-4</v>
+        <v>2.3214760408747949E-4</v>
       </c>
       <c r="R3" s="21">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.516270374529955E-4</v>
+        <v>2.3154532046393053E-4</v>
       </c>
       <c r="S3" s="21">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5123365634572906E-4</v>
+        <v>2.3094459940470189E-4</v>
       </c>
       <c r="T3" s="21">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5084129582620313E-4</v>
+        <v>2.3034543685587753E-4</v>
       </c>
       <c r="U3" s="21">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5044995324660541E-4</v>
+        <v>2.2974782877405883E-4</v>
       </c>
       <c r="V3" s="21">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5005962596599306E-4</v>
+        <v>2.2915177112633743E-4</v>
       </c>
       <c r="W3" s="21">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4967031135027496E-4</v>
+        <v>2.2855725989026789E-4</v>
       </c>
       <c r="X3" s="21">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4928200677219379E-4</v>
+        <v>2.2796429105384063E-4</v>
       </c>
       <c r="Y3" s="21">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4889470961130844E-4</v>
+        <v>2.2737286061545481E-4</v>
       </c>
       <c r="Z3" s="21">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4850841725397627E-4</v>
+        <v>2.2678296458389136E-4</v>
       </c>
       <c r="AA3" s="21">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4812312709333545E-4</v>
+        <v>2.2619459897828601E-4</v>
       </c>
       <c r="AB3" s="21">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4773883652928742E-4</v>
+        <v>2.2560775982810247E-4</v>
       </c>
       <c r="AC3" s="21">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4735554296847929E-4</v>
+        <v>2.2502244317310554E-4</v>
       </c>
       <c r="AD3" s="21">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4697324382428637E-4</v>
+        <v>2.2443864506333454E-4</v>
       </c>
       <c r="AE3" s="21">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.465919365167947E-4</v>
+        <v>2.2385636155907652E-4</v>
       </c>
       <c r="AF3" s="21">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4621161847278369E-4</v>
+        <v>2.2327558873083971E-4</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -10631,127 +10528,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.048223051368783E-4</v>
+        <v>2.6929951214014277E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0455035420283891E-4</v>
+        <v>2.6860084162562561E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0427910881816166E-4</v>
+        <v>2.6790398374152867E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0400856715236962E-4</v>
+        <v>2.6720893378516449E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0373872737973488E-4</v>
+        <v>2.6651568706604636E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0346958767926621E-4</v>
+        <v>2.6582423890585648E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0320114623469673E-4</v>
+        <v>2.6513458463841449E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0293340123447171E-4</v>
+        <v>2.6444671960964601E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0266635087173631E-4</v>
+        <v>2.6376063917755109E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0239999334432338E-4</v>
+        <v>2.6307633871217311E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0213432685474131E-4</v>
+        <v>2.6239381359556731E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0186934961016192E-4</v>
+        <v>2.617130592217698E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0160505982240833E-4</v>
+        <v>2.6103407099676629E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.013414557079429E-4</v>
+        <v>2.6035684433846134E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0107853548785523E-4</v>
+        <v>2.5968137467664718E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0081629738785008E-4</v>
+        <v>2.5900765745297304E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0055473963823548E-4</v>
+        <v>2.5833568812091431E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0029386047391071E-4</v>
+        <v>2.5766546214574189E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0003365813435446E-4</v>
+        <v>2.5699697500449154E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9774130863612898E-5</v>
+        <v>2.5633022218593348E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9515276910287843E-5</v>
+        <v>2.556651991905418E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9257094527524929E-5</v>
+        <v>2.5500190153046419E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8999581973001845E-5</v>
+        <v>2.543403247294916E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8742737508916565E-5</v>
+        <v>2.536804643230281E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8486559401975593E-5</v>
+        <v>2.5302231585806062E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.82310459233823E-5</v>
+        <v>2.5236587489312903E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7976195348825236E-5</v>
+        <v>2.5171113699829612E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7722005958466533E-5</v>
+        <v>2.5105809775511772E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7468476036930235E-5</v>
+        <v>2.504067527566129E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7215603873290778E-5</v>
+        <v>2.4975709760723412E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6963387761061419E-5</v>
+        <v>2.4910912792283765E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -10761,127 +10658,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0353800468445456E-4</v>
+        <v>2.5034880573028084E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0326938573884235E-4</v>
+        <v>2.496993009186371E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.030014636980832E-4</v>
+        <v>2.4905148118193953E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0273423675412753E-4</v>
+        <v>2.4840534214843062E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0246770310361655E-4</v>
+        <v>2.4776087945769485E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0220186094787012E-4</v>
+        <v>2.4711808876062944E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0193670849287456E-4</v>
+        <v>2.4647696571941484E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0167224394927063E-4</v>
+        <v>2.4583750600748558E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0140846553234134E-4</v>
+        <v>2.4519970530950105E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0114537146200003E-4</v>
+        <v>2.4456355932131636E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0088295996277826E-4</v>
+        <v>2.4392906374995322E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0062122926381386E-4</v>
+        <v>2.4329621431357109E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.00360177598839E-4</v>
+        <v>2.4266500674143823E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0009980320616826E-4</v>
+        <v>2.4203543677390286E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9840104328686714E-5</v>
+        <v>2.414075001623645E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9581079213838106E-5</v>
+        <v>2.4078119266924519E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9322726113613025E-5</v>
+        <v>2.4015651006796095E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9065043284537061E-5</v>
+        <v>2.3953344814289324E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8808028987659109E-5</v>
+        <v>2.3891200268936051E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8551681488539576E-5</v>
+        <v>2.3829216951358988E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8295999057238705E-5</v>
+        <v>2.3767394443268875E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8040979968304885E-5</v>
+        <v>2.3705732327461662E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7786622500763029E-5</v>
+        <v>2.3644230187815692E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7532924938102943E-5</v>
+        <v>2.3582887609288898E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7279885568267739E-5</v>
+        <v>2.3521704177915996E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7027502683642288E-5</v>
+        <v>2.346067948080569E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6775774581041717E-5</v>
+        <v>2.3399813106137892E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6524699561699868E-5</v>
+        <v>2.333910464316094E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6274275931257884E-5</v>
+        <v>2.3278553682188824E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6024501999752735E-5</v>
+        <v>2.3218159814598425E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5775376081605836E-5</v>
+        <v>2.3157922632826756E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -10891,127 +10788,127 @@
       </c>
       <c r="B6" s="15">
         <f>B5*Calibration!$C$21</f>
-        <v>1.5894731353058238E-4</v>
+        <v>3.8432525561690983E-4</v>
       </c>
       <c r="C6" s="15">
         <f>B6*(1+CAGR!$C$13)</f>
-        <v>1.6013282661803488E-4</v>
+        <v>3.8719175653631488E-4</v>
       </c>
       <c r="D6" s="15">
         <f>C6*(1+CAGR!$C$13)</f>
-        <v>1.6132718188878261E-4</v>
+        <v>3.9007963733487399E-4</v>
       </c>
       <c r="E6" s="15">
         <f>D6*(1+CAGR!$C$13)</f>
-        <v>1.6253044529250274E-4</v>
+        <v>3.9298905747502778E-4</v>
       </c>
       <c r="F6" s="15">
         <f>E6*(1+CAGR!$C$13)</f>
-        <v>1.6374268327076007E-4</v>
+        <v>3.9592017760857207E-4</v>
       </c>
       <c r="G6" s="15">
         <f>F6*(1+CAGR!$C$13)</f>
-        <v>1.6496396276067561E-4</v>
+        <v>3.9887315958552866E-4</v>
       </c>
       <c r="H6" s="15">
         <f>G6*(1+CAGR!$C$13)</f>
-        <v>1.6619435119862288E-4</v>
+        <v>4.0184816646308242E-4</v>
       </c>
       <c r="I6" s="15">
         <f>H6*(1+CAGR!$C$13)</f>
-        <v>1.6743391652395149E-4</v>
+        <v>4.0484536251458484E-4</v>
       </c>
       <c r="J6" s="15">
         <f>I6*(1+CAGR!$C$13)</f>
-        <v>1.6868272718273863E-4</v>
+        <v>4.0786491323862488E-4</v>
       </c>
       <c r="K6" s="15">
         <f>J6*(1+CAGR!$C$13)</f>
-        <v>1.6994085213156856E-4</v>
+        <v>4.1090698536816759E-4</v>
       </c>
       <c r="L6" s="15">
         <f>K6*(1+CAGR!$C$13)</f>
-        <v>1.7120836084134013E-4</v>
+        <v>4.1397174687976047E-4</v>
       </c>
       <c r="M6" s="15">
         <f>L6*(1+CAGR!$C$13)</f>
-        <v>1.724853233011029E-4</v>
+        <v>4.1705936700280901E-4</v>
       </c>
       <c r="N6" s="15">
         <f>M6*(1+CAGR!$C$13)</f>
-        <v>1.737718100219218E-4</v>
+        <v>4.2017001622892097E-4</v>
       </c>
       <c r="O6" s="15">
         <f>N6*(1+CAGR!$C$13)</f>
-        <v>1.7506789204077051E-4</v>
+        <v>4.2330386632132076E-4</v>
       </c>
       <c r="P6" s="15">
         <f>O6*(1+CAGR!$C$13)</f>
-        <v>1.7637364092445404E-4</v>
+        <v>4.2646109032433362E-4</v>
       </c>
       <c r="Q6" s="15">
         <f>P6*(1+CAGR!$C$13)</f>
-        <v>1.7768912877356044E-4</v>
+        <v>4.2964186257294095E-4</v>
       </c>
       <c r="R6" s="15">
         <f>Q6*(1+CAGR!$C$13)</f>
-        <v>1.7901442822644209E-4</v>
+        <v>4.3284635870240645E-4</v>
       </c>
       <c r="S6" s="15">
         <f>R6*(1+CAGR!$C$13)</f>
-        <v>1.8034961246322657E-4</v>
+        <v>4.3607475565797456E-4</v>
       </c>
       <c r="T6" s="15">
         <f>S6*(1+CAGR!$C$13)</f>
-        <v>1.8169475520985753E-4</v>
+        <v>4.3932723170464087E-4</v>
       </c>
       <c r="U6" s="15">
         <f>T6*(1+CAGR!$C$13)</f>
-        <v>1.8304993074216573E-4</v>
+        <v>4.4260396643699555E-4</v>
       </c>
       <c r="V6" s="15">
         <f>U6*(1+CAGR!$C$13)</f>
-        <v>1.8441521388997027E-4</v>
+        <v>4.4590514078914013E-4</v>
       </c>
       <c r="W6" s="15">
         <f>V6*(1+CAGR!$C$13)</f>
-        <v>1.8579068004121068E-4</v>
+        <v>4.492309370446784E-4</v>
       </c>
       <c r="X6" s="15">
         <f>W6*(1+CAGR!$C$13)</f>
-        <v>1.871764051461095E-4</v>
+        <v>4.5258153884678151E-4</v>
       </c>
       <c r="Y6" s="15">
         <f>X6*(1+CAGR!$C$13)</f>
-        <v>1.8857246572136628E-4</v>
+        <v>4.5595713120832854E-4</v>
       </c>
       <c r="Z6" s="15">
         <f>Y6*(1+CAGR!$C$13)</f>
-        <v>1.8997893885438249E-4</v>
+        <v>4.5935790052212234E-4</v>
       </c>
       <c r="AA6" s="15">
         <f>Z6*(1+CAGR!$C$13)</f>
-        <v>1.9139590220751821E-4</v>
+        <v>4.6278403457118196E-4</v>
       </c>
       <c r="AB6" s="15">
         <f>AA6*(1+CAGR!$C$13)</f>
-        <v>1.9282343402238046E-4</v>
+        <v>4.6623572253911129E-4</v>
       </c>
       <c r="AC6" s="15">
         <f>AB6*(1+CAGR!$C$13)</f>
-        <v>1.9426161312414354E-4</v>
+        <v>4.6971315502054574E-4</v>
       </c>
       <c r="AD6" s="15">
         <f>AC6*(1+CAGR!$C$13)</f>
-        <v>1.9571051892590153E-4</v>
+        <v>4.7321652403167606E-4</v>
       </c>
       <c r="AE6" s="15">
         <f>AD6*(1+CAGR!$C$13)</f>
-        <v>1.9717023143305337E-4</v>
+        <v>4.7674602302085145E-4</v>
       </c>
       <c r="AF6" s="15">
         <f>AE6*(1+CAGR!$C$13)</f>
-        <v>1.9864083124772057E-4</v>
+        <v>4.8030184687926104E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -11021,127 +10918,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3305639910853227E-4</v>
+        <v>2.7727875694429516E-4</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3271119765574766E-4</v>
+        <v>2.7655938508119968E-4</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3236689179343299E-4</v>
+        <v>2.7584187955609243E-4</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3202347919806881E-4</v>
+        <v>2.7512623552694712E-4</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3168095755216377E-4</v>
+        <v>2.7441244816429954E-4</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.313393245442391E-4</v>
+        <v>2.7370051265121514E-4</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3099857786881284E-4</v>
+        <v>2.7299042418325636E-4</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3065871522638446E-4</v>
+        <v>2.722821779684503E-4</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3031973432341918E-4</v>
+        <v>2.715757692272563E-4</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2998163287233263E-4</v>
+        <v>2.708711931925338E-4</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2964440859147526E-4</v>
+        <v>2.7016844510951006E-4</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2930805920511712E-4</v>
+        <v>2.6946752023574816E-4</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2897258244343236E-4</v>
+        <v>2.6876841384111493E-4</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.28637976042484E-4</v>
+        <v>2.6807112120774907E-4</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2830423774420858E-4</v>
+        <v>2.6737563763002927E-4</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2797136529640098E-4</v>
+        <v>2.6668195841454256E-4</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.276393564526992E-4</v>
+        <v>2.6599007888005241E-4</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.273082089725692E-4</v>
+        <v>2.6529999435746744E-4</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2697792062128975E-4</v>
+        <v>2.6461170018980972E-4</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2664848916993742E-4</v>
+        <v>2.6392519173218328E-4</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.263199123953715E-4</v>
+        <v>2.6324046435174296E-4</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2599218808021897E-4</v>
+        <v>2.6255751342766308E-4</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2566531401285956E-4</v>
+        <v>2.6187633435110613E-4</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2533928798741086E-4</v>
+        <v>2.6119692252519181E-4</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2501410780371334E-4</v>
+        <v>2.6051927336496604E-4</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2468977126731562E-4</v>
+        <v>2.5984338229736981E-4</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2436627618945959E-4</v>
+        <v>2.5916924476120855E-4</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2404362038706564E-4</v>
+        <v>2.5849685620712119E-4</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2372180168271796E-4</v>
+        <v>2.5782621209754955E-4</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2340081790464979E-4</v>
+        <v>2.5715730790670766E-4</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2308066688672883E-4</v>
+        <v>2.5649013912055135E-4</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -11151,127 +11048,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$21</f>
-        <v>3.1061401405336363E-4</v>
+        <v>7.5104641719084242E-4</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$15)</f>
-        <v>3.0980815721652697E-4</v>
+        <v>7.4909790275591115E-4</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$15)</f>
-        <v>3.0900439109424953E-4</v>
+        <v>7.4715444354581855E-4</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$15)</f>
-        <v>3.0820271026238253E-4</v>
+        <v>7.4521602644529185E-4</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$15)</f>
-        <v>3.0740310931084964E-4</v>
+        <v>7.4328263837308459E-4</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$15)</f>
-        <v>3.0660558284361034E-4</v>
+        <v>7.4135426628188831E-4</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$15)</f>
-        <v>3.0581012547862369E-4</v>
+        <v>7.3943089715824452E-4</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$15)</f>
-        <v>3.0501673184781187E-4</v>
+        <v>7.3751251802245681E-4</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$15)</f>
-        <v>3.0422539659702403E-4</v>
+        <v>7.3559911592850332E-4</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$15)</f>
-        <v>3.034361143860001E-4</v>
+        <v>7.3369067796394914E-4</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$15)</f>
-        <v>3.0264887988833475E-4</v>
+        <v>7.3178719124985972E-4</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$15)</f>
-        <v>3.0186368779144156E-4</v>
+        <v>7.298886429407133E-4</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$15)</f>
-        <v>3.0108053279651699E-4</v>
+        <v>7.2799502022431468E-4</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$15)</f>
-        <v>3.0029940961850477E-4</v>
+        <v>7.2610631032170867E-4</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$15)</f>
-        <v>2.9952031298606014E-4</v>
+        <v>7.2422250048709356E-4</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$15)</f>
-        <v>2.9874323764151435E-4</v>
+        <v>7.2234357800773561E-4</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$15)</f>
-        <v>2.9796817834083908E-4</v>
+        <v>7.2046953020388292E-4</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$15)</f>
-        <v>2.971951298536112E-4</v>
+        <v>7.1860034442867982E-4</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$15)</f>
-        <v>2.9642408696297734E-4</v>
+        <v>7.1673600806808162E-4</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$15)</f>
-        <v>2.9565504446561872E-4</v>
+        <v>7.1487650854076975E-4</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$15)</f>
-        <v>2.948879971717161E-4</v>
+        <v>7.1302183329806639E-4</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$15)</f>
-        <v>2.9412293990491465E-4</v>
+        <v>7.1117196982384994E-4</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$15)</f>
-        <v>2.9335986750228906E-4</v>
+        <v>7.0932690563447088E-4</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$15)</f>
-        <v>2.9259877481430877E-4</v>
+        <v>7.0748662827866706E-4</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$15)</f>
-        <v>2.9183965670480318E-4</v>
+        <v>7.0565112533747993E-4</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$15)</f>
-        <v>2.9108250805092687E-4</v>
+        <v>7.0382038442417074E-4</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$15)</f>
-        <v>2.9032732374312514E-4</v>
+        <v>7.0199439318413678E-4</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$15)</f>
-        <v>2.895740986850996E-4</v>
+        <v>7.0017313929482817E-4</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$15)</f>
-        <v>2.8882282779377368E-4</v>
+        <v>6.9835661046566469E-4</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$15)</f>
-        <v>2.8807350599925825E-4</v>
+        <v>6.9654479443795271E-4</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$15)</f>
-        <v>2.8732612824481756E-4</v>
+        <v>6.9473767898480259E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -11296,7 +11193,7 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -12323,7 +12220,7 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -12425,127 +12322,127 @@
       </c>
       <c r="B2" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A2,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.3142037164590048E-2</v>
+        <v>1.1480487681490801E-2</v>
       </c>
       <c r="C2" s="21">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.415056458870004E-2</v>
+        <v>1.1663858177421419E-2</v>
       </c>
       <c r="D2" s="21">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.5175200577101841E-2</v>
+        <v>1.185015753314534E-2</v>
       </c>
       <c r="E2" s="21">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.6216202421602643E-2</v>
+        <v>1.2039432529469072E-2</v>
       </c>
       <c r="F2" s="21">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.7273831523567307E-2</v>
+        <v>1.2231730694399055E-2</v>
       </c>
       <c r="G2" s="21">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.8348353459557698E-2</v>
+        <v>1.242710031507622E-2</v>
       </c>
       <c r="H2" s="21">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.9440038048020472E-2</v>
+        <v>1.262559044990115E-2</v>
       </c>
       <c r="I2" s="21">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.0549159417039958E-2</v>
+        <v>1.2827250940852925E-2</v>
       </c>
       <c r="J2" s="21">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.1675996073173279E-2</v>
+        <v>1.3032132426004718E-2</v>
       </c>
       <c r="K2" s="21">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.2820830971384851E-2</v>
+        <v>1.3240286352239292E-2</v>
       </c>
       <c r="L2" s="21">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.3983951586098023E-2</v>
+        <v>1.3451764988167608E-2</v>
       </c>
       <c r="M2" s="21">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.5165649983381433E-2</v>
+        <v>1.366662143725376E-2</v>
       </c>
       <c r="N2" s="21">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.6366222894288474E-2</v>
+        <v>1.3884909651149548E-2</v>
       </c>
       <c r="O2" s="21">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.7585971789368116E-2</v>
+        <v>1.4106684443242047E-2</v>
       </c>
       <c r="P2" s="21">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.8825202954365792E-2</v>
+        <v>1.4332001502417544E-2</v>
       </c>
       <c r="Q2" s="21">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.0084227567133529E-2</v>
+        <v>1.4560917407045335E-2</v>
       </c>
       <c r="R2" s="21">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.1363361775768361E-2</v>
+        <v>1.4793489639184863E-2</v>
       </c>
       <c r="S2" s="21">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.2662926777998955E-2</v>
+        <v>1.502977659901979E-2</v>
       </c>
       <c r="T2" s="21">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.3983248901840099E-2</v>
+        <v>1.5269837619522603E-2</v>
       </c>
       <c r="U2" s="21">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.5324659687535498E-2</v>
+        <v>1.5513732981353457E-2</v>
       </c>
       <c r="V2" s="21">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.6687495970809381E-2</v>
+        <v>1.5761523927996984E-2</v>
       </c>
       <c r="W2" s="21">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.8072099967447845E-2</v>
+        <v>1.6013272681140875E-2</v>
       </c>
       <c r="X2" s="21">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.9478819359231104E-2</v>
+        <v>1.6269042456300089E-2</v>
       </c>
       <c r="Y2" s="21">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.0908007381238345E-2</v>
+        <v>1.6528897478690623E-2</v>
       </c>
       <c r="Z2" s="21">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.2360022910547054E-2</v>
+        <v>1.6792902999356818E-2</v>
       </c>
       <c r="AA2" s="21">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.3835230556349E-2</v>
+        <v>1.7061125311556274E-2</v>
       </c>
       <c r="AB2" s="21">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.5334000751505665E-2</v>
+        <v>1.7333631767406436E-2</v>
       </c>
       <c r="AC2" s="21">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.6856709845565978E-2</v>
+        <v>1.7610490794797099E-2</v>
       </c>
       <c r="AD2" s="21">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.8403740199269826E-2</v>
+        <v>1.7891771914573033E-2</v>
       </c>
       <c r="AE2" s="21">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.9975480280560927E-2</v>
+        <v>1.8177545757991045E-2</v>
       </c>
       <c r="AF2" s="21">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>0.10157232476213329</v>
+        <v>1.8467884084455891E-2</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -12555,127 +12452,127 @@
       </c>
       <c r="B3" s="13">
         <f>B5*Calibration!$C$27</f>
-        <v>7.2870071134607615E-3</v>
+        <v>1.8426798976574875E-3</v>
       </c>
       <c r="C3" s="13">
         <f>B3*(1+CAGR!$C$24)</f>
-        <v>7.3408582877475892E-3</v>
+        <v>1.8562973505813754E-3</v>
       </c>
       <c r="D3" s="13">
         <f>C3*(1+CAGR!$C$24)</f>
-        <v>7.3951074236292E-3</v>
+        <v>1.8700154368406407E-3</v>
       </c>
       <c r="E3" s="13">
         <f>D3*(1+CAGR!$C$24)</f>
-        <v>7.4497574620522502E-3</v>
+        <v>1.8838349001182796E-3</v>
       </c>
       <c r="F3" s="13">
         <f>E3*(1+CAGR!$C$24)</f>
-        <v>7.5048113656970682E-3</v>
+        <v>1.8977564895931249E-3</v>
       </c>
       <c r="G3" s="13">
         <f>F3*(1+CAGR!$C$24)</f>
-        <v>7.5602721191382685E-3</v>
+        <v>1.9117809599804611E-3</v>
       </c>
       <c r="H3" s="13">
         <f>G3*(1+CAGR!$C$24)</f>
-        <v>7.6161427290065507E-3</v>
+        <v>1.9259090715729381E-3</v>
       </c>
       <c r="I3" s="13">
         <f>H3*(1+CAGR!$C$24)</f>
-        <v>7.6724262241516933E-3</v>
+        <v>1.9401415902817886E-3</v>
       </c>
       <c r="J3" s="13">
         <f>I3*(1+CAGR!$C$24)</f>
-        <v>7.729125655806756E-3</v>
+        <v>1.9544792876783497E-3</v>
       </c>
       <c r="K3" s="13">
         <f>J3*(1+CAGR!$C$24)</f>
-        <v>7.7862440977534897E-3</v>
+        <v>1.9689229410358908E-3</v>
       </c>
       <c r="L3" s="13">
         <f>K3*(1+CAGR!$C$24)</f>
-        <v>7.8437846464889729E-3</v>
+        <v>1.9834733333717511E-3</v>
       </c>
       <c r="M3" s="13">
         <f>L3*(1+CAGR!$C$24)</f>
-        <v>7.9017504213934817E-3</v>
+        <v>1.9981312534897884E-3</v>
       </c>
       <c r="N3" s="13">
         <f>M3*(1+CAGR!$C$24)</f>
-        <v>7.960144564899593E-3</v>
+        <v>2.0128974960231423E-3</v>
       </c>
       <c r="O3" s="13">
         <f>N3*(1+CAGR!$C$24)</f>
-        <v>8.0189702426625414E-3</v>
+        <v>2.027772861477312E-3</v>
       </c>
       <c r="P3" s="13">
         <f>O3*(1+CAGR!$C$24)</f>
-        <v>8.0782306437318391E-3</v>
+        <v>2.0427581562735531E-3</v>
       </c>
       <c r="Q3" s="13">
         <f>P3*(1+CAGR!$C$24)</f>
-        <v>8.1379289807241573E-3</v>
+        <v>2.0578541927925957E-3</v>
       </c>
       <c r="R3" s="13">
         <f>Q3*(1+CAGR!$C$24)</f>
-        <v>8.1980684899974881E-3</v>
+        <v>2.0730617894186847E-3</v>
       </c>
       <c r="S3" s="13">
         <f>R3*(1+CAGR!$C$24)</f>
-        <v>8.2586524318265971E-3</v>
+        <v>2.0883817705839467E-3</v>
       </c>
       <c r="T3" s="13">
         <f>S3*(1+CAGR!$C$24)</f>
-        <v>8.3196840905797632E-3</v>
+        <v>2.103814966813083E-3</v>
       </c>
       <c r="U3" s="13">
         <f>T3*(1+CAGR!$C$24)</f>
-        <v>8.3811667748968349E-3</v>
+        <v>2.1193622147683937E-3</v>
       </c>
       <c r="V3" s="13">
         <f>U3*(1+CAGR!$C$24)</f>
-        <v>8.4431038178685944E-3</v>
+        <v>2.1350243572951363E-3</v>
       </c>
       <c r="W3" s="13">
         <f>V3*(1+CAGR!$C$24)</f>
-        <v>8.5054985772174563E-3</v>
+        <v>2.1508022434672167E-3</v>
       </c>
       <c r="X3" s="13">
         <f>W3*(1+CAGR!$C$24)</f>
-        <v>8.5683544354794878E-3</v>
+        <v>2.1666967286332189E-3</v>
       </c>
       <c r="Y3" s="13">
         <f>X3*(1+CAGR!$C$24)</f>
-        <v>8.6316748001877882E-3</v>
+        <v>2.1827086744627753E-3</v>
       </c>
       <c r="Z3" s="13">
         <f>Y3*(1+CAGR!$C$24)</f>
-        <v>8.6954631040572182E-3</v>
+        <v>2.1988389489932805E-3</v>
       </c>
       <c r="AA3" s="13">
         <f>Z3*(1+CAGR!$C$24)</f>
-        <v>8.7597228051704886E-3</v>
+        <v>2.2150884266769473E-3</v>
       </c>
       <c r="AB3" s="13">
         <f>AA3*(1+CAGR!$C$24)</f>
-        <v>8.8244573871656337E-3</v>
+        <v>2.2314579884282139E-3</v>
       </c>
       <c r="AC3" s="13">
         <f>AB3*(1+CAGR!$C$24)</f>
-        <v>8.8896703594248654E-3</v>
+        <v>2.2479485216714994E-3</v>
       </c>
       <c r="AD3" s="13">
         <f>AC3*(1+CAGR!$C$24)</f>
-        <v>8.9553652572648204E-3</v>
+        <v>2.2645609203893122E-3</v>
       </c>
       <c r="AE3" s="13">
         <f>AD3*(1+CAGR!$C$24)</f>
-        <v>9.021545642128221E-3</v>
+        <v>2.2812960851707155E-3</v>
       </c>
       <c r="AF3" s="13">
         <f>AE3*(1+CAGR!$C$24)</f>
-        <v>9.088215101776943E-3</v>
+        <v>2.2981549232601491E-3</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -12685,127 +12582,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.9999571100748211E-3</v>
+        <v>2.6897313702466726E-3</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0073857056213296E-2</v>
+        <v>2.7096085558385927E-3</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0148303124898015E-2</v>
+        <v>2.7296326343549983E-3</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.022329935198896E-2</v>
+        <v>2.7498046913384659E-3</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.029884980317123E-2</v>
+        <v>2.7701258203537602E-3</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.037495857417544E-2</v>
+        <v>2.7905971230471186E-3</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0451629790999764E-2</v>
+        <v>2.8112197092059732E-3</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0528867610133611E-2</v>
+        <v>2.8319946968191141E-3</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0606676218782954E-2</v>
+        <v>2.852923212137298E-3</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.068505983509733E-2</v>
+        <v>2.8740063897343044E-3</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0764022708398512E-2</v>
+        <v>2.895245372568443E-3</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0843569119410871E-2</v>
+        <v>2.9166413120445154E-3</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0923703380493447E-2</v>
+        <v>2.9381953680762351E-3</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1004429835873726E-2</v>
+        <v>2.9599087091491077E-3</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1085752861883147E-2</v>
+        <v>2.9817825123837787E-3</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1167676867194356E-2</v>
+        <v>3.0038179635998451E-3</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1250206293060203E-2</v>
+        <v>3.0260162573801427E-3</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1333345613554516E-2</v>
+        <v>3.0483785971355051E-3</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1417099335814645E-2</v>
+        <v>3.0709061951700043E-3</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1501472000285805E-2</v>
+        <v>3.0936002727466709E-3</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1586468180967219E-2</v>
+        <v>3.1164620601537014E-3</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1672092485660085E-2</v>
+        <v>3.1394927967711549E-3</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1758349556217376E-2</v>
+        <v>3.1626937311381412E-3</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1845244068795474E-2</v>
+        <v>3.186066121020507E-3</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1932780734107685E-2</v>
+        <v>3.2096112334790219E-3</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2020964297679609E-2</v>
+        <v>3.2333303449380681E-3</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2109799540106405E-2</v>
+        <v>3.2572247412548374E-3</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2199291277311957E-2</v>
+        <v>3.2812957177890401E-3</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2289444360809951E-2</v>
+        <v>3.3055445794731284E-3</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2380263677966888E-2</v>
+        <v>3.3299726408830407E-3</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2471754152267036E-2</v>
+        <v>3.3545812263094652E-3</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -12815,127 +12712,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0636731671736769E-2</v>
+        <v>2.6897313702466726E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0715337398639221E-2</v>
+        <v>2.7096085558385927E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0794524023931568E-2</v>
+        <v>2.7296326343549983E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0874295840468196E-2</v>
+        <v>2.7498046913384659E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0954657172827795E-2</v>
+        <v>2.7701258203537602E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1035612377547807E-2</v>
+        <v>2.7905971230471186E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.11171658433606E-2</v>
+        <v>2.8112197092059732E-3</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.119932199143139E-2</v>
+        <v>2.8319946968191141E-3</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.128208527559792E-2</v>
+        <v>2.852923212137298E-3</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1365460182611911E-2</v>
+        <v>2.8740063897343044E-3</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1449451232382297E-2</v>
+        <v>2.895245372568443E-3</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1534062978220258E-2</v>
+        <v>2.9166413120445154E-3</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1619300007086063E-2</v>
+        <v>2.9381953680762351E-3</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1705166939837742E-2</v>
+        <v>2.9599087091491077E-3</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.179166843148158E-2</v>
+        <v>2.9817825123837787E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1878809171424486E-2</v>
+        <v>3.0038179635998451E-3</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1966593883728211E-2</v>
+        <v>3.0260162573801427E-3</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2055027327365443E-2</v>
+        <v>3.0483785971355051E-3</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2144114296477803E-2</v>
+        <v>3.0709061951700043E-3</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2233859620635747E-2</v>
+        <v>3.0936002727466709E-3</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2324268165100384E-2</v>
+        <v>3.1164620601537014E-3</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2415344831087229E-2</v>
+        <v>3.1394927967711549E-3</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2507094556031908E-2</v>
+        <v>3.1626937311381412E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2599522313857829E-2</v>
+        <v>3.186066121020507E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2692633115245822E-2</v>
+        <v>3.2096112334790219E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2786432007905781E-2</v>
+        <v>3.2333303449380681E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2880924076850309E-2</v>
+        <v>3.2572247412548374E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2976114444670388E-2</v>
+        <v>3.2812957177890401E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3072008271813079E-2</v>
+        <v>3.3055445794731284E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3168610756861284E-2</v>
+        <v>3.3299726408830407E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3265927136815571E-2</v>
+        <v>3.3545812263094652E-3</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -12945,127 +12842,127 @@
       </c>
       <c r="B6" s="13">
         <f>B5*Calibration!$E$26</f>
-        <v>2.3586006368547578E-2</v>
+        <v>5.9642400679232061E-3</v>
       </c>
       <c r="C6" s="13">
         <f>B6*(1+CAGR!$C$27)</f>
-        <v>2.3760307576149896E-2</v>
+        <v>6.0083159589420197E-3</v>
       </c>
       <c r="D6" s="13">
         <f>C6*(1+CAGR!$C$27)</f>
-        <v>2.3935896874262192E-2</v>
+        <v>6.0527175719550822E-3</v>
       </c>
       <c r="E6" s="13">
         <f>D6*(1+CAGR!$C$27)</f>
-        <v>2.4112783781907225E-2</v>
+        <v>6.0974473140565002E-3</v>
       </c>
       <c r="F6" s="13">
         <f>E6*(1+CAGR!$C$27)</f>
-        <v>2.429097788845358E-2</v>
+        <v>6.1425076101288703E-3</v>
       </c>
       <c r="G6" s="13">
         <f>F6*(1+CAGR!$C$27)</f>
-        <v>2.4470488854135532E-2</v>
+        <v>6.1879009029747337E-3</v>
       </c>
       <c r="H6" s="13">
         <f>G6*(1+CAGR!$C$27)</f>
-        <v>2.4651326410576737E-2</v>
+        <v>6.2336296534490085E-3</v>
       </c>
       <c r="I6" s="13">
         <f>H6*(1+CAGR!$C$27)</f>
-        <v>2.483350036131781E-2</v>
+        <v>6.2796963405923941E-3</v>
       </c>
       <c r="J6" s="13">
         <f>I6*(1+CAGR!$C$27)</f>
-        <v>2.5017020582347786E-2</v>
+        <v>6.3261034617657658E-3</v>
       </c>
       <c r="K6" s="13">
         <f>J6*(1+CAGR!$C$27)</f>
-        <v>2.520189702263952E-2</v>
+        <v>6.3728535327855626E-3</v>
       </c>
       <c r="L6" s="13">
         <f>K6*(1+CAGR!$C$27)</f>
-        <v>2.5388139704689037E-2</v>
+        <v>6.4199490880601714E-3</v>
       </c>
       <c r="M6" s="13">
         <f>L6*(1+CAGR!$C$27)</f>
-        <v>2.5575758725058875E-2</v>
+        <v>6.4673926807273258E-3</v>
       </c>
       <c r="N6" s="13">
         <f>M6*(1+CAGR!$C$27)</f>
-        <v>2.576476425492543E-2</v>
+        <v>6.5151868827925136E-3</v>
       </c>
       <c r="O6" s="13">
         <f>N6*(1+CAGR!$C$27)</f>
-        <v>2.5955166540630362E-2</v>
+        <v>6.5633342852684101E-3</v>
       </c>
       <c r="P6" s="13">
         <f>O6*(1+CAGR!$C$27)</f>
-        <v>2.6146975904236064E-2</v>
+        <v>6.6118374983153427E-3</v>
       </c>
       <c r="Q6" s="13">
         <f>P6*(1+CAGR!$C$27)</f>
-        <v>2.6340202744085241E-2</v>
+        <v>6.6606991513827934E-3</v>
       </c>
       <c r="R6" s="13">
         <f>Q6*(1+CAGR!$C$27)</f>
-        <v>2.653485753536463E-2</v>
+        <v>6.7099218933519434E-3</v>
       </c>
       <c r="S6" s="13">
         <f>R6*(1+CAGR!$C$27)</f>
-        <v>2.6730950830672864E-2</v>
+        <v>6.7595083926792771E-3</v>
       </c>
       <c r="T6" s="13">
         <f>S6*(1+CAGR!$C$27)</f>
-        <v>2.6928493260592566E-2</v>
+        <v>6.8094613375412416E-3</v>
       </c>
       <c r="U6" s="13">
         <f>T6*(1+CAGR!$C$27)</f>
-        <v>2.7127495534266639E-2</v>
+        <v>6.8597834359799791E-3</v>
       </c>
       <c r="V6" s="13">
         <f>U6*(1+CAGR!$C$27)</f>
-        <v>2.7327968439978839E-2</v>
+        <v>6.9104774160501335E-3</v>
       </c>
       <c r="W6" s="13">
         <f>V6*(1+CAGR!$C$27)</f>
-        <v>2.7529922845738616E-2</v>
+        <v>6.9615460259667451E-3</v>
       </c>
       <c r="X6" s="13">
         <f>W6*(1+CAGR!$C$27)</f>
-        <v>2.7733369699870301E-2</v>
+        <v>7.0129920342542366E-3</v>
       </c>
       <c r="Y6" s="13">
         <f>X6*(1+CAGR!$C$27)</f>
-        <v>2.7938320031606626E-2</v>
+        <v>7.0648182298964973E-3</v>
       </c>
       <c r="Z6" s="13">
         <f>Y6*(1+CAGR!$C$27)</f>
-        <v>2.8144784951686649E-2</v>
+        <v>7.1170274224880816E-3</v>
       </c>
       <c r="AA6" s="13">
         <f>Z6*(1+CAGR!$C$27)</f>
-        <v>2.8352775652958073E-2</v>
+        <v>7.1696224423865211E-3</v>
       </c>
       <c r="AB6" s="13">
         <f>AA6*(1+CAGR!$C$27)</f>
-        <v>2.856230341098405E-2</v>
+        <v>7.2226061408657647E-3</v>
       </c>
       <c r="AC6" s="13">
         <f>AB6*(1+CAGR!$C$27)</f>
-        <v>2.8773379584654434E-2</v>
+        <v>7.2759813902707506E-3</v>
       </c>
       <c r="AD6" s="13">
         <f>AC6*(1+CAGR!$C$27)</f>
-        <v>2.8986015616801575E-2</v>
+        <v>7.3297510841731214E-3</v>
       </c>
       <c r="AE6" s="13">
         <f>AD6*(1+CAGR!$C$27)</f>
-        <v>2.9200223034820654E-2</v>
+        <v>7.3839181375280911E-3</v>
       </c>
       <c r="AF6" s="13">
         <f>AE6*(1+CAGR!$C$27)</f>
-        <v>2.9416013451294611E-2</v>
+        <v>7.4384854868324683E-3</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -13075,127 +12972,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A7,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2518527696520577E-2</v>
+        <v>2.7300269712990572E-3</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.261103994555551E-2</v>
+        <v>2.7502019424429161E-3</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2704235862544773E-2</v>
+        <v>2.7705260071543242E-3</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2798120499812535E-2</v>
+        <v>2.7910002672386675E-3</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2892698947019774E-2</v>
+        <v>2.8116258326437043E-3</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2987976331440198E-2</v>
+        <v>2.8324038215197349E-3</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.30839578182382E-2</v>
+        <v>2.8533353602802204E-3</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3180648610748875E-2</v>
+        <v>2.8744215836628466E-3</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3278053950760102E-2</v>
+        <v>2.8956636347910406E-3</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3376179118796709E-2</v>
+        <v>2.9170626652359421E-3</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3475029434406741E-2</v>
+        <v>2.938619835078832E-3</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3574610256449845E-2</v>
+        <v>2.9603363129740217E-3</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3674926983387781E-2</v>
+        <v>2.982213276212209E-3</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3775985053577083E-2</v>
+        <v>3.0042519107843007E-3</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3877789945563882E-2</v>
+        <v>3.0264534114457084E-3</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3980347178380911E-2</v>
+        <v>3.0488189817811165E-3</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.40836623118467E-2</v>
+        <v>3.0713498342697329E-3</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4187740946866983E-2</v>
+        <v>3.0940471903510183E-3</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4292588725738334E-2</v>
+        <v>3.1169122804909034E-3</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.439821133245405E-2</v>
+        <v>3.1399463442484937E-3</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4504614493012285E-2</v>
+        <v>3.1631506303432698E-3</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4611803975726471E-2</v>
+        <v>3.1865263967227821E-3</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4719785591538029E-2</v>
+        <v>3.2100749106308466E-3</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.482856519433139E-2</v>
+        <v>3.2337974486762442E-3</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4938148681251342E-2</v>
+        <v>3.2576952969019281E-3</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5048541993022732E-2</v>
+        <v>3.2817697508547429E-3</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5159751114272519E-2</v>
+        <v>3.3060221156556587E-3</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.527178207385421E-2</v>
+        <v>3.3304537060705238E-3</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5384640945174702E-2</v>
+        <v>3.3550658465813401E-3</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5498333846523526E-2</v>
+        <v>3.3798598714580674E-3</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5612866941404534E-2</v>
+        <v>3.404837124830955E-3</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -13205,127 +13102,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$F$27</f>
-        <v>4.2481520860393585E-2</v>
+        <v>1.0742386180296676E-2</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$29)</f>
-        <v>4.279546041722436E-2</v>
+        <v>1.0821772696797115E-2</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$29)</f>
-        <v>4.3111719995639744E-2</v>
+        <v>1.090174588174312E-2</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$29)</f>
-        <v>4.3430316740660287E-2</v>
+        <v>1.0982310070629941E-2</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$29)</f>
-        <v>4.3751267924008685E-2</v>
+        <v>1.1063469630992247E-2</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$29)</f>
-        <v>4.4074590945046128E-2</v>
+        <v>1.1145228962640908E-2</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$29)</f>
-        <v>4.4400303331715546E-2</v>
+        <v>1.122759249790151E-2</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$29)</f>
-        <v>4.4728422741491816E-2</v>
+        <v>1.1310564701854639E-2</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$29)</f>
-        <v>4.5058966962339027E-2</v>
+        <v>1.1394150072577949E-2</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$29)</f>
-        <v>4.5391953913674794E-2</v>
+        <v>1.1478353141390004E-2</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$29)</f>
-        <v>4.5727401647341688E-2</v>
+        <v>1.1563178473095931E-2</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$29)</f>
-        <v>4.6065328348585885E-2</v>
+        <v>1.1648630666234885E-2</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$29)</f>
-        <v>4.6405752337042999E-2</v>
+        <v>1.173471435332935E-2</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$29)</f>
-        <v>4.6748692067731232E-2</v>
+        <v>1.1821434201136273E-2</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$29)</f>
-        <v>4.7094166132051862E-2</v>
+        <v>1.1908794910900055E-2</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$29)</f>
-        <v>4.7442193258797116E-2</v>
+        <v>1.1996801218607418E-2</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$29)</f>
-        <v>4.7792792315165471E-2</v>
+        <v>1.208545789524415E-2</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$29)</f>
-        <v>4.8145982307784517E-2</v>
+        <v>1.2174769747053751E-2</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$29)</f>
-        <v>4.850178238374131E-2</v>
+        <v>1.2264741615797985E-2</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$29)</f>
-        <v>4.8860211831620384E-2</v>
+        <v>1.2355378379019363E-2</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$29)</f>
-        <v>4.9221290082549427E-2</v>
+        <v>1.2446684950305566E-2</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$29)</f>
-        <v>4.9585036711252667E-2</v>
+        <v>1.2538666279555816E-2</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$29)</f>
-        <v>4.9951471437112059E-2</v>
+        <v>1.2631327353249218E-2</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$29)</f>
-        <v>5.0320614125236307E-2</v>
+        <v>1.272467319471509E-2</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$29)</f>
-        <v>5.0692484787537795E-2</v>
+        <v>1.281870886440529E-2</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$29)</f>
-        <v>5.1067103583817462E-2</v>
+        <v>1.2913439460168543E-2</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$29)</f>
-        <v>5.1444490822857715E-2</v>
+        <v>1.300887011752681E-2</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$29)</f>
-        <v>5.1824666963523391E-2</v>
+        <v>1.31050060099537E-2</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$29)</f>
-        <v>5.2207652615870875E-2</v>
+        <v>1.3201852349154922E-2</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$29)</f>
-        <v>5.2593468542265411E-2</v>
+        <v>1.3299414385350832E-2</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$29)</f>
-        <v>5.2982135658506672E-2</v>
+        <v>1.3397697407561049E-2</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -13350,7 +13247,7 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -14377,7 +14274,7 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -14479,127 +14376,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$32</f>
-        <v>9.6856162281727373E-2</v>
+        <v>2.0712433062386879E-2</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$37)</f>
-        <v>9.7544665549863283E-2</v>
+        <v>2.0859667657672821E-2</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$37)</f>
-        <v>9.8238063052285038E-2</v>
+        <v>2.1007948871962129E-2</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$37)</f>
-        <v>9.8936389579719633E-2</v>
+        <v>2.1157284145159369E-2</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$37)</f>
-        <v>9.96396801702044E-2</v>
+        <v>2.1307680970055771E-2</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$37)</f>
-        <v>0.10034797011084502</v>
+        <v>2.1459146892705158E-2</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$37)</f>
-        <v>0.101061294939586</v>
+        <v>2.1611689512802585E-2</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$37)</f>
-        <v>0.10177969044699378</v>
+        <v>2.1765316484065624E-2</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$37)</f>
-        <v>0.10250319267805251</v>
+        <v>2.1920035514618404E-2</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$37)</f>
-        <v>0.10323183793397257</v>
+        <v>2.2075854367378352E-2</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$37)</f>
-        <v>0.10396566277401195</v>
+        <v>2.2232780860445691E-2</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$37)</f>
-        <v>0.10470470401731059</v>
+        <v>2.2390822867495708E-2</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$37)</f>
-        <v>0.10544899874473777</v>
+        <v>2.2549988318173817E-2</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$37)</f>
-        <v>0.1061985843007526</v>
+        <v>2.2710285198493413E-2</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$37)</f>
-        <v>0.10695349829527775</v>
+        <v>2.2871721551236568E-2</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$37)</f>
-        <v>0.10771377860558652</v>
+        <v>2.303430547635758E-2</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$37)</f>
-        <v>0.10847946337820326</v>
+        <v>2.3198045131389369E-2</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$37)</f>
-        <v>0.1092505910308174</v>
+        <v>2.3362948731852788E-2</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$37)</f>
-        <v>0.11002720025421101</v>
+        <v>2.3529024551668817E-2</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$37)</f>
-        <v>0.11080933001420007</v>
+        <v>2.3696280923573718E-2</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$37)</f>
-        <v>0.11159701955358955</v>
+        <v>2.3864726239537112E-2</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$37)</f>
-        <v>0.11239030839414244</v>
+        <v>2.4034368951183039E-2</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$37)</f>
-        <v>0.11318923633856263</v>
+        <v>2.4205217570214019E-2</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$37)</f>
-        <v>0.11399384347249211</v>
+        <v>2.4377280668838125E-2</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$37)</f>
-        <v>0.1148041701665221</v>
+        <v>2.4550566880199069E-2</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$37)</f>
-        <v>0.11562025707821873</v>
+        <v>2.4725084898809386E-2</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$37)</f>
-        <v>0.11644214515416293</v>
+        <v>2.4900843480986659E-2</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$37)</f>
-        <v>0.11726987563200494</v>
+        <v>2.5077851445292867E-2</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$37)</f>
-        <v>0.11810349004253337</v>
+        <v>2.5256117672976849E-2</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$37)</f>
-        <v>0.11894303021175895</v>
+        <v>2.5435651108419916E-2</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$37)</f>
-        <v>0.11978853826301315</v>
+        <v>2.5616460759584628E-2</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -14869,127 +14766,127 @@
       </c>
       <c r="B5" s="14">
         <f>'SYFAFE frgt'!E4*(1+CAGR!$C$40)</f>
-        <v>3.0140633774832004E-2</v>
+        <v>6.445494481840534E-3</v>
       </c>
       <c r="C5" s="14">
         <f>B5*(1+CAGR!$C$40)</f>
-        <v>3.0354888855446266E-2</v>
+        <v>6.4913123617869953E-3</v>
       </c>
       <c r="D5" s="14">
         <f>C5*(1+CAGR!$C$40)</f>
-        <v>3.0570666971040879E-2</v>
+        <v>6.537455938718956E-3</v>
       </c>
       <c r="E5" s="14">
         <f>D5*(1+CAGR!$C$40)</f>
-        <v>3.0787978948129478E-2</v>
+        <v>6.5839275278576029E-3</v>
       </c>
       <c r="F5" s="14">
         <f>E5*(1+CAGR!$C$40)</f>
-        <v>3.1006835690186106E-2</v>
+        <v>6.6307294608819014E-3</v>
       </c>
       <c r="G5" s="14">
         <f>F5*(1+CAGR!$C$40)</f>
-        <v>3.122724817819229E-2</v>
+        <v>6.677864086045586E-3</v>
       </c>
       <c r="H5" s="14">
         <f>G5*(1+CAGR!$C$40)</f>
-        <v>3.1449227471188008E-2</v>
+        <v>6.7253337682949849E-3</v>
       </c>
       <c r="I5" s="14">
         <f>H5*(1+CAGR!$C$40)</f>
-        <v>3.1672784706826565E-2</v>
+        <v>6.7731408893876759E-3</v>
       </c>
       <c r="J5" s="14">
         <f>I5*(1+CAGR!$C$40)</f>
-        <v>3.1897931101933417E-2</v>
+        <v>6.8212878480119919E-3</v>
       </c>
       <c r="K5" s="14">
         <f>J5*(1+CAGR!$C$40)</f>
-        <v>3.2124677953068968E-2</v>
+        <v>6.8697770599073721E-3</v>
       </c>
       <c r="L5" s="14">
         <f>K5*(1+CAGR!$C$40)</f>
-        <v>3.2353036637095357E-2</v>
+        <v>6.9186109579855706E-3</v>
       </c>
       <c r="M5" s="14">
         <f>L5*(1+CAGR!$C$40)</f>
-        <v>3.2583018611747304E-2</v>
+        <v>6.967791992452726E-3</v>
       </c>
       <c r="N5" s="14">
         <f>M5*(1+CAGR!$C$40)</f>
-        <v>3.281463541620698E-2</v>
+        <v>7.0173226309322972E-3</v>
       </c>
       <c r="O5" s="14">
         <f>N5*(1+CAGR!$C$40)</f>
-        <v>3.3047898671682972E-2</v>
+        <v>7.0672053585888774E-3</v>
       </c>
       <c r="P5" s="14">
         <f>O5*(1+CAGR!$C$40)</f>
-        <v>3.3282820081993389E-2</v>
+        <v>7.1174426782528843E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>P5*(1+CAGR!$C$40)</f>
-        <v>3.3519411434153074E-2</v>
+        <v>7.1680371105461368E-3</v>
       </c>
       <c r="R5" s="14">
         <f>Q5*(1+CAGR!$C$40)</f>
-        <v>3.375768459896502E-2</v>
+        <v>7.218991194008326E-3</v>
       </c>
       <c r="S5" s="14">
         <f>R5*(1+CAGR!$C$40)</f>
-        <v>3.399765153161597E-2</v>
+        <v>7.270307485224386E-3</v>
       </c>
       <c r="T5" s="14">
         <f>S5*(1+CAGR!$C$40)</f>
-        <v>3.4239324272276266E-2</v>
+        <v>7.3219885589527666E-3</v>
       </c>
       <c r="U5" s="14">
         <f>T5*(1+CAGR!$C$40)</f>
-        <v>3.4482714946703956E-2</v>
+        <v>7.3740370082546218E-3</v>
       </c>
       <c r="V5" s="14">
         <f>U5*(1+CAGR!$C$40)</f>
-        <v>3.4727835766853198E-2</v>
+        <v>7.4264554446239125E-3</v>
       </c>
       <c r="W5" s="14">
         <f>V5*(1+CAGR!$C$40)</f>
-        <v>3.4974699031486971E-2</v>
+        <v>7.4792464981184399E-3</v>
       </c>
       <c r="X5" s="14">
         <f>W5*(1+CAGR!$C$40)</f>
-        <v>3.5223317126794176E-2</v>
+        <v>7.532412817491803E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>X5*(1+CAGR!$C$40)</f>
-        <v>3.5473702527011097E-2</v>
+        <v>7.5859570703263003E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>Y5*(1+CAGR!$C$40)</f>
-        <v>3.5725867795047286E-2</v>
+        <v>7.6398819431667733E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>Z5*(1+CAGR!$C$40)</f>
-        <v>3.5979825583115896E-2</v>
+        <v>7.6941901416554019E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>AA5*(1+CAGR!$C$40)</f>
-        <v>3.6235588633368496E-2</v>
+        <v>7.7488843906674577E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>AB5*(1+CAGR!$C$40)</f>
-        <v>3.6493169778534409E-2</v>
+        <v>7.8039674344480229E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>AC5*(1+CAGR!$C$40)</f>
-        <v>3.6752581942564574E-2</v>
+        <v>7.8594420367496809E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>AD5*(1+CAGR!$C$40)</f>
-        <v>3.7013838141280002E-2</v>
+        <v>7.9153109809711863E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>AE5*(1+CAGR!$C$40)</f>
-        <v>3.7276951483024831E-2</v>
+        <v>7.9715770702971193E-3</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -15259,127 +15156,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$32</f>
-        <v>9.0421901324495998E-2</v>
+        <v>1.93364834455216E-2</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$43)</f>
-        <v>9.1064666566338784E-2</v>
+        <v>1.9473937085360986E-2</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$43)</f>
-        <v>9.1712000913122621E-2</v>
+        <v>1.961236781615687E-2</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$43)</f>
-        <v>9.2363936844388414E-2</v>
+        <v>1.9751782583572811E-2</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$43)</f>
-        <v>9.3020507070558298E-2</v>
+        <v>1.9892188382645705E-2</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$43)</f>
-        <v>9.3681744534576852E-2</v>
+        <v>2.0033592258136761E-2</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$43)</f>
-        <v>9.4347682413564019E-2</v>
+        <v>2.017600130488496E-2</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$43)</f>
-        <v>9.5018354120479695E-2</v>
+        <v>2.0319422668163035E-2</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$43)</f>
-        <v>9.5693793305800259E-2</v>
+        <v>2.0463863544035985E-2</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$43)</f>
-        <v>9.6374033859206898E-2</v>
+        <v>2.0609331179722128E-2</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$43)</f>
-        <v>9.7059109911286065E-2</v>
+        <v>2.0755832873956725E-2</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$43)</f>
-        <v>9.7749055835241905E-2</v>
+        <v>2.0903375977358189E-2</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$43)</f>
-        <v>9.8443906248620927E-2</v>
+        <v>2.1051967892796904E-2</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$43)</f>
-        <v>9.914369601504891E-2</v>
+        <v>2.1201616075766646E-2</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$43)</f>
-        <v>9.9848460245980167E-2</v>
+        <v>2.1352328034758668E-2</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$43)</f>
-        <v>0.10055823430245923</v>
+        <v>2.1504111331638424E-2</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$43)</f>
-        <v>0.10127305379689508</v>
+        <v>2.1656973582024994E-2</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$43)</f>
-        <v>0.10199295459484793</v>
+        <v>2.1810922455673173E-2</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$43)</f>
-        <v>0.10271797281682882</v>
+        <v>2.1965965676858316E-2</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$43)</f>
-        <v>0.10344814484011189</v>
+        <v>2.2122111024763882E-2</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$43)</f>
-        <v>0.1041835073005596</v>
+        <v>2.2279366333871755E-2</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$43)</f>
-        <v>0.10492409709446092</v>
+        <v>2.2437739494355336E-2</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$43)</f>
-        <v>0.10566995138038254</v>
+        <v>2.2597238452475427E-2</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$43)</f>
-        <v>0.10642110758103331</v>
+        <v>2.2757871210978921E-2</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$43)</f>
-        <v>0.10717760338514187</v>
+        <v>2.2919645829500339E-2</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$43)</f>
-        <v>0.1079394767493477</v>
+        <v>2.3082570424966226E-2</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$43)</f>
-        <v>0.1087067659001055</v>
+        <v>2.3246653172002394E-2</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$43)</f>
-        <v>0.10947950933560324</v>
+        <v>2.3411902303344088E-2</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$43)</f>
-        <v>0.11025774582769374</v>
+        <v>2.3578326110249063E-2</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$43)</f>
-        <v>0.11104151442384001</v>
+        <v>2.3745932942913581E-2</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$43)</f>
-        <v>0.11183085444907451</v>
+        <v>2.3914731210891379E-2</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -15404,7 +15301,7 @@
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -16430,7 +16327,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -16532,127 +16429,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$5:$H$5,,MATCH($A2,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$51:$B$57,0))),0)</f>
-        <v>1.0084146809931577E-3</v>
+        <v>7.8489543431513396E-4</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0147436910357458E-3</v>
+        <v>7.8982159334454202E-4</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.021112423197492E-3</v>
+        <v>7.9477866992260946E-4</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0275211267822748E-3</v>
+        <v>7.9976685809398848E-4</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.033970052658653E-3</v>
+        <v>8.0478635312119379E-4</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0404594532696864E-3</v>
+        <v>8.0983735149224632E-4</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0469895826428171E-3</v>
+        <v>8.1492005092836473E-4</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0535606963998137E-3</v>
+        <v>8.2003465039170499E-4</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0601730517667779E-3</v>
+        <v>8.2518135009314905E-4</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.066826907584213E-3</v>
+        <v>8.3036035150014207E-4</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0735225243171565E-3</v>
+        <v>8.3557185734457859E-4</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0802601640653763E-3</v>
+        <v>8.4081607163073865E-4</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.08704009057363E-3</v>
+        <v>8.460931996432735E-4</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.0938625692419896E-3</v>
+        <v>8.5140344795524162E-4</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1007278671362304E-3</v>
+        <v>8.5674702443619476E-4</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1076362529982852E-3</v>
+        <v>8.6212413826031501E-4</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.114587997256765E-3</v>
+        <v>8.6753499991460326E-4</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1215833720375433E-3</v>
+        <v>8.7297982120711822E-4</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1286226511744103E-3</v>
+        <v>8.7845881527526802E-4</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1357061102197905E-3</v>
+        <v>8.8397219659415319E-4</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1428340264555306E-3</v>
+        <v>8.8952018098496257E-4</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1500066789037525E-3</v>
+        <v>8.9510298562342147E-4</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1572243483377765E-3</v>
+        <v>9.0072082904829294E-4</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1644873172931113E-3</v>
+        <v>9.0637393116993253E-4</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1717958700785151E-3</v>
+        <v>9.1206251327889676E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1791502927871234E-3</v>
+        <v>9.1778679805460544E-4</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1865508733076495E-3</v>
+        <v>9.2354700957405849E-4</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.1939979013356526E-3</v>
+        <v>9.293433733206074E-4</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.2014916683848788E-3</v>
+        <v>9.3517611619278176E-4</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.2090324677986721E-3</v>
+        <v>9.4104546651317125E-4</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A2,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.2166205947614576E-3</v>
+        <v>9.4695165403736324E-4</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -16919,127 +16816,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$5:$H$5,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$51:$B$57,0))),0)</f>
-        <v>1.6209751680771489E-2</v>
+        <v>5.564707374054732E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.631148728925591E-2</v>
+        <v>5.5996325784555346E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.6413861410546543E-2</v>
+        <v>5.6347769803487564E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.6516878052076085E-2</v>
+        <v>5.6701419554612258E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.6620541246428668E-2</v>
+        <v>5.7057288881541043E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.6724855051497726E-2</v>
+        <v>5.7415391714770794E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.6829823550644833E-2</v>
+        <v>5.7775742072228931E-3</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.6935450852859545E-2</v>
+        <v>5.8138354059822156E-3</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7041741092920254E-2</v>
+        <v>5.8503241871988645E-3</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7148698431556034E-2</v>
+        <v>5.8870419792253666E-3</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7256327055609526E-2</v>
+        <v>5.9239902193788715E-3</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7364631178200814E-2</v>
+        <v>5.9611703539974165E-3</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7473615038892363E-2</v>
+        <v>5.9985838384965422E-3</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7583282903854969E-2</v>
+        <v>6.0362321374262647E-3</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7693639066034762E-2</v>
+        <v>6.074116724528407E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.780468784532125E-2</v>
+        <v>6.1122390827942855E-3</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.7916433588716422E-2</v>
+        <v>6.1506007045227648E-3</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8028880670504909E-2</v>
+        <v>6.1892030913786719E-3</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8142033492425224E-2</v>
+        <v>6.2280477544515798E-3</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8255896483842054E-2</v>
+        <v>6.2671362143149577E-3</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8370474101919661E-2</v>
+        <v>6.3064700010856964E-3</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8485770831796349E-2</v>
+        <v>6.3460506544840006E-3</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8601791186760037E-2</v>
+        <v>6.3858797238936661E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8718539708424936E-2</v>
+        <v>6.4259587684227263E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8836020966909322E-2</v>
+        <v>6.4662893569644858E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.8954239561014437E-2</v>
+        <v>6.5068730682589339E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.9073200118404514E-2</v>
+        <v>6.5477114909545438E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.9192907295787917E-2</v>
+        <v>6.5888062236704615E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.9313365779099437E-2</v>
+        <v>6.6301588750590822E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.9434580283683715E-2</v>
+        <v>6.6717710638690229E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$44:$B$50,0))),0)</f>
-        <v>1.955655555447983E-2</v>
+        <v>6.7136444190084871E-3</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -17306,127 +17203,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$38</f>
-        <v>4.8629255042314461E-2</v>
+        <v>1.6694122122164194E-2</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$57)</f>
-        <v>4.8934461867767724E-2</v>
+        <v>1.6798897735366605E-2</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$57)</f>
-        <v>4.9241584231639622E-2</v>
+        <v>1.6904330941046271E-2</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$57)</f>
-        <v>4.9550634156228249E-2</v>
+        <v>1.7010425866383679E-2</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$57)</f>
-        <v>4.9861623739286001E-2</v>
+        <v>1.7117186664462315E-2</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$57)</f>
-        <v>5.0174565154493179E-2</v>
+        <v>1.7224617514431238E-2</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$57)</f>
-        <v>5.0489470651934501E-2</v>
+        <v>1.733272262166868E-2</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$57)</f>
-        <v>5.0806352558578641E-2</v>
+        <v>1.7441506217946649E-2</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$57)</f>
-        <v>5.1125223278760769E-2</v>
+        <v>1.7550972561596594E-2</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$57)</f>
-        <v>5.1446095294668114E-2</v>
+        <v>1.76611259376761E-2</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$57)</f>
-        <v>5.1768981166828584E-2</v>
+        <v>1.7771970658136613E-2</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$57)</f>
-        <v>5.2093893534602448E-2</v>
+        <v>1.7883511061992246E-2</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$57)</f>
-        <v>5.2420845116677099E-2</v>
+        <v>1.7995751515489624E-2</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$57)</f>
-        <v>5.274984871156492E-2</v>
+        <v>1.8108696412278791E-2</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$57)</f>
-        <v>5.3080917198104302E-2</v>
+        <v>1.8222350173585217E-2</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$57)</f>
-        <v>5.3414063535963764E-2</v>
+        <v>1.8336717248382851E-2</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$57)</f>
-        <v>5.3749300766149276E-2</v>
+        <v>1.845180211356829E-2</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$57)</f>
-        <v>5.4086642011514738E-2</v>
+        <v>1.8567609274136011E-2</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$57)</f>
-        <v>5.4426100477275675E-2</v>
+        <v>1.8684143263354734E-2</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$57)</f>
-        <v>5.4767689451526165E-2</v>
+        <v>1.880140864294487E-2</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$57)</f>
-        <v>5.5111422305758988E-2</v>
+        <v>1.8919410003257083E-2</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$57)</f>
-        <v>5.5457312495389051E-2</v>
+        <v>1.9038151963451998E-2</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$57)</f>
-        <v>5.5805373560280119E-2</v>
+        <v>1.9157639171680996E-2</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$57)</f>
-        <v>5.6155619125274815E-2</v>
+        <v>1.9277876305268178E-2</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$57)</f>
-        <v>5.6508062900727969E-2</v>
+        <v>1.9398868070893457E-2</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$57)</f>
-        <v>5.6862718683043316E-2</v>
+        <v>1.9520619204776799E-2</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$57)</f>
-        <v>5.7219600355213542E-2</v>
+        <v>1.964313447286363E-2</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$57)</f>
-        <v>5.7578721887363751E-2</v>
+        <v>1.9766418671011383E-2</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$57)</f>
-        <v>5.7940097337298303E-2</v>
+        <v>1.9890476625177244E-2</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$57)</f>
-        <v>5.8303740851051139E-2</v>
+        <v>2.0015313191607067E-2</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$57)</f>
-        <v>5.8669666663439486E-2</v>
+        <v>2.014093325702546E-2</v>
       </c>
     </row>
   </sheetData>
@@ -17448,7 +17345,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -18466,7 +18363,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -18568,127 +18465,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$44</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$65)</f>
-        <v>1.5467626362604087E-2</v>
+        <v>3.2134746404239212E-5</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -18697,127 +18594,127 @@
       </c>
       <c r="B3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="N3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="T3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="U3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="V3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="W3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="X3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="Y3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="Z3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="AB3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="AC3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="AD3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="AF3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -18826,127 +18723,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -18955,127 +18852,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8435746310157238E-3</v>
+        <v>1.0062761978399154E-5</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8739738636523729E-3</v>
+        <v>1.0125917863391565E-5</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.9045638878872314E-3</v>
+        <v>1.0189470127212942E-5</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.9353459011661155E-3</v>
+        <v>1.0253421257615237E-5</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.9663211084502489E-3</v>
+        <v>1.0317773757964024E-5</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.9974907222634299E-3</v>
+        <v>1.0382530147336492E-5</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.0288559627394962E-3</v>
+        <v>1.044769296062006E-5</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.0604180576700871E-3</v>
+        <v>1.0513264748611601E-5</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.0921782425527046E-3</v>
+        <v>1.0579248078117295E-5</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.1241377606390777E-3</v>
+        <v>1.0645645532053102E-5</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.1562978629838292E-3</v>
+        <v>1.0712459709545877E-5</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.1886598084934484E-3</v>
+        <v>1.0779693226035108E-5</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.2212248639755699E-3</v>
+        <v>1.0847348713375299E-5</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.2539943041885655E-3</v>
+        <v>1.0915428819938993E-5</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.286969411891441E-3</v>
+        <v>1.0983936210720444E-5</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.320151477894052E-3</v>
+        <v>1.1052873567439935E-5</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.3535418011076323E-3</v>
+        <v>1.1122243588648758E-5</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.3871416885956404E-3</v>
+        <v>1.1192048989834847E-5</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.4209524556249221E-3</v>
+        <v>1.1262292503529075E-5</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.4549754257171984E-3</v>
+        <v>1.1332976879412217E-5</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.4892119307008757E-3</v>
+        <v>1.1404104884422593E-5</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.523663310763178E-3</v>
+        <v>1.1475679302864374E-5</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.5583309145026093E-3</v>
+        <v>1.1547702936516572E-5</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.5932160989817445E-3</v>
+        <v>1.1620178604742721E-5</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.6283202297803528E-3</v>
+        <v>1.1693109144601238E-5</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.6636446810488517E-3</v>
+        <v>1.1766497410956478E-5</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.6991908355620985E-3</v>
+        <v>1.1840346276590491E-5</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.734960084773518E-3</v>
+        <v>1.1914658632315477E-5</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.7709538288695742E-3</v>
+        <v>1.1989437387086944E-5</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.807173476824576E-3</v>
+        <v>1.2064685468117578E-5</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -19342,127 +19239,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$44</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$71)</f>
-        <v>1.4440094999999998E-2</v>
+        <v>2.9999999999999997E-5</v>
       </c>
     </row>
   </sheetData>
@@ -19476,7 +19373,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
@@ -19489,179 +19386,161 @@
     <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="72">
-      <c r="A1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="6">
-        <f>[1]Road!C44</f>
-        <v>6.5798820574477688E-4</v>
+        <v>1.14E-3</v>
       </c>
       <c r="C2" s="6">
-        <f>[1]Road!D44</f>
-        <v>1.5847326557973324E-4</v>
+        <v>2.42E-4</v>
       </c>
       <c r="D2" s="6">
-        <f>[1]Road!E44</f>
-        <v>1.0509496345551802E-4</v>
+        <v>2.7E-4</v>
       </c>
       <c r="E2" s="6">
-        <f>[1]Road!F44</f>
-        <v>1.0380732234767244E-4</v>
+        <v>2.5099999999999998E-4</v>
       </c>
       <c r="F2" s="6">
-        <f>[1]Road!G44</f>
-        <v>0</v>
+        <v>2.52E-4</v>
       </c>
       <c r="G2" s="6">
-        <f>[1]Road!H44</f>
-        <v>1.3340249848135008E-4</v>
+        <v>2.7799999999999998E-4</v>
       </c>
       <c r="H2" s="6">
-        <f>[1]Road!I44</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>4.9700000000000005E-4</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="6">
-        <f>[1]Road!C45</f>
-        <v>6.2149365057914963E-2</v>
+        <v>1.1299999999999999E-2</v>
       </c>
       <c r="C3" s="6">
-        <f>[1]Road!D45</f>
-        <v>0</v>
+        <v>2.3500000000000001E-3</v>
       </c>
       <c r="D3" s="6">
-        <f>[1]Road!E45</f>
-        <v>9.9265992802289229E-3</v>
+        <v>2.6700000000000001E-3</v>
       </c>
       <c r="E3" s="6">
-        <f>[1]Road!F45</f>
-        <v>1.0558702581861411E-2</v>
+        <v>2.6700000000000001E-3</v>
       </c>
       <c r="F3" s="6">
-        <f>[1]Road!G45</f>
-        <v>0</v>
+        <v>2.49E-3</v>
       </c>
       <c r="G3" s="6">
-        <f>[1]Road!H45</f>
-        <v>1.2426694100178716E-2</v>
+        <v>2.7100000000000002E-3</v>
       </c>
       <c r="H3" s="6">
-        <f>[1]Road!I45</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>4.8399999999999997E-3</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="6">
-        <f>[1]aircraft!C24</f>
         <v>0</v>
       </c>
       <c r="C4" s="6">
-        <f>[1]aircraft!D24</f>
         <v>0</v>
       </c>
       <c r="D4" s="6">
-        <f>[1]aircraft!E24</f>
         <v>0</v>
       </c>
       <c r="E4" s="6">
-        <f>[1]aircraft!F24</f>
-        <v>2.992789097910166E-2</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="F4" s="6">
-        <f>[1]aircraft!G24</f>
         <v>0</v>
       </c>
       <c r="G4" s="6">
-        <f>[1]aircraft!H24</f>
         <v>0</v>
       </c>
       <c r="H4" s="6">
-        <f>[1]aircraft!I24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="6">
-        <f>[1]rail!C23</f>
-        <v>1.0021251453207708E-3</v>
+        <v>7.7999999999999999E-4</v>
       </c>
       <c r="C5" s="6">
-        <f>[1]rail!D23</f>
         <v>0</v>
       </c>
       <c r="D5" s="6">
-        <f>[1]rail!E23</f>
         <v>0</v>
       </c>
       <c r="E5" s="6">
-        <f>[1]rail!F23</f>
-        <v>1.6108650602655154E-2</v>
+        <v>5.5300000000000002E-3</v>
       </c>
       <c r="F5" s="6">
-        <f>[1]rail!G23</f>
         <v>0</v>
       </c>
       <c r="G5" s="6">
-        <f>[1]rail!H23</f>
         <v>0</v>
       </c>
       <c r="H5" s="6">
-        <f>[1]rail!I23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="6">
-        <v>1.5467626362604087E-2</v>
+        <v>3.2299999999999999E-5</v>
       </c>
       <c r="C6" s="6">
-        <v>4.813365E-3</v>
+        <v>0</v>
       </c>
       <c r="D6" s="6">
-        <v>4.813365E-3</v>
-      </c>
-      <c r="E6" s="35">
-        <v>4.813365E-3</v>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="F6" s="6">
         <v>0</v>
@@ -19670,10 +19549,12 @@
         <v>0</v>
       </c>
       <c r="H6" s="6">
-        <v>1.4440094999999998E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>3.01E-5</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -19684,8 +19565,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="6">
-        <f>[1]Motobikes!D19</f>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="E7" s="6">
         <v>0</v>
@@ -19699,6 +19579,56 @@
       <c r="H7" s="6">
         <v>0</v>
       </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -19719,7 +19649,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -20733,7 +20663,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -21093,127 +21023,127 @@
       </c>
       <c r="B4" s="21">
         <f>'SYFAFE frgt'!D7</f>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="C4" s="21">
         <f t="shared" si="1"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="D4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="E4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="F4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="G4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="H4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="I4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="J4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="K4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="L4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="M4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="N4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="O4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="P4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="Q4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="R4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="S4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="T4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="U4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="V4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="W4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="X4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="Y4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="Z4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="AA4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="AB4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="AC4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="AD4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="AE4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
       <c r="AF4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>7.0099999999999996E-5</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -21748,7 +21678,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -22546,7 +22476,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -23344,7 +23274,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -24142,7 +24072,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -24940,7 +24870,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -25738,7 +25668,7 @@
   <sheetData>
     <row r="1" spans="1:32">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1">
         <v>2020</v>
@@ -26527,21 +26457,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -26685,24 +26600,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7954CBA-CC49-4137-B897-2F07557F3495}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E16404-9CDB-444B-B1EF-816DE1AF2890}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26718,4 +26631,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7954CBA-CC49-4137-B897-2F07557F3495}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
+++ b/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flust\Desktop\EPS 수정\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\administer\Dropbox\kjh\2026\01.EPS\01.EI\01.메일\260108_메일회신\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E3E9456-84DC-40DF-9F1C-120D080F3901}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179D1F4C-35FD-4B01-B6E3-2703D4407B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37650" yWindow="2730" windowWidth="26565" windowHeight="11490" firstSheet="9" activeTab="17" xr2:uid="{9F7C64E4-EC04-4C16-8383-3C9CBB105721}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -45,10 +45,21 @@
     <sheet name="BNVFE-motorbikes-psgr" sheetId="24" r:id="rId30"/>
     <sheet name="BNVFE-motorbikes-frgt" sheetId="25" r:id="rId31"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -317,7 +328,7 @@
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +400,14 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -505,7 +524,7 @@
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -592,6 +611,7 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="2" builtinId="3"/>
@@ -617,9 +637,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -657,7 +677,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -763,7 +783,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -905,7 +925,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -8732,7 +8752,7 @@
     <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="49.5">
+    <row r="1" spans="1:8" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -8762,77 +8782,77 @@
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6">
-        <v>1.1416112460254815E-3</v>
-      </c>
-      <c r="C2" s="6">
-        <v>2.4150976013430963E-4</v>
-      </c>
-      <c r="D2" s="6">
-        <v>2.7043451753289681E-4</v>
-      </c>
-      <c r="E2" s="6">
-        <v>2.5123994341015219E-4</v>
-      </c>
-      <c r="F2" s="6">
-        <v>2.5226752874127518E-4</v>
-      </c>
-      <c r="G2" s="6">
-        <v>2.782720892201053E-4</v>
-      </c>
-      <c r="H2" s="6">
-        <v>4.9724968911319105E-4</v>
+      <c r="B2" s="34">
+        <v>3.4494855384074131E-4</v>
+      </c>
+      <c r="C2" s="34">
+        <v>4.537587230344271E-4</v>
+      </c>
+      <c r="D2" s="34">
+        <v>3.3955214948039873E-4</v>
+      </c>
+      <c r="E2" s="34">
+        <v>3.8835543291031518E-4</v>
+      </c>
+      <c r="F2" s="34">
+        <v>1.147549878921855E-4</v>
+      </c>
+      <c r="G2" s="34">
+        <v>4.3237660652546884E-4</v>
+      </c>
+      <c r="H2" s="34">
+        <v>1.9715881593092513E-4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6">
-        <v>1.1323863316620761E-2</v>
-      </c>
-      <c r="C3" s="6">
-        <v>2.3517867886234905E-3</v>
-      </c>
-      <c r="D3" s="6">
-        <v>2.670252470465435E-3</v>
-      </c>
-      <c r="E3" s="6">
-        <v>2.6714242899436046E-3</v>
-      </c>
-      <c r="F3" s="6">
-        <v>2.4908728293445708E-3</v>
-      </c>
-      <c r="G3" s="6">
-        <v>2.7097729827007914E-3</v>
-      </c>
-      <c r="H3" s="6">
-        <v>4.8421448841371633E-3</v>
+      <c r="B3" s="34">
+        <v>4.3725550386066337E-4</v>
+      </c>
+      <c r="C3" s="34">
+        <v>5.6725587224799282E-4</v>
+      </c>
+      <c r="D3" s="34">
+        <v>4.3041504176466358E-4</v>
+      </c>
+      <c r="E3" s="34">
+        <v>5.3012016240422985E-4</v>
+      </c>
+      <c r="F3" s="34">
+        <v>1.454629958370202E-4</v>
+      </c>
+      <c r="G3" s="34">
+        <v>5.4052551857085361E-4</v>
+      </c>
+      <c r="H3" s="34">
+        <v>2.4647349003975621E-4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="B4" s="34">
+        <v>0</v>
+      </c>
+      <c r="C4" s="34">
+        <v>0</v>
+      </c>
+      <c r="D4" s="34">
+        <v>0</v>
+      </c>
+      <c r="E4" s="34">
         <v>6.3999198108760673E-3</v>
       </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="F4" s="34">
+        <v>0</v>
+      </c>
+      <c r="G4" s="34">
+        <v>0</v>
+      </c>
+      <c r="H4" s="34">
         <v>0</v>
       </c>
     </row>
@@ -8840,25 +8860,25 @@
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="34">
         <v>7.8030705230531052E-4</v>
       </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="C5" s="34">
+        <v>0</v>
+      </c>
+      <c r="D5" s="34">
+        <v>0</v>
+      </c>
+      <c r="E5" s="34">
         <v>5.5294125429859176E-3</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="F5" s="34">
+        <v>0</v>
+      </c>
+      <c r="G5" s="34">
+        <v>0</v>
+      </c>
+      <c r="H5" s="34">
         <v>0</v>
       </c>
     </row>
@@ -8866,25 +8886,25 @@
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="34">
         <v>3.2293482418666772E-5</v>
       </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C6" s="34">
+        <v>0</v>
+      </c>
+      <c r="D6" s="34">
         <v>1.0049397002369564E-5</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="34">
         <v>1.0049397002369565E-5</v>
       </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="F6" s="34">
+        <v>0</v>
+      </c>
+      <c r="G6" s="34">
+        <v>0</v>
+      </c>
+      <c r="H6" s="34">
         <v>3.0148191007108693E-5</v>
       </c>
     </row>
@@ -8892,25 +8912,25 @@
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>7.0063905313000519E-5</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
+        <v>5.9831905534842047E-5</v>
+      </c>
+      <c r="E7" s="34">
+        <v>0</v>
+      </c>
+      <c r="F7" s="34">
+        <v>0</v>
+      </c>
+      <c r="G7" s="34">
+        <v>0</v>
+      </c>
+      <c r="H7" s="34">
         <v>0</v>
       </c>
     </row>
@@ -9040,127 +9060,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1398918869414251E-3</v>
+        <v>3.4442903335454861E-4</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1381751173515334E-3</v>
+        <v>3.4391029530832429E-4</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1364609333558181E-3</v>
+        <v>3.4339233852365039E-4</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.134749331060165E-3</v>
+        <v>3.4287516182388364E-4</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1330403065763243E-3</v>
+        <v>3.4235876403415297E-4</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1313338560219027E-3</v>
+        <v>3.4184314398135672E-4</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1296299755203536E-3</v>
+        <v>3.4132830049416E-4</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1279286612009692E-3</v>
+        <v>3.4081423240299203E-4</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.126229909198871E-3</v>
+        <v>3.4030093854004357E-4</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1245337156550014E-3</v>
+        <v>3.3978841773926413E-4</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1228400767161152E-3</v>
+        <v>3.3927666883635946E-4</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1211489885347699E-3</v>
+        <v>3.3876569066878875E-4</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.119460447269318E-3</v>
+        <v>3.382554820757621E-4</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1177744490838977E-3</v>
+        <v>3.3774604189823791E-4</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1160909901484241E-3</v>
+        <v>3.3723736897892006E-4</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1144100666385813E-3</v>
+        <v>3.3672946216225554E-4</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1127316747358124E-3</v>
+        <v>3.3622232029443166E-4</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1110558106273121E-3</v>
+        <v>3.3571594222337343E-4</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1093824705060173E-3</v>
+        <v>3.3521032679874097E-4</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1077116505705986E-3</v>
+        <v>3.3470547287192697E-4</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1060433470254519E-3</v>
+        <v>3.3420137929605399E-4</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1043775560806892E-3</v>
+        <v>3.3369804492597191E-4</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1027142739521308E-3</v>
+        <v>3.331954686182552E-4</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.1010534968612961E-3</v>
+        <v>3.3269364923120049E-4</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.0993952210353953E-3</v>
+        <v>3.3219258562482395E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.0977394427073204E-3</v>
+        <v>3.3169227666085858E-4</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.0960861581156374E-3</v>
+        <v>3.3119272120275172E-4</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.0944353635045771E-3</v>
+        <v>3.3069391811566245E-4</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.0927870551240269E-3</v>
+        <v>3.3019586626645904E-4</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.091141229229522E-3</v>
+        <v>3.2969856452371636E-4</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.0894978820822371E-3</v>
+        <v>3.2920201175771325E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -9170,127 +9190,127 @@
       </c>
       <c r="B3" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4211563070789988E-4</v>
+        <v>4.5489705822072995E-4</v>
       </c>
       <c r="C3" s="14">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4272302121655087E-4</v>
+        <v>4.5603824912512832E-4</v>
       </c>
       <c r="D3" s="14">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4333193547329248E-4</v>
+        <v>4.5718230291170357E-4</v>
       </c>
       <c r="E3" s="14">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4394237730072024E-4</v>
+        <v>4.5832922676250937E-4</v>
       </c>
       <c r="F3" s="14">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4455435053101932E-4</v>
+        <v>4.5947902787761688E-4</v>
       </c>
       <c r="G3" s="14">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.451678590059887E-4</v>
+        <v>4.6063171347515995E-4</v>
       </c>
       <c r="H3" s="14">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.457829065770651E-4</v>
+        <v>4.6178729079138041E-4</v>
       </c>
       <c r="I3" s="14">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4639949710534729E-4</v>
+        <v>4.6294576708067348E-4</v>
       </c>
       <c r="J3" s="14">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4701763446162038E-4</v>
+        <v>4.6410714961563337E-4</v>
       </c>
       <c r="K3" s="14">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4763732252637989E-4</v>
+        <v>4.6527144568709889E-4</v>
       </c>
       <c r="L3" s="14">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.482585651898564E-4</v>
+        <v>4.6643866260419922E-4</v>
       </c>
       <c r="M3" s="14">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4888136635203975E-4</v>
+        <v>4.6760880769439975E-4</v>
       </c>
       <c r="N3" s="14">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.4950572992270362E-4</v>
+        <v>4.6878188830354821E-4</v>
       </c>
       <c r="O3" s="14">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5013165982143009E-4</v>
+        <v>4.6995791179592068E-4</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5075915997763414E-4</v>
+        <v>4.7113688555426781E-4</v>
       </c>
       <c r="Q3" s="14">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5138823433058853E-4</v>
+        <v>4.7231881697986131E-4</v>
       </c>
       <c r="R3" s="14">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5201888682944827E-4</v>
+        <v>4.7350371349254018E-4</v>
       </c>
       <c r="S3" s="14">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5265112143327555E-4</v>
+        <v>4.7469158253075748E-4</v>
       </c>
       <c r="T3" s="14">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5328494211106461E-4</v>
+        <v>4.7588243155162696E-4</v>
       </c>
       <c r="U3" s="14">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5392035284176658E-4</v>
+        <v>4.7707626803096992E-4</v>
       </c>
       <c r="V3" s="14">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5455735761431461E-4</v>
+        <v>4.7827309946336201E-4</v>
       </c>
       <c r="W3" s="14">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5519596042764865E-4</v>
+        <v>4.7947293336218045E-4</v>
       </c>
       <c r="X3" s="14">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5583616529074085E-4</v>
+        <v>4.8067577725965102E-4</v>
       </c>
       <c r="Y3" s="14">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.564779762226205E-4</v>
+        <v>4.8188163870689556E-4</v>
       </c>
       <c r="Z3" s="14">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5712139725239934E-4</v>
+        <v>4.8309052527397919E-4</v>
       </c>
       <c r="AA3" s="14">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5776643241929697E-4</v>
+        <v>4.8430244454995787E-4</v>
       </c>
       <c r="AB3" s="14">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5841308577266597E-4</v>
+        <v>4.8551740414292614E-4</v>
       </c>
       <c r="AC3" s="14">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5906136137201748E-4</v>
+        <v>4.8673541168006473E-4</v>
       </c>
       <c r="AD3" s="14">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5971126328704671E-4</v>
+        <v>4.8795647480768856E-4</v>
       </c>
       <c r="AE3" s="14">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6036279559765838E-4</v>
+        <v>4.8918060119129475E-4</v>
       </c>
       <c r="AF3" s="14">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6101596239399232E-4</v>
+        <v>4.9040779851561062E-4</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -9300,127 +9320,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7122647055143658E-4</v>
+        <v>3.4054650978686355E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7202074276202809E-4</v>
+        <v>3.4154378202429561E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7281734095630118E-4</v>
+        <v>3.4254397472012905E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7361627194577467E-4</v>
+        <v>3.4354709642676998E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.744175425619145E-4</v>
+        <v>3.4455315572166993E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7522115965619221E-4</v>
+        <v>3.4556216120739899E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7602713010014353E-4</v>
+        <v>3.4657412151171941E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7683546078542703E-4</v>
+        <v>3.4758904528765935E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7764615862388323E-4</v>
+        <v>3.4860694121358694E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.784592305475936E-4</v>
+        <v>3.4962781799328441E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7927468350893981E-4</v>
+        <v>3.5065168435602259E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8009252448066318E-4</v>
+        <v>3.5167854905663551E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8091276045592438E-4</v>
+        <v>3.527084208755952E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8173539844836314E-4</v>
+        <v>3.5374130861908691E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.825604454921583E-4</v>
+        <v>3.5477722111908433E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8338790864208791E-4</v>
+        <v>3.5581616723342509E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8421779497358953E-4</v>
+        <v>3.5685815584588648E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8505011158282075E-4</v>
+        <v>3.5790319586626149E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.858848655867199E-4</v>
+        <v>3.5895129623043502E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8672206412306688E-4</v>
+        <v>3.6000246590046014E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8756171435054419E-4</v>
+        <v>3.6105671386463489E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.884038234487982E-4</v>
+        <v>3.6211404913757901E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8924839861850044E-4</v>
+        <v>3.6317448076031108E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9009544708140925E-4</v>
+        <v>3.6423801780032579E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9094497608043144E-4</v>
+        <v>3.6530466935167158E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9179699287968438E-4</v>
+        <v>3.6637444453502829E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.926515047645579E-4</v>
+        <v>3.6744735249778516E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9350851904177684E-4</v>
+        <v>3.6852340241411906E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9436804303946325E-4</v>
+        <v>3.6960260348507302E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9523008410719935E-4</v>
+        <v>3.7068496493863472E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9609464961609009E-4</v>
+        <v>3.7177049602981564E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -9430,127 +9450,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5146183585679277E-4</v>
+        <v>3.8869842429936337E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5168392427648293E-4</v>
+        <v>3.890417186147594E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5190620884230395E-4</v>
+        <v>3.8938531612404465E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5212868972748997E-4</v>
+        <v>3.8972921709499672E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5235136710542819E-4</v>
+        <v>3.9007342179562968E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5257424114965893E-4</v>
+        <v>3.9041793049419439E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5279731203387576E-4</v>
+        <v>3.9076274345917862E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5302057993192568E-4</v>
+        <v>3.9110786095930718E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5324404501780921E-4</v>
+        <v>3.9145328326354228E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.534677074656805E-4</v>
+        <v>3.9179901064108368E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5369156744984759E-4</v>
+        <v>3.9214504336136891E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5391562514477249E-4</v>
+        <v>3.924913816940734E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5413988072507117E-4</v>
+        <v>3.9283802590911075E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5436433436551393E-4</v>
+        <v>3.9318497627663308E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5458898624102535E-4</v>
+        <v>3.9353223306703094E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5481383652668457E-4</v>
+        <v>3.9387979655093375E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5503888539772526E-4</v>
+        <v>3.9422766699921002E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5526413302953596E-4</v>
+        <v>3.9457584468296738E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5548957959766009E-4</v>
+        <v>3.949243298735529E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5571522527779604E-4</v>
+        <v>3.9527312284255337E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5594107024579744E-4</v>
+        <v>3.9562222386179546E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5616711467767324E-4</v>
+        <v>3.9597163320334583E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5639335874958781E-4</v>
+        <v>3.9632135113951145E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5661980263786105E-4</v>
+        <v>3.9667137794283981E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5684644651896869E-4</v>
+        <v>3.9702171388611912E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.570732905695423E-4</v>
+        <v>3.9737235924237847E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5730033496636939E-4</v>
+        <v>3.9772331428488815E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5752757988639364E-4</v>
+        <v>3.9807457928715974E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5775502550671499E-4</v>
+        <v>3.9842615452294642E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5798267200458986E-4</v>
+        <v>3.9877804026624311E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5821051955743113E-4</v>
+        <v>3.9913023679128676E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -9560,127 +9580,127 @@
       </c>
       <c r="B6" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A6,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5309183671566799E-4</v>
+        <v>1.1512996065262306E-4</v>
       </c>
       <c r="C6" s="14">
         <f>IFERROR(B6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5391883819421505E-4</v>
+        <v>1.155061586719679E-4</v>
       </c>
       <c r="D6" s="14">
         <f>IFERROR(C6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5474854197819557E-4</v>
+        <v>1.1588358595386922E-4</v>
       </c>
       <c r="E6" s="14">
         <f>IFERROR(D6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.555809568976477E-4</v>
+        <v>1.1626224651505851E-4</v>
       </c>
       <c r="F6" s="14">
         <f>IFERROR(E6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5641609181146271E-4</v>
+        <v>1.1664214438539231E-4</v>
       </c>
       <c r="G6" s="14">
         <f>IFERROR(F6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5725395560747904E-4</v>
+        <v>1.1702328360789512E-4</v>
       </c>
       <c r="H6" s="14">
         <f>IFERROR(G6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5809455720257699E-4</v>
+        <v>1.1740566823880238E-4</v>
       </c>
       <c r="I6" s="14">
         <f>IFERROR(H6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5893790554277362E-4</v>
+        <v>1.1778930234760365E-4</v>
       </c>
       <c r="J6" s="14">
         <f>IFERROR(I6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.5978400960331797E-4</v>
+        <v>1.1817419001708597E-4</v>
       </c>
       <c r="K6" s="14">
         <f>IFERROR(J6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6063287838878647E-4</v>
+        <v>1.1856033534337724E-4</v>
       </c>
       <c r="L6" s="14">
         <f>IFERROR(K6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6148452093317895E-4</v>
+        <v>1.1894774243598987E-4</v>
       </c>
       <c r="M6" s="14">
         <f>IFERROR(L6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6233894630001462E-4</v>
+        <v>1.1933641541786447E-4</v>
       </c>
       <c r="N6" s="14">
         <f>IFERROR(M6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6319616358242868E-4</v>
+        <v>1.1972635842541374E-4</v>
       </c>
       <c r="O6" s="14">
         <f>IFERROR(N6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.640561819032689E-4</v>
+        <v>1.2011757560856654E-4</v>
       </c>
       <c r="P6" s="14">
         <f>IFERROR(O6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6491901041519292E-4</v>
+        <v>1.2051007113081197E-4</v>
       </c>
       <c r="Q6" s="14">
         <f>IFERROR(P6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6578465830076544E-4</v>
+        <v>1.2090384916924374E-4</v>
       </c>
       <c r="R6" s="14">
         <f>IFERROR(Q6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6665313477255612E-4</v>
+        <v>1.2129891391460463E-4</v>
       </c>
       <c r="S6" s="14">
         <f>IFERROR(R6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6752444907323763E-4</v>
+        <v>1.2169526957133103E-4</v>
       </c>
       <c r="T6" s="14">
         <f>IFERROR(S6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6839861047568383E-4</v>
+        <v>1.2209292035759775E-4</v>
       </c>
       <c r="U6" s="14">
         <f>IFERROR(T6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.6927562828306861E-4</v>
+        <v>1.2249187050536285E-4</v>
       </c>
       <c r="V6" s="14">
         <f>IFERROR(U6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.701555118289649E-4</v>
+        <v>1.2289212426041277E-4</v>
       </c>
       <c r="W6" s="14">
         <f>IFERROR(V6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7103827047744391E-4</v>
+        <v>1.2329368588240742E-4</v>
       </c>
       <c r="X6" s="14">
         <f>IFERROR(W6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7192391362317481E-4</v>
+        <v>1.2369655964492555E-4</v>
       </c>
       <c r="Y6" s="14">
         <f>IFERROR(X6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7281245069152483E-4</v>
+        <v>1.2410074983551023E-4</v>
       </c>
       <c r="Z6" s="14">
         <f>IFERROR(Y6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7370389113865942E-4</v>
+        <v>1.2450626075571452E-4</v>
       </c>
       <c r="AA6" s="14">
         <f>IFERROR(Z6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7459824445164299E-4</v>
+        <v>1.2491309672114717E-4</v>
       </c>
       <c r="AB6" s="14">
         <f>IFERROR(AA6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7549552014853975E-4</v>
+        <v>1.2532126206151858E-4</v>
       </c>
       <c r="AC6" s="14">
         <f>IFERROR(AB6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7639572777851516E-4</v>
+        <v>1.2573076112068693E-4</v>
       </c>
       <c r="AD6" s="14">
         <f>IFERROR(AC6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.772988769219374E-4</v>
+        <v>1.2614159825670435E-4</v>
       </c>
       <c r="AE6" s="14">
         <f>IFERROR(AD6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7820497719047946E-4</v>
+        <v>1.265537778418633E-4</v>
       </c>
       <c r="AF6" s="14">
         <f>IFERROR(AE6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7911403822722142E-4</v>
+        <v>1.2696730426274314E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -9690,127 +9710,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7886228613719304E-4</v>
+        <v>4.3329364905354774E-4</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.7945373482337455E-4</v>
+        <v>4.3421263656890301E-4</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8004643793357026E-4</v>
+        <v>4.3513357319672558E-4</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8064039812833154E-4</v>
+        <v>4.3605646307095565E-4</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8123561807385258E-4</v>
+        <v>4.3698131033430119E-4</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8183210044198246E-4</v>
+        <v>4.3790811913825664E-4</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8242984791023703E-4</v>
+        <v>4.3883689364312143E-4</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8302886316181096E-4</v>
+        <v>4.3976763801801871E-4</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8362914888558982E-4</v>
+        <v>4.4070035644091414E-4</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8423070777616218E-4</v>
+        <v>4.4163505309863455E-4</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8483354253383157E-4</v>
+        <v>4.4257173218688664E-4</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8543765586462876E-4</v>
+        <v>4.4351039791027611E-4</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8604305048032379E-4</v>
+        <v>4.4445105448232621E-4</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8664972909843818E-4</v>
+        <v>4.4539370612549687E-4</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8725769444225719E-4</v>
+        <v>4.4633835707120356E-4</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8786694924084197E-4</v>
+        <v>4.4728501155983632E-4</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8847749622904178E-4</v>
+        <v>4.4823367384077878E-4</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8908933814750633E-4</v>
+        <v>4.4918434817242724E-4</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.8970247774269813E-4</v>
+        <v>4.5013703882220975E-4</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9031691776690473E-4</v>
+        <v>4.5109175006660532E-4</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9093266097825107E-4</v>
+        <v>4.5204848619116305E-4</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9154971014071191E-4</v>
+        <v>4.5300725149052145E-4</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9216806802412424E-4</v>
+        <v>4.5396805026842773E-4</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9278773740419969E-4</v>
+        <v>4.5493088683775697E-4</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9340872106253698E-4</v>
+        <v>4.5589576552053162E-4</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9403102178663439E-4</v>
+        <v>4.5686269064794085E-4</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9465464236990232E-4</v>
+        <v>4.5783166656035998E-4</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9527958561167587E-4</v>
+        <v>4.5880269760737005E-4</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9590585431722727E-4</v>
+        <v>4.5977578814777718E-4</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9653345129777858E-4</v>
+        <v>4.6075094254963232E-4</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9716237937051429E-4</v>
+        <v>4.617281651902507E-4</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -9820,127 +9840,127 @@
       </c>
       <c r="B8" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A8,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.96930465916364E-4</v>
+        <v>1.9703224437365305E-4</v>
       </c>
       <c r="C8" s="14">
         <f>IFERROR(B8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9661144765370099E-4</v>
+        <v>1.969057540724944E-4</v>
       </c>
       <c r="D8" s="14">
         <f>IFERROR(C8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9629263419363897E-4</v>
+        <v>1.9677934497528457E-4</v>
       </c>
       <c r="E8" s="14">
         <f>IFERROR(D8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9597402540469922E-4</v>
+        <v>1.9665301702989242E-4</v>
       </c>
       <c r="F8" s="14">
         <f>IFERROR(E8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9565562115548741E-4</v>
+        <v>1.9652677018422031E-4</v>
       </c>
       <c r="G8" s="14">
         <f>IFERROR(F8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9533742131469363E-4</v>
+        <v>1.9640060438620404E-4</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(G8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9501942575109223E-4</v>
+        <v>1.9627451958381282E-4</v>
       </c>
       <c r="I8" s="14">
         <f>IFERROR(H8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9470163433354181E-4</v>
+        <v>1.9614851572504925E-4</v>
       </c>
       <c r="J8" s="14">
         <f>IFERROR(I8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.943840469309852E-4</v>
+        <v>1.9602259275794935E-4</v>
       </c>
       <c r="K8" s="14">
         <f>IFERROR(J8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9406666341244936E-4</v>
+        <v>1.9589675063058247E-4</v>
       </c>
       <c r="L8" s="14">
         <f>IFERROR(K8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9374948364704519E-4</v>
+        <v>1.9577098929105129E-4</v>
       </c>
       <c r="M8" s="14">
         <f>IFERROR(L8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9343250750396781E-4</v>
+        <v>1.9564530868749184E-4</v>
       </c>
       <c r="N8" s="14">
         <f>IFERROR(M8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9311573485249615E-4</v>
+        <v>1.9551970876807343E-4</v>
       </c>
       <c r="O8" s="14">
         <f>IFERROR(N8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.927991655619933E-4</v>
+        <v>1.9539418948099865E-4</v>
       </c>
       <c r="P8" s="14">
         <f>IFERROR(O8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.924827995019059E-4</v>
+        <v>1.9526875077450332E-4</v>
       </c>
       <c r="Q8" s="14">
         <f>IFERROR(P8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9216663654176466E-4</v>
+        <v>1.9514339259685653E-4</v>
       </c>
       <c r="R8" s="14">
         <f>IFERROR(Q8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9185067655118384E-4</v>
+        <v>1.9501811489636053E-4</v>
       </c>
       <c r="S8" s="14">
         <f>IFERROR(R8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9153491939986165E-4</v>
+        <v>1.9489291762135079E-4</v>
       </c>
       <c r="T8" s="14">
         <f>IFERROR(S8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9121936495757977E-4</v>
+        <v>1.9476780072019597E-4</v>
       </c>
       <c r="U8" s="14">
         <f>IFERROR(T8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9090401309420347E-4</v>
+        <v>1.9464276414129782E-4</v>
       </c>
       <c r="V8" s="14">
         <f>IFERROR(U8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9058886367968162E-4</v>
+        <v>1.9451780783309125E-4</v>
       </c>
       <c r="W8" s="14">
         <f>IFERROR(V8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.9027391658404667E-4</v>
+        <v>1.943929317440443E-4</v>
       </c>
       <c r="X8" s="14">
         <f>IFERROR(W8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8995917167741435E-4</v>
+        <v>1.9426813582265802E-4</v>
       </c>
       <c r="Y8" s="14">
         <f>IFERROR(X8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8964462882998387E-4</v>
+        <v>1.9414342001746658E-4</v>
       </c>
       <c r="Z8" s="14">
         <f>IFERROR(Y8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.893302879120377E-4</v>
+        <v>1.9401878427703718E-4</v>
       </c>
       <c r="AA8" s="14">
         <f>IFERROR(Z8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8901614879394157E-4</v>
+        <v>1.9389422854997E-4</v>
       </c>
       <c r="AB8" s="14">
         <f>IFERROR(AA8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8870221134614451E-4</v>
+        <v>1.9376975278489827E-4</v>
       </c>
       <c r="AC8" s="14">
         <f>IFERROR(AB8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8838847543917878E-4</v>
+        <v>1.9364535693048817E-4</v>
       </c>
       <c r="AD8" s="14">
         <f>IFERROR(AC8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8807494094365954E-4</v>
+        <v>1.9352104093543884E-4</v>
       </c>
       <c r="AE8" s="14">
         <f>IFERROR(AD8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8776160773028523E-4</v>
+        <v>1.9339680474848237E-4</v>
       </c>
       <c r="AF8" s="14">
         <f>IFERROR(AE8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8744847566983715E-4</v>
+        <v>1.9327264831838373E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -10067,127 +10087,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.6484314679036462E-4</v>
+        <v>7.354262652985215E-5</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.7354617590480181E-4</v>
+        <v>7.4505325209881261E-5</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.8236313071153563E-4</v>
+        <v>7.5480625952037615E-5</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>6.9129550253768841E-4</v>
+        <v>7.6468693721718132E-5</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.0034480223237579E-4</v>
+        <v>7.7469695643774409E-5</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.0951256042225605E-4</v>
+        <v>7.8483801030780756E-5</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.1880032777042551E-4</v>
+        <v>7.9511181411672256E-5</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.2820967523870225E-4</v>
+        <v>8.0552010560757669E-5</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3774219435334342E-4</v>
+        <v>8.1606464527112202E-5</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.4739949747424099E-4</v>
+        <v>8.2674721664354972E-5</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.5718321806764145E-4</v>
+        <v>8.3756962660816285E-5</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.6709501098243531E-4</v>
+        <v>8.4853370570099829E-5</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.771365527300631E-4</v>
+        <v>8.5964130842044941E-5</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.8730954176808616E-4</v>
+        <v>8.708943135409416E-5</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.9761569878746875E-4</v>
+        <v>8.8229462443071383E-5</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.0805676700362102E-4</v>
+        <v>8.938441693737606E-5</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.1863451245125216E-4</v>
+        <v>9.0554490189598765E-5</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.293507242830828E-4</v>
+        <v>9.1739880109563757E-5</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.4020721507246769E-4</v>
+        <v>9.2940787197804027E-5</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.5120582111998045E-4</v>
+        <v>9.4157414579474632E-5</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.6234840276401071E-4</v>
+        <v>9.5389968038709865E-5</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.7363684469542776E-4</v>
+        <v>9.6638656053430269E-5</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.8507305627636302E-4</v>
+        <v>9.790368983060521E-5</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>8.966589718631653E-4</v>
+        <v>9.9185283341977085E-5</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.0839655113358398E-4</v>
+        <v>1.0048365336025317E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.2028777941823502E-4</v>
+        <v>1.0179901949577121E-4</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.3233466803640586E-4</v>
+        <v>1.0313160423364506E-4</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.4453925463625619E-4</v>
+        <v>1.0448163297139641E-4</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5690360353947225E-4</v>
+        <v>1.058493340570793E-4</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6942980609043253E-4</v>
+        <v>1.0723493882790359E-4</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8211998100994412E-4</v>
+        <v>1.0863868164936403E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -10197,127 +10217,127 @@
       </c>
       <c r="B3" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5764518800147088E-4</v>
+        <v>1.7491806860027309E-4</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5723619340754518E-4</v>
+        <v>1.744642612538873E-4</v>
       </c>
       <c r="D3" s="21">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5682825990898168E-4</v>
+        <v>1.7401163126504543E-4</v>
       </c>
       <c r="E3" s="21">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5642138475287511E-4</v>
+        <v>1.7356017557921166E-4</v>
       </c>
       <c r="F3" s="21">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5601556519346236E-4</v>
+        <v>1.7310989114977492E-4</v>
       </c>
       <c r="G3" s="21">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5561079849210391E-4</v>
+        <v>1.7266077493802818E-4</v>
       </c>
       <c r="H3" s="21">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5520708191726538E-4</v>
+        <v>1.7221282391314809E-4</v>
       </c>
       <c r="I3" s="21">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5480441274449904E-4</v>
+        <v>1.7176603505217441E-4</v>
       </c>
       <c r="J3" s="21">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5440278825642554E-4</v>
+        <v>1.7132040533998977E-4</v>
       </c>
       <c r="K3" s="21">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5400220574271543E-4</v>
+        <v>1.7087593176929911E-4</v>
       </c>
       <c r="L3" s="21">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5360266250007097E-4</v>
+        <v>1.7043261134060955E-4</v>
       </c>
       <c r="M3" s="21">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5320415583220783E-4</v>
+        <v>1.6999044106221007E-4</v>
       </c>
       <c r="N3" s="21">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5280668304983697E-4</v>
+        <v>1.6954941795015136E-4</v>
       </c>
       <c r="O3" s="21">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5241024147064639E-4</v>
+        <v>1.6910953902822567E-4</v>
       </c>
       <c r="P3" s="21">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5201482841928308E-4</v>
+        <v>1.686708013279467E-4</v>
       </c>
       <c r="Q3" s="21">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5162044122733498E-4</v>
+        <v>1.682332018885296E-4</v>
       </c>
       <c r="R3" s="21">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5122707723331299E-4</v>
+        <v>1.6779673775687101E-4</v>
       </c>
       <c r="S3" s="21">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5083473378263291E-4</v>
+        <v>1.6736140598752904E-4</v>
       </c>
       <c r="T3" s="21">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5044340822759761E-4</v>
+        <v>1.6692720364270349E-4</v>
       </c>
       <c r="U3" s="21">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.5005309792737919E-4</v>
+        <v>1.6649412779221599E-4</v>
       </c>
       <c r="V3" s="21">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4966380024800105E-4</v>
+        <v>1.6606217551349021E-4</v>
       </c>
       <c r="W3" s="21">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4927551256232023E-4</v>
+        <v>1.6563134389153215E-4</v>
       </c>
       <c r="X3" s="21">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.488882322500096E-4</v>
+        <v>1.6520163001891049E-4</v>
       </c>
       <c r="Y3" s="21">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4850195669754022E-4</v>
+        <v>1.647730309957369E-4</v>
       </c>
       <c r="Z3" s="21">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4811668329816366E-4</v>
+        <v>1.6434554392964656E-4</v>
       </c>
       <c r="AA3" s="21">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4773240945189448E-4</v>
+        <v>1.639191659357786E-4</v>
       </c>
       <c r="AB3" s="21">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4734913256549262E-4</v>
+        <v>1.6349389413675662E-4</v>
       </c>
       <c r="AC3" s="21">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4696685005244589E-4</v>
+        <v>1.6306972566266928E-4</v>
       </c>
       <c r="AD3" s="21">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4658555933295259E-4</v>
+        <v>1.6264665765105095E-4</v>
       </c>
       <c r="AE3" s="21">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4620525783390402E-4</v>
+        <v>1.6222468724686238E-4</v>
       </c>
       <c r="AF3" s="21">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.458259429888672E-4</v>
+        <v>1.6180381160247142E-4</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -10327,127 +10347,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0454580595246884E-4</v>
+        <v>6.4117197267208695E-5</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0427457236776997E-4</v>
+        <v>6.3950851643898506E-5</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0400404247134247E-4</v>
+        <v>6.3784937587587102E-5</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0373421443753784E-4</v>
+        <v>6.3619453978617274E-5</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0346508644544406E-4</v>
+        <v>6.345439970023666E-5</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0319665667887329E-4</v>
+        <v>6.3289773638590199E-5</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0292892332634957E-4</v>
+        <v>6.3125574682712635E-5</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0266188458109667E-4</v>
+        <v>6.2961801724520968E-5</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0239553864102585E-4</v>
+        <v>6.2798453658807031E-5</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0212988370872371E-4</v>
+        <v>6.2635529383229987E-5</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0186491799144004E-4</v>
+        <v>6.2473027798308939E-5</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0160063970107576E-4</v>
+        <v>6.231094780741547E-5</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0133704705417084E-4</v>
+        <v>6.2149288316766245E-5</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0107413827189223E-4</v>
+        <v>6.1988048235415652E-5</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.008119115800219E-4</v>
+        <v>6.1827226475248416E-5</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0055036520894485E-4</v>
+        <v>6.1666821950972294E-5</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0028949739363717E-4</v>
+        <v>6.1506833580110689E-5</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0002930637365412E-4</v>
+        <v>6.1347260282995414E-5</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9769790393118264E-5</v>
+        <v>6.1188100982759343E-5</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9510947700707611E-5</v>
+        <v>6.1029354605329192E-5</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9252776549643793E-5</v>
+        <v>6.0871020079418251E-5</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8995275197680287E-5</v>
+        <v>6.0713096336519152E-5</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8738441907090662E-5</v>
+        <v>6.0555582310896658E-5</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8482274944656828E-5</v>
+        <v>6.0398476939580481E-5</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8226772581657372E-5</v>
+        <v>6.0241779162358102E-5</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7971933093855872E-5</v>
+        <v>6.0085487921767617E-5</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7717754761489242E-5</v>
+        <v>5.9929602163090599E-5</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7464235869256175E-5</v>
+        <v>5.9774120834344979E-5</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7211374706305536E-5</v>
+        <v>5.9619042886277957E-5</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6959169566224808E-5</v>
+        <v>5.9464367272358907E-5</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6707618747028597E-5</v>
+        <v>5.9310092948772322E-5</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -10457,127 +10477,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0326489321439816E-4</v>
+        <v>1.1050070240770316E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.029969828290421E-4</v>
+        <v>1.1021401944273171E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0272976751025075E-4</v>
+        <v>1.0992808024789578E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0246324545474377E-4</v>
+        <v>1.0964288289355852E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0219741486391926E-4</v>
+        <v>1.0935842545508932E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0193227394384161E-4</v>
+        <v>1.0907470601285084E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0166782090522939E-4</v>
+        <v>1.0879172265218604E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0140405396344327E-4</v>
+        <v>1.0850947346340527E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0114097133847402E-4</v>
+        <v>1.0822795654177337E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0087857125493044E-4</v>
+        <v>1.0794716998749683E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.006168519420274E-4</v>
+        <v>1.0766711190571096E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0035581163357392E-4</v>
+        <v>1.0738778040646712E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0009544856796119E-4</v>
+        <v>1.0710917360471992E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9835760988150745E-5</v>
+        <v>1.0683128962031457E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.9576747141662581E-5</v>
+        <v>1.0655412657797412E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.93184052805633E-5</v>
+        <v>1.0627768260728686E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.906073366145436E-5</v>
+        <v>1.0600195584269367E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.880373054546029E-5</v>
+        <v>1.0572694442347542E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.854739419821696E-5</v>
+        <v>1.0545264649374044E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8291722889859868E-5</v>
+        <v>1.05179060202412E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8036714895012472E-5</v>
+        <v>1.0490618370321578E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7782368492774549E-5</v>
+        <v>1.0463401515466744E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.752868196671058E-5</v>
+        <v>1.0436255272006018E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7275653604838146E-5</v>
+        <v>1.0409179456745236E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7023281699616429E-5</v>
+        <v>1.0382173886965514E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6771564547934618E-5</v>
+        <v>1.0355238380422011E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6520500451100486E-5</v>
+        <v>1.0328372755342703E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6270087714828861E-5</v>
+        <v>1.0301576830427156E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6020324649230248E-5</v>
+        <v>1.0274850424845302E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5771209568799382E-5</v>
+        <v>1.0248193358236217E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5522740792403885E-5</v>
+        <v>1.0221605450706906E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -10587,127 +10607,127 @@
       </c>
       <c r="B6" s="15">
         <f>B5*Calibration!$C$21</f>
-        <v>1.5852804396292795E-4</v>
+        <v>1.6963616253253761E-4</v>
       </c>
       <c r="C6" s="15">
         <f>B6*(1+CAGR!$C$13)</f>
-        <v>1.5971042991630953E-4</v>
+        <v>1.7090139870621379E-4</v>
       </c>
       <c r="D6" s="15">
         <f>C6*(1+CAGR!$C$13)</f>
-        <v>1.6090163472916733E-4</v>
+        <v>1.7217607168010568E-4</v>
       </c>
       <c r="E6" s="15">
         <f>D6*(1+CAGR!$C$13)</f>
-        <v>1.6210172417721721E-4</v>
+        <v>1.734602518388578E-4</v>
       </c>
       <c r="F6" s="15">
         <f>E6*(1+CAGR!$C$13)</f>
-        <v>1.6331076452676506E-4</v>
+        <v>1.7475401009208055E-4</v>
       </c>
       <c r="G6" s="15">
         <f>F6*(1+CAGR!$C$13)</f>
-        <v>1.6452882253836589E-4</v>
+        <v>1.7605741787826565E-4</v>
       </c>
       <c r="H6" s="15">
         <f>G6*(1+CAGR!$C$13)</f>
-        <v>1.6575596547051022E-4</v>
+        <v>1.7737054716873094E-4</v>
       </c>
       <c r="I6" s="15">
         <f>H6*(1+CAGR!$C$13)</f>
-        <v>1.6699226108333798E-4</v>
+        <v>1.7869347047159433E-4</v>
       </c>
       <c r="J6" s="15">
         <f>I6*(1+CAGR!$C$13)</f>
-        <v>1.6823777764238E-4</v>
+        <v>1.8002626083577763E-4</v>
       </c>
       <c r="K6" s="15">
         <f>J6*(1+CAGR!$C$13)</f>
-        <v>1.6949258392232755E-4</v>
+        <v>1.8136899185504011E-4</v>
       </c>
       <c r="L6" s="15">
         <f>K6*(1+CAGR!$C$13)</f>
-        <v>1.7075674921082989E-4</v>
+        <v>1.8272173767204221E-4</v>
       </c>
       <c r="M6" s="15">
         <f>L6*(1+CAGR!$C$13)</f>
-        <v>1.7203034331232021E-4</v>
+        <v>1.8408457298243951E-4</v>
       </c>
       <c r="N6" s="15">
         <f>M6*(1+CAGR!$C$13)</f>
-        <v>1.7331343655187006E-4</v>
+        <v>1.8545757303900729E-4</v>
       </c>
       <c r="O6" s="15">
         <f>N6*(1+CAGR!$C$13)</f>
-        <v>1.7460609977907257E-4</v>
+        <v>1.8684081365579581E-4</v>
       </c>
       <c r="P6" s="15">
         <f>O6*(1+CAGR!$C$13)</f>
-        <v>1.7590840437195452E-4</v>
+        <v>1.8823437121231657E-4</v>
       </c>
       <c r="Q6" s="15">
         <f>P6*(1+CAGR!$C$13)</f>
-        <v>1.7722042224091784E-4</v>
+        <v>1.8963832265775989E-4</v>
       </c>
       <c r="R6" s="15">
         <f>Q6*(1+CAGR!$C$13)</f>
-        <v>1.7854222583271018E-4</v>
+        <v>1.9105274551524379E-4</v>
       </c>
       <c r="S6" s="15">
         <f>R6*(1+CAGR!$C$13)</f>
-        <v>1.7987388813442534E-4</v>
+        <v>1.9247771788609468E-4</v>
       </c>
       <c r="T6" s="15">
         <f>S6*(1+CAGR!$C$13)</f>
-        <v>1.8121548267753347E-4</v>
+        <v>1.9391331845415997E-4</v>
       </c>
       <c r="U6" s="15">
         <f>T6*(1+CAGR!$C$13)</f>
-        <v>1.8256708354194131E-4</v>
+        <v>1.9535962649015279E-4</v>
       </c>
       <c r="V6" s="15">
         <f>U6*(1+CAGR!$C$13)</f>
-        <v>1.8392876536008266E-4</v>
+        <v>1.9681672185602916E-4</v>
       </c>
       <c r="W6" s="15">
         <f>V6*(1+CAGR!$C$13)</f>
-        <v>1.8530060332103948E-4</v>
+        <v>1.9828468500939774E-4</v>
       </c>
       <c r="X6" s="15">
         <f>W6*(1+CAGR!$C$13)</f>
-        <v>1.8668267317469367E-4</v>
+        <v>1.9976359700796267E-4</v>
       </c>
       <c r="Y6" s="15">
         <f>X6*(1+CAGR!$C$13)</f>
-        <v>1.8807505123590975E-4</v>
+        <v>2.0125353951399918E-4</v>
       </c>
       <c r="Z6" s="15">
         <f>Y6*(1+CAGR!$C$13)</f>
-        <v>1.8947781438874889E-4</v>
+        <v>2.02754594798863E-4</v>
       </c>
       <c r="AA6" s="15">
         <f>Z6*(1+CAGR!$C$13)</f>
-        <v>1.9089104009071419E-4</v>
+        <v>2.0426684574753305E-4</v>
       </c>
       <c r="AB6" s="15">
         <f>AA6*(1+CAGR!$C$13)</f>
-        <v>1.923148063770278E-4</v>
+        <v>2.057903758631883E-4</v>
       </c>
       <c r="AC6" s="15">
         <f>AB6*(1+CAGR!$C$13)</f>
-        <v>1.9374919186493977E-4</v>
+        <v>2.0732526927181856E-4</v>
       </c>
       <c r="AD6" s="15">
         <f>AC6*(1+CAGR!$C$13)</f>
-        <v>1.9519427575806915E-4</v>
+        <v>2.0887161072686972E-4</v>
       </c>
       <c r="AE6" s="15">
         <f>AD6*(1+CAGR!$C$13)</f>
-        <v>1.9665013785077749E-4</v>
+        <v>2.1042948561392371E-4</v>
       </c>
       <c r="AF6" s="15">
         <f>AE6*(1+CAGR!$C$13)</f>
-        <v>1.9811685853257484E-4</v>
+        <v>2.119989799554132E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -10717,127 +10737,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3270542432519846E-4</v>
+        <v>7.6797287878194905E-5</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3236113344120955E-4</v>
+        <v>7.6598045034385144E-5</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3201773578531137E-4</v>
+        <v>7.6399319106105944E-5</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3167522904011342E-4</v>
+        <v>7.6201108752271929E-5</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3133361089423743E-4</v>
+        <v>7.6003412635277019E-5</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3099287904230178E-4</v>
+        <v>7.5806229420985423E-5</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3065303118490595E-4</v>
+        <v>7.5609557778722638E-5</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3031406502861493E-4</v>
+        <v>7.5413396381266465E-5</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2997597828594385E-4</v>
+        <v>7.5217743904838034E-5</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2963876867534249E-4</v>
+        <v>7.5022599029092891E-5</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2930243392117983E-4</v>
+        <v>7.4827960437112091E-5</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2896697175372881E-4</v>
+        <v>7.4633826815393307E-5</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.286323799091509E-4</v>
+        <v>7.4440196853841942E-5</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.282986561294809E-4</v>
+        <v>7.4247069245762318E-5</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2796579816261165E-4</v>
+        <v>7.4054442687848855E-5</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2763380376227886E-4</v>
+        <v>7.3862315880177259E-5</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2730267068804599E-4</v>
+        <v>7.367068752619577E-5</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2697239670528905E-4</v>
+        <v>7.3479556332716378E-5</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2664297958518152E-4</v>
+        <v>7.3288921009906152E-5</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2631441710467945E-4</v>
+        <v>7.3098780271278467E-5</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2598670704650622E-4</v>
+        <v>7.290913283368439E-5</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2565984719913783E-4</v>
+        <v>7.2719977417303974E-5</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.253338353567878E-4</v>
+        <v>7.2531312745637629E-5</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2500866931939236E-4</v>
+        <v>7.2343137545497529E-5</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2468434689259555E-4</v>
+        <v>7.2155450546999004E-5</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2436086588773449E-4</v>
+        <v>7.1968250483551963E-5</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2403822412182454E-4</v>
+        <v>7.178153609185237E-5</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2371641941754459E-4</v>
+        <v>7.1595306111873691E-5</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.233954496032224E-4</v>
+        <v>7.1409559286858396E-5</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2307531251281987E-4</v>
+        <v>7.1224294363309519E-5</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.2275600598591854E-4</v>
+        <v>7.103951009098213E-5</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -10847,127 +10867,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$21</f>
-        <v>3.0979467964319443E-4</v>
+        <v>3.3150210722310942E-4</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$15)</f>
-        <v>3.0899094848712622E-4</v>
+        <v>3.3064205832819505E-4</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$15)</f>
-        <v>3.0818930253075219E-4</v>
+        <v>3.2978424074368726E-4</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$15)</f>
-        <v>3.0738973636423124E-4</v>
+        <v>3.2892864868067545E-4</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$15)</f>
-        <v>3.0659224459175772E-4</v>
+        <v>3.2807527636526785E-4</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$15)</f>
-        <v>3.0579682183152476E-4</v>
+        <v>3.2722411803855239E-4</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$15)</f>
-        <v>3.0500346271568807E-4</v>
+        <v>3.2637516795655795E-4</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$15)</f>
-        <v>3.0421216189032975E-4</v>
+        <v>3.2552842039021564E-4</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$15)</f>
-        <v>3.0342291401542202E-4</v>
+        <v>3.2468386962531992E-4</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$15)</f>
-        <v>3.026357137647913E-4</v>
+        <v>3.2384150996249032E-4</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$15)</f>
-        <v>3.018505558260822E-4</v>
+        <v>3.230013357171327E-4</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$15)</f>
-        <v>3.0106743490072174E-4</v>
+        <v>3.2216334121940119E-4</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$15)</f>
-        <v>3.0028634570388357E-4</v>
+        <v>3.2132752081415959E-4</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$15)</f>
-        <v>2.9950728296445223E-4</v>
+        <v>3.2049386886094352E-4</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$15)</f>
-        <v>2.9873024142498773E-4</v>
+        <v>3.1966237973392217E-4</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$15)</f>
-        <v>2.9795521584168987E-4</v>
+        <v>3.1883304782186038E-4</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$15)</f>
-        <v>2.9718220098436305E-4</v>
+        <v>3.1800586752808079E-4</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$15)</f>
-        <v>2.9641119163638087E-4</v>
+        <v>3.1718083327042604E-4</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$15)</f>
-        <v>2.9564218259465087E-4</v>
+        <v>3.1635793948122114E-4</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$15)</f>
-        <v>2.948751686695796E-4</v>
+        <v>3.1553718060723583E-4</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$15)</f>
-        <v>2.9411014468503743E-4</v>
+        <v>3.1471855110964714E-4</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$15)</f>
-        <v>2.9334710547832368E-4</v>
+        <v>3.139020454640021E-4</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$15)</f>
-        <v>2.9258604590013174E-4</v>
+        <v>3.1308765816018031E-4</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$15)</f>
-        <v>2.9182696081451445E-4</v>
+        <v>3.1227538370235688E-4</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$15)</f>
-        <v>2.9106984509884927E-4</v>
+        <v>3.1146521660896522E-4</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$15)</f>
-        <v>2.9031469364380387E-4</v>
+        <v>3.1065715141266012E-4</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$15)</f>
-        <v>2.8956150135330146E-4</v>
+        <v>3.0985118266028087E-4</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$15)</f>
-        <v>2.8881026314448658E-4</v>
+        <v>3.0904730491281446E-4</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$15)</f>
-        <v>2.8806097394769076E-4</v>
+        <v>3.0824551274535883E-4</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$15)</f>
-        <v>2.8731362870639817E-4</v>
+        <v>3.0744580074708631E-4</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$15)</f>
-        <v>2.8656822237721165E-4</v>
+        <v>3.0664816352120701E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -11094,127 +11114,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.1504732151623913E-2</v>
+        <v>4.4423950670233626E-4</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.1688489888988452E-2</v>
+        <v>4.5133506055997536E-4</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.1875182671306345E-2</v>
+        <v>4.585439471666993E-4</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.206485737817571E-2</v>
+        <v>4.6586797671411152E-4</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2257561637972534E-2</v>
+        <v>4.7330898830684964E-4</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2453343839810433E-2</v>
+        <v>4.8086885042439477E-4</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.2652253145691419E-2</v>
+        <v>4.8854946139025729E-4</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.285433950285076E-2</v>
+        <v>4.9635274984865618E-4</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3059653656299004E-2</v>
+        <v>5.0428067524881267E-4</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3268247161564339E-2</v>
+        <v>5.123352283369785E-4</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3480172397638468E-2</v>
+        <v>5.2051843165632373E-4</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3695482580129269E-2</v>
+        <v>5.2883234005480855E-4</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3914231774623535E-2</v>
+        <v>5.3727904120116671E-4</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4136474910263132E-2</v>
+        <v>5.4586065610913123E-4</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4362267793538023E-2</v>
+        <v>5.5457933967003258E-4</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4591667122299588E-2</v>
+        <v>5.6343728119390374E-4</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4824730499997765E-2</v>
+        <v>5.7243670495922842E-4</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5061516450145604E-2</v>
+        <v>5.8157987077146962E-4</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5302084431014837E-2</v>
+        <v>5.9086907453051939E-4</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5546494850566197E-2</v>
+        <v>6.0030664880721227E-4</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5794809081618177E-2</v>
+        <v>6.0989496342904643E-4</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6047089477258098E-2</v>
+        <v>6.1963642607526113E-4</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6303399386499315E-2</v>
+        <v>6.2953348288141784E-4</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6563803170188501E-2</v>
+        <v>6.3958861905363872E-4</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6828366217167025E-2</v>
+        <v>6.4980435949265594E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.709715496069044E-2</v>
+        <v>6.6018326942782809E-4</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7370236895110261E-2</v>
+        <v>6.7072795506128351E-4</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7647680592822158E-2</v>
+        <v>6.8144106422235234E-4</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7929555721484875E-2</v>
+        <v>6.9232528703245112E-4</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8215933061514162E-2</v>
+        <v>7.0338335658058746E-4</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8506884523856137E-2</v>
+        <v>7.1461804960965361E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -11224,127 +11244,127 @@
       </c>
       <c r="B3" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.3691665548660236E-3</v>
+        <v>5.7144790806818921E-4</v>
       </c>
       <c r="C3" s="14">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.386674758038344E-3</v>
+        <v>5.7567092314338771E-4</v>
       </c>
       <c r="D3" s="14">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4043123472927419E-3</v>
+        <v>5.7992514641109778E-4</v>
       </c>
       <c r="E3" s="14">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4220802787957678E-3</v>
+        <v>5.8421080850068322E-4</v>
       </c>
       <c r="F3" s="14">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4399795157800685E-3</v>
+        <v>5.8852814174586477E-4</v>
       </c>
       <c r="G3" s="14">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4580110285966051E-3</v>
+        <v>5.9287738019731559E-4</v>
       </c>
       <c r="H3" s="14">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4761757947672582E-3</v>
+        <v>5.9725875963534945E-4</v>
       </c>
       <c r="I3" s="14">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4944747990378207E-3</v>
+        <v>6.0167251758270275E-4</v>
       </c>
       <c r="J3" s="14">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.512909033431382E-3</v>
+        <v>6.0611889331741136E-4</v>
       </c>
       <c r="K3" s="14">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5314794973021098E-3</v>
+        <v>6.1059812788578189E-4</v>
       </c>
       <c r="L3" s="14">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5501871973894236E-3</v>
+        <v>6.1511046411545959E-4</v>
       </c>
       <c r="M3" s="14">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5690331478725754E-3</v>
+        <v>6.1965614662859241E-4</v>
       </c>
       <c r="N3" s="14">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5880183704256273E-3</v>
+        <v>6.2423542185509242E-4</v>
       </c>
       <c r="O3" s="14">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6071438942728399E-3</v>
+        <v>6.2884853804599523E-4</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6264107562444686E-3</v>
+        <v>6.334957452869182E-4</v>
       </c>
       <c r="Q3" s="14">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6458200008329714E-3</v>
+        <v>6.3817729551161775E-4</v>
       </c>
       <c r="R3" s="14">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6653726802496332E-3</v>
+        <v>6.4289344251564767E-4</v>
       </c>
       <c r="S3" s="14">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6850698544816074E-3</v>
+        <v>6.4764444197011736E-4</v>
       </c>
       <c r="T3" s="14">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7049125913493812E-3</v>
+        <v>6.5243055143555256E-4</v>
       </c>
       <c r="U3" s="14">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7249019665646626E-3</v>
+        <v>6.5725203037585807E-4</v>
       </c>
       <c r="V3" s="14">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7450390637886973E-3</v>
+        <v>6.621091401723836E-4</v>
       </c>
       <c r="W3" s="14">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7653249746910171E-3</v>
+        <v>6.6700214413809424E-4</v>
       </c>
       <c r="X3" s="14">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7857607990086197E-3</v>
+        <v>6.7193130753184446E-4</v>
       </c>
       <c r="Y3" s="14">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8063476446055879E-3</v>
+        <v>6.7689689757275892E-4</v>
       </c>
       <c r="Z3" s="14">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8270866275331499E-3</v>
+        <v>6.8189918345471846E-4</v>
       </c>
       <c r="AA3" s="14">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.847978872090181E-3</v>
+        <v>6.8693843636095388E-4</v>
       </c>
       <c r="AB3" s="14">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8690255108841556E-3</v>
+        <v>6.9201492947874724E-4</v>
       </c>
       <c r="AC3" s="14">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8902276848925467E-3</v>
+        <v>6.9712893801424168E-4</v>
       </c>
       <c r="AD3" s="14">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9115865435246809E-3</v>
+        <v>7.0228073920736102E-4</v>
       </c>
       <c r="AE3" s="14">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9331032446840498E-3</v>
+        <v>7.0747061234683944E-4</v>
       </c>
       <c r="AF3" s="14">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9547789548310826E-3</v>
+        <v>7.1269883878536213E-4</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -11354,127 +11374,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6899857064754894E-3</v>
+        <v>4.3359582024735853E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.709864771618832E-3</v>
+        <v>4.3680010476672567E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7298907435765944E-3</v>
+        <v>4.400280690329944E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7500647079940002E-3</v>
+        <v>4.4327988804011739E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7703877585392202E-3</v>
+        <v>4.4655573807525712E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7908609969626609E-3</v>
+        <v>4.498557967283429E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8114855331566936E-3</v>
+        <v>4.5318024290169823E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.832262485215824E-3</v>
+        <v>4.5652925681973958E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8531929794973049E-3</v>
+        <v>4.5990302003874649E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8742781506821994E-3</v>
+        <v>4.633017154567043E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.895519141836893E-3</v>
+        <v>4.6672552732321919E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9169171044750621E-3</v>
+        <v>4.701746412495068E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9384731986200991E-3</v>
+        <v>4.7364924421845452E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9601885928680007E-3</v>
+        <v>4.7714952459475821E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9820644644507179E-3</v>
+        <v>4.8067567213513386E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0041019992999773E-3</v>
+        <v>4.8422787799860443E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0263023921115718E-3</v>
+        <v>4.8780633475686326E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0486668464101275E-3</v>
+        <v>4.9141123640471338E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.07119657461435E-3</v>
+        <v>4.9504277837058468E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0938927981027501E-3</v>
+        <v>4.9870115752712833E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1167567472798583E-3</v>
+        <v>5.0238657220188934E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1397896616429271E-3</v>
+        <v>5.0609922218805873E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1629927898491261E-3</v>
+        <v>5.098393087553043E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1863673897832342E-3</v>
+        <v>5.13607034660682E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2099147286258319E-3</v>
+        <v>5.1740260415962785E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2336360829219981E-3</v>
+        <v>5.2122622301703091E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2575327386505123E-3</v>
+        <v>5.2507809851838811E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2816059912935723E-3</v>
+        <v>5.2895843948104167E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3058571459070227E-3</v>
+        <v>5.3286745626549958E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.330287517191105E-3</v>
+        <v>5.3680536078683932E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3548984295617302E-3</v>
+        <v>5.4077236652619657E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -11484,127 +11504,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6911661857304328E-3</v>
+        <v>5.3403776435165457E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7110539746465273E-3</v>
+        <v>5.3798431748054135E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7310887348459519E-3</v>
+        <v>5.4196003574088288E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7512715524503572E-3</v>
+        <v>5.4596513466376802E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7716035216078612E-3</v>
+        <v>5.4999983137306589E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7920857445523652E-3</v>
+        <v>5.5406434459719675E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8127193316633088E-3</v>
+        <v>5.5815889468098967E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8335054015258638E-3</v>
+        <v>5.6228370359762787E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8544450809915765E-3</v>
+        <v>5.6643899496068215E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8755395052394556E-3</v>
+        <v>5.7062499403623358E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8967898178375129E-3</v>
+        <v>5.748419277550853E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9181971708047575E-3</v>
+        <v>5.790900247250653E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9397627246736491E-3</v>
+        <v>5.8336951524341925E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9614876485530134E-3</v>
+        <v>5.8768063130929557E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9833731201914207E-3</v>
+        <v>5.9202360663632256E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.005420326041034E-3</v>
+        <v>5.9639867666527822E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0276304613219293E-3</v>
+        <v>6.0080607857685429E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0500047300868905E-3</v>
+        <v>6.0524605130451395E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0725443452866833E-3</v>
+        <v>6.0971883554744501E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0952505288358114E-3</v>
+        <v>6.1422467378360857E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1181245116787583E-3</v>
+        <v>6.1876381028288423E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1411675338567204E-3</v>
+        <v>6.2333649112031244E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1643808445748307E-3</v>
+        <v>6.2794296418943471E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1877657022698811E-3</v>
+        <v>6.3258347921573235E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2113233746785446E-3</v>
+        <v>6.372582877701645E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2350551389061012E-3</v>
+        <v>6.4196764328280627E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2589622814956729E-3</v>
+        <v>6.4671180105658782E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2830460984979693E-3</v>
+        <v>6.5149101828113466E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3073078955415487E-3</v>
+        <v>6.5630555404671024E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3317489879035986E-3</v>
+        <v>6.6115566935826204E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3563707005812397E-3</v>
+        <v>6.660416271495708E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -11614,127 +11634,127 @@
       </c>
       <c r="B6" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A6,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5092804450873329E-3</v>
+        <v>1.4653797120333121E-4</v>
       </c>
       <c r="C6" s="14">
         <f>IFERROR(B6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5278240935947311E-3</v>
+        <v>1.4762089066588146E-4</v>
       </c>
       <c r="D6" s="14">
         <f>IFERROR(C6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5465047801524754E-3</v>
+        <v>1.4871181293175115E-4</v>
       </c>
       <c r="E6" s="14">
         <f>IFERROR(D6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5653235174753629E-3</v>
+        <v>1.4981079714186736E-4</v>
       </c>
       <c r="F6" s="14">
         <f>IFERROR(E6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5842813257621802E-3</v>
+        <v>1.5091790287421019E-4</v>
       </c>
       <c r="G6" s="14">
         <f>IFERROR(F6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6033792327510097E-3</v>
+        <v>1.5203319014704255E-4</v>
       </c>
       <c r="H6" s="14">
         <f>IFERROR(G6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6226182737749456E-3</v>
+        <v>1.5315671942216393E-4</v>
       </c>
       <c r="I6" s="14">
         <f>IFERROR(H6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6419994918182197E-3</v>
+        <v>1.5428855160818807E-4</v>
       </c>
       <c r="J6" s="14">
         <f>IFERROR(I6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6615239375727463E-3</v>
+        <v>1.5542874806384499E-4</v>
       </c>
       <c r="K6" s="14">
         <f>IFERROR(J6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6811926694950794E-3</v>
+        <v>1.5657737060130735E-4</v>
       </c>
       <c r="L6" s="14">
         <f>IFERROR(K6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7010067538637953E-3</v>
+        <v>1.5773448148954138E-4</v>
       </c>
       <c r="M6" s="14">
         <f>IFERROR(L6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.720967264837297E-3</v>
+        <v>1.589001434576826E-4</v>
       </c>
       <c r="N6" s="14">
         <f>IFERROR(M6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7410752845120462E-3</v>
+        <v>1.600744196984365E-4</v>
       </c>
       <c r="O6" s="14">
         <f>IFERROR(N6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7613319029812259E-3</v>
+        <v>1.6125737387150433E-4</v>
       </c>
       <c r="P6" s="14">
         <f>IFERROR(O6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.781738218393837E-3</v>
+        <v>1.6244907010703419E-4</v>
       </c>
       <c r="Q6" s="14">
         <f>IFERROR(P6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8022953370142297E-3</v>
+        <v>1.636495730090977E-4</v>
       </c>
       <c r="R6" s="14">
         <f>IFERROR(Q6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8230043732820767E-3</v>
+        <v>1.6485894765919221E-4</v>
       </c>
       <c r="S6" s="14">
         <f>IFERROR(R6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8438664498727901E-3</v>
+        <v>1.6607725961976911E-4</v>
       </c>
       <c r="T6" s="14">
         <f>IFERROR(S6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8648826977583819E-3</v>
+        <v>1.6730457493778801E-4</v>
       </c>
       <c r="U6" s="14">
         <f>IFERROR(T6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8860542562687778E-3</v>
+        <v>1.6854096014829725E-4</v>
       </c>
       <c r="V6" s="14">
         <f>IFERROR(U6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9073822731535809E-3</v>
+        <v>1.6978648227804097E-4</v>
       </c>
       <c r="W6" s="14">
         <f>IFERROR(V6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9288679046442947E-3</v>
+        <v>1.710412088490927E-4</v>
       </c>
       <c r="X6" s="14">
         <f>IFERROR(W6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9505123155170033E-3</v>
+        <v>1.7230520788251587E-4</v>
       </c>
       <c r="Y6" s="14">
         <f>IFERROR(X6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9723166791555174E-3</v>
+        <v>1.7357854790205136E-4</v>
       </c>
       <c r="Z6" s="14">
         <f>IFERROR(Y6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9942821776149848E-3</v>
+        <v>1.7486129793783232E-4</v>
       </c>
       <c r="AA6" s="14">
         <f>IFERROR(Z6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0164100016859714E-3</v>
+        <v>1.7615352753012634E-4</v>
       </c>
       <c r="AB6" s="14">
         <f>IFERROR(AA6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.038701350959017E-3</v>
+        <v>1.774553067331055E-4</v>
       </c>
       <c r="AC6" s="14">
         <f>IFERROR(AB6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0611574338896674E-3</v>
+        <v>1.7876670611864399E-4</v>
       </c>
       <c r="AD6" s="14">
         <f>IFERROR(AC6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0837794678639859E-3</v>
+        <v>1.8008779678014401E-4</v>
       </c>
       <c r="AE6" s="14">
         <f>IFERROR(AD6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1065686792645518E-3</v>
+        <v>1.8141865033638989E-4</v>
       </c>
       <c r="AF6" s="14">
         <f>IFERROR(AE6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1295263035369431E-3</v>
+        <v>1.8275933893543067E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -11744,127 +11764,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7297982763360346E-3</v>
+        <v>5.4452001637411056E-4</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7499715574180999E-3</v>
+        <v>5.4854403362122731E-4</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7702939195781129E-3</v>
+        <v>5.5259778846167057E-4</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7907664645291622E-3</v>
+        <v>5.5668150065703748E-4</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8113903021260243E-3</v>
+        <v>5.6079539159296899E-4</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8321665504253326E-3</v>
+        <v>5.6493968429115193E-4</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8530963357461876E-3</v>
+        <v>5.6911460342140921E-4</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8741807927312184E-3</v>
+        <v>5.7332037531387958E-4</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8954210644080926E-3</v>
+        <v>5.775572279712876E-4</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9168183022514824E-3</v>
+        <v>5.8182539108130385E-4</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9383736662454878E-3</v>
+        <v>5.8612509602899677E-4</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9600883249465224E-3</v>
+        <v>5.9045657590937677E-4</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9819634555466618E-3</v>
+        <v>5.948200655400323E-4</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0040002439374624E-3</v>
+        <v>5.9921580147386021E-4</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0261998847742506E-3</v>
+        <v>6.0364402201188913E-4</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0485635815408869E-3</v>
+        <v>6.0810496721619889E-4</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0710925466150086E-3</v>
+        <v>6.1259887892293422E-4</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0937880013337565E-3</v>
+        <v>6.1712600075541544E-4</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1166511760599845E-3</v>
+        <v>6.2168657813734549E-4</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.139683310248961E-3</v>
+        <v>6.2628085830611509E-4</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1628856525155605E-3</v>
+        <v>6.3090909032620564E-4</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1862594607019548E-3</v>
+        <v>6.3557152510269161E-4</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2098060019458024E-3</v>
+        <v>6.402684153948427E-4</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2335265527489426E-3</v>
+        <v>6.4500001582982623E-4</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2574223990465964E-3</v>
+        <v>6.4976658291651082E-4</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2814948362770804E-3</v>
+        <v>6.5456837505937257E-4</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3057451694520341E-3</v>
+        <v>6.5940565257250337E-4</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3301747132271678E-3</v>
+        <v>6.642786776937231E-4</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3547847919735319E-3</v>
+        <v>6.6918771459879606E-4</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3795767398493129E-3</v>
+        <v>6.7413302941575243E-4</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.4045519008721629E-3</v>
+        <v>6.791148902393154E-4</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -11874,127 +11894,127 @@
       </c>
       <c r="B8" s="18">
         <f>'SYFAFE psgr'!H3</f>
-        <v>4.8421448841371633E-3</v>
+        <v>2.4647349003975621E-4</v>
       </c>
       <c r="C8" s="18">
         <f>B8*(1+CAGR!$D$22)</f>
-        <v>4.8934316780402344E-3</v>
+        <v>2.490840759244642E-4</v>
       </c>
       <c r="D8" s="18">
         <f>C8*(1+CAGR!$D$22)</f>
-        <v>4.945261688904341E-3</v>
+        <v>2.5172231248535786E-4</v>
       </c>
       <c r="E8" s="18">
         <f>D8*(1+CAGR!$D$22)</f>
-        <v>4.9976406703483838E-3</v>
+        <v>2.5438849259151996E-4</v>
       </c>
       <c r="F8" s="18">
         <f>E8*(1+CAGR!$D$22)</f>
-        <v>5.0505744369321644E-3</v>
+        <v>2.5708291221402969E-4</v>
       </c>
       <c r="G8" s="18">
         <f>F8*(1+CAGR!$D$22)</f>
-        <v>5.1040688648018532E-3</v>
+        <v>2.598058704588183E-4</v>
       </c>
       <c r="H8" s="18">
         <f>G8*(1+CAGR!$D$22)</f>
-        <v>5.1581298923422999E-3</v>
+        <v>2.6255766959987263E-4</v>
       </c>
       <c r="I8" s="18">
         <f>H8*(1+CAGR!$D$22)</f>
-        <v>5.2127635208362496E-3</v>
+        <v>2.6533861511279046E-4</v>
       </c>
       <c r="J8" s="18">
         <f>I8*(1+CAGR!$D$22)</f>
-        <v>5.2679758151305406E-3</v>
+        <v>2.6814901570869105E-4</v>
       </c>
       <c r="K8" s="18">
         <f>J8*(1+CAGR!$D$22)</f>
-        <v>5.3237729043093592E-3</v>
+        <v>2.7098918336848496E-4</v>
       </c>
       <c r="L8" s="18">
         <f>K8*(1+CAGR!$D$22)</f>
-        <v>5.380160982374628E-3</v>
+        <v>2.7385943337750705E-4</v>
       </c>
       <c r="M8" s="18">
         <f>L8*(1+CAGR!$D$22)</f>
-        <v>5.4371463089335961E-3</v>
+        <v>2.7676008436051594E-4</v>
       </c>
       <c r="N8" s="18">
         <f>M8*(1+CAGR!$D$22)</f>
-        <v>5.494735209893715E-3</v>
+        <v>2.7969145831706446E-4</v>
       </c>
       <c r="O8" s="18">
         <f>N8*(1+CAGR!$D$22)</f>
-        <v>5.5529340781648746E-3</v>
+        <v>2.8265388065724456E-4</v>
       </c>
       <c r="P8" s="18">
         <f>O8*(1+CAGR!$D$22)</f>
-        <v>5.6117493743690749E-3</v>
+        <v>2.8564768023781089E-4</v>
       </c>
       <c r="Q8" s="18">
         <f>P8*(1+CAGR!$D$22)</f>
-        <v>5.6711876275576181E-3</v>
+        <v>2.8867318939868709E-4</v>
       </c>
       <c r="R8" s="18">
         <f>Q8*(1+CAGR!$D$22)</f>
-        <v>5.7312554359358926E-3</v>
+        <v>2.917307439998586E-4</v>
       </c>
       <c r="S8" s="18">
         <f>R8*(1+CAGR!$D$22)</f>
-        <v>5.7919594675958372E-3</v>
+        <v>2.9482068345865621E-4</v>
       </c>
       <c r="T8" s="18">
         <f>S8*(1+CAGR!$D$22)</f>
-        <v>5.85330646125616E-3</v>
+        <v>2.9794335078743459E-4</v>
       </c>
       <c r="U8" s="18">
         <f>T8*(1+CAGR!$D$22)</f>
-        <v>5.9153032270104029E-3</v>
+        <v>3.0109909263165006E-4</v>
       </c>
       <c r="V8" s="18">
         <f>U8*(1+CAGR!$D$22)</f>
-        <v>5.9779566470829232E-3</v>
+        <v>3.0428825930834129E-4</v>
       </c>
       <c r="W8" s="18">
         <f>V8*(1+CAGR!$D$22)</f>
-        <v>6.0412736765928874E-3</v>
+        <v>3.0751120484501785E-4</v>
       </c>
       <c r="X8" s="18">
         <f>W8*(1+CAGR!$D$22)</f>
-        <v>6.1052613443263529E-3</v>
+        <v>3.1076828701896063E-4</v>
       </c>
       <c r="Y8" s="18">
         <f>X8*(1+CAGR!$D$22)</f>
-        <v>6.1699267535165296E-3</v>
+        <v>3.1405986739693851E-4</v>
       </c>
       <c r="Z8" s="18">
         <f>Y8*(1+CAGR!$D$22)</f>
-        <v>6.2352770826323081E-3</v>
+        <v>3.1738631137534555E-4</v>
       </c>
       <c r="AA8" s="18">
         <f>Z8*(1+CAGR!$D$22)</f>
-        <v>6.3013195861751341E-3</v>
+        <v>3.207479882207636E-4</v>
       </c>
       <c r="AB8" s="18">
         <f>AA8*(1+CAGR!$D$22)</f>
-        <v>6.368061595484328E-3</v>
+        <v>3.2414527111095418E-4</v>
       </c>
       <c r="AC8" s="18">
         <f>AB8*(1+CAGR!$D$22)</f>
-        <v>6.4355105195509328E-3</v>
+        <v>3.2757853717628482E-4</v>
       </c>
       <c r="AD8" s="18">
         <f>AC8*(1+CAGR!$D$22)</f>
-        <v>6.5036738458401806E-3</v>
+        <v>3.3104816754159417E-4</v>
       </c>
       <c r="AE8" s="18">
         <f>AD8*(1+CAGR!$D$22)</f>
-        <v>6.572559141122673E-3</v>
+        <v>3.3455454736850023E-4</v>
       </c>
       <c r="AF8" s="18">
         <f>AE8*(1+CAGR!$D$22)</f>
-        <v>6.6421740523143627E-3</v>
+        <v>3.3809806589815716E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -12121,127 +12141,127 @@
       </c>
       <c r="B2" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A2,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>5.9920151090392774E-2</v>
+        <v>5.8989559032638431E-3</v>
       </c>
       <c r="C2" s="21">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.0877217386400166E-2</v>
+        <v>5.9931761576175217E-3</v>
       </c>
       <c r="D2" s="21">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.184957029097387E-2</v>
+        <v>6.088901331905516E-3</v>
       </c>
       <c r="E2" s="21">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.2837453967347343E-2</v>
+        <v>6.1861554632525852E-3</v>
       </c>
       <c r="F2" s="21">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.3841116478617385E-2</v>
+        <v>6.284962972713126E-3</v>
       </c>
       <c r="G2" s="21">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.4860809850034187E-2</v>
+        <v>6.3853486714034379E-3</v>
       </c>
       <c r="H2" s="21">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.5896790132286262E-2</v>
+        <v>6.4873377667319316E-3</v>
       </c>
       <c r="I2" s="21">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.6949317465796201E-2</v>
+        <v>6.5909558687288483E-3</v>
       </c>
       <c r="J2" s="21">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.8018656146043383E-2</v>
+        <v>6.6962289964770834E-3</v>
       </c>
       <c r="K2" s="21">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>6.910507468993006E-2</v>
+        <v>6.8031835846457224E-3</v>
       </c>
       <c r="L2" s="21">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.0208845903207417E-2</v>
+        <v>6.911846490127934E-3</v>
       </c>
       <c r="M2" s="21">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.1330246948978646E-2</v>
+        <v>7.0222449987848833E-3</v>
       </c>
       <c r="N2" s="21">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.2469559417296117E-2</v>
+        <v>7.1344068322973667E-3</v>
       </c>
       <c r="O2" s="21">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.3627069395870243E-2</v>
+        <v>7.2483601551268789E-3</v>
       </c>
       <c r="P2" s="21">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.4803067541907672E-2</v>
+        <v>7.3641335815878665E-3</v>
       </c>
       <c r="Q2" s="21">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.5997849155096941E-2</v>
+        <v>7.4817561830329412E-3</v>
       </c>
       <c r="R2" s="21">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.7211714251759878E-2</v>
+        <v>7.6012574951528598E-3</v>
       </c>
       <c r="S2" s="21">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.8444967640187352E-2</v>
+        <v>7.7226675253931005E-3</v>
       </c>
       <c r="T2" s="21">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>7.969791899717836E-2</v>
+        <v>7.8460167604888966E-3</v>
       </c>
       <c r="U2" s="21">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.0970882945801584E-2</v>
+        <v>7.9713361741206318E-3</v>
       </c>
       <c r="V2" s="21">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.2264179134398999E-2</v>
+        <v>8.0986572346914976E-3</v>
       </c>
       <c r="W2" s="21">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.357813231685135E-2</v>
+        <v>8.2280119132293883E-3</v>
       </c>
       <c r="X2" s="21">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.4913072434125686E-2</v>
+        <v>8.3594326914150051E-3</v>
       </c>
       <c r="Y2" s="21">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.6269334697125319E-2</v>
+        <v>8.4929525697381818E-3</v>
       </c>
       <c r="Z2" s="21">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.7647259670863203E-2</v>
+        <v>8.6286050757844995E-3</v>
       </c>
       <c r="AA2" s="21">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>8.9047193359979696E-2</v>
+        <v>8.766424272654243E-3</v>
       </c>
       <c r="AB2" s="21">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.0469487295626233E-2</v>
+        <v>8.9064447675158403E-3</v>
       </c>
       <c r="AC2" s="21">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.1914498623736768E-2</v>
+        <v>9.0487017202959125E-3</v>
       </c>
       <c r="AD2" s="21">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.3382590194709125E-2</v>
+        <v>9.1932308525081285E-3</v>
       </c>
       <c r="AE2" s="21">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.4874130654518746E-2</v>
+        <v>9.3400684562230749E-3</v>
       </c>
       <c r="AF2" s="21">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.638949453728772E-2</v>
+        <v>9.4892514031814004E-3</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -12251,127 +12271,127 @@
       </c>
       <c r="B3" s="13">
         <f>B5*Calibration!$C$27</f>
-        <v>6.9151802324205315E-3</v>
+        <v>6.5856425093374178E-3</v>
       </c>
       <c r="C3" s="13">
         <f>B3*(1+CAGR!$C$24)</f>
-        <v>6.9662835962738499E-3</v>
+        <v>6.6343105807471414E-3</v>
       </c>
       <c r="D3" s="13">
         <f>C3*(1+CAGR!$C$24)</f>
-        <v>7.017764615330554E-3</v>
+        <v>6.683338310485021E-3</v>
       </c>
       <c r="E3" s="13">
         <f>D3*(1+CAGR!$C$24)</f>
-        <v>7.069626080472533E-3</v>
+        <v>6.7327283564355645E-3</v>
       </c>
       <c r="F3" s="13">
         <f>E3*(1+CAGR!$C$24)</f>
-        <v>7.1218708032063666E-3</v>
+        <v>6.7824833961251151E-3</v>
       </c>
       <c r="G3" s="13">
         <f>F3*(1+CAGR!$C$24)</f>
-        <v>7.1745016158157419E-3</v>
+        <v>6.832606126867008E-3</v>
       </c>
       <c r="H3" s="13">
         <f>G3*(1+CAGR!$C$24)</f>
-        <v>7.2275213715149965E-3</v>
+        <v>6.8830992659077925E-3</v>
       </c>
       <c r="I3" s="13">
         <f>H3*(1+CAGR!$C$24)</f>
-        <v>7.2809329446037983E-3</v>
+        <v>6.9339655505745437E-3</v>
       </c>
       <c r="J3" s="13">
         <f>I3*(1+CAGR!$C$24)</f>
-        <v>7.3347392306229641E-3</v>
+        <v>6.9852077384232551E-3</v>
       </c>
       <c r="K3" s="13">
         <f>J3*(1+CAGR!$C$24)</f>
-        <v>7.3889431465114343E-3</v>
+        <v>7.0368286073883299E-3</v>
       </c>
       <c r="L3" s="13">
         <f>K3*(1+CAGR!$C$24)</f>
-        <v>7.4435476307644043E-3</v>
+        <v>7.0888309559331824E-3</v>
       </c>
       <c r="M3" s="13">
         <f>L3*(1+CAGR!$C$24)</f>
-        <v>7.4985556435926267E-3</v>
+        <v>7.1412176032019433E-3</v>
       </c>
       <c r="N3" s="13">
         <f>M3*(1+CAGR!$C$24)</f>
-        <v>7.5539701670828893E-3</v>
+        <v>7.1939913891722928E-3</v>
       </c>
       <c r="O3" s="13">
         <f>N3*(1+CAGR!$C$24)</f>
-        <v>7.6097942053596802E-3</v>
+        <v>7.2471551748094212E-3</v>
       </c>
       <c r="P3" s="13">
         <f>O3*(1+CAGR!$C$24)</f>
-        <v>7.6660307847480451E-3</v>
+        <v>7.3007118422211267E-3</v>
       </c>
       <c r="Q3" s="13">
         <f>P3*(1+CAGR!$C$24)</f>
-        <v>7.7226829539376526E-3</v>
+        <v>7.3546642948140598E-3</v>
       </c>
       <c r="R3" s="13">
         <f>Q3*(1+CAGR!$C$24)</f>
-        <v>7.779753784148068E-3</v>
+        <v>7.4090154574511227E-3</v>
       </c>
       <c r="S3" s="13">
         <f>R3*(1+CAGR!$C$24)</f>
-        <v>7.8372463692952497E-3</v>
+        <v>7.4637682766100317E-3</v>
       </c>
       <c r="T3" s="13">
         <f>S3*(1+CAGR!$C$24)</f>
-        <v>7.8951638261592783E-3</v>
+        <v>7.5189257205430507E-3</v>
       </c>
       <c r="U3" s="13">
         <f>T3*(1+CAGR!$C$24)</f>
-        <v>7.9535092945533167E-3</v>
+        <v>7.5744907794379063E-3</v>
       </c>
       <c r="V3" s="13">
         <f>U3*(1+CAGR!$C$24)</f>
-        <v>8.0122859374938352E-3</v>
+        <v>7.6304664655798896E-3</v>
       </c>
       <c r="W3" s="13">
         <f>V3*(1+CAGR!$C$24)</f>
-        <v>8.071496941372075E-3</v>
+        <v>7.6868558135151609E-3</v>
       </c>
       <c r="X3" s="13">
         <f>W3*(1+CAGR!$C$24)</f>
-        <v>8.1311455161267934E-3</v>
+        <v>7.7436618802152564E-3</v>
       </c>
       <c r="Y3" s="13">
         <f>X3*(1+CAGR!$C$24)</f>
-        <v>8.1912348954182798E-3</v>
+        <v>7.8008877452428113E-3</v>
       </c>
       <c r="Z3" s="13">
         <f>Y3*(1+CAGR!$C$24)</f>
-        <v>8.2517683368036592E-3</v>
+        <v>7.8585365109185099E-3</v>
       </c>
       <c r="AA3" s="13">
         <f>Z3*(1+CAGR!$C$24)</f>
-        <v>8.3127491219134875E-3</v>
+        <v>7.9166113024892685E-3</v>
       </c>
       <c r="AB3" s="13">
         <f>AA3*(1+CAGR!$C$24)</f>
-        <v>8.3741805566296592E-3</v>
+        <v>7.9751152682976615E-3</v>
       </c>
       <c r="AC3" s="13">
         <f>AB3*(1+CAGR!$C$24)</f>
-        <v>8.4360659712646204E-3</v>
+        <v>8.034051579952595E-3</v>
       </c>
       <c r="AD3" s="13">
         <f>AC3*(1+CAGR!$C$24)</f>
-        <v>8.4984087207419148E-3</v>
+        <v>8.0934234325012507E-3</v>
       </c>
       <c r="AE3" s="13">
         <f>AD3*(1+CAGR!$C$24)</f>
-        <v>8.5612121847780612E-3</v>
+        <v>8.1532340446022911E-3</v>
       </c>
       <c r="AF3" s="13">
         <f>AE3*(1+CAGR!$C$24)</f>
-        <v>8.6244797680657698E-3</v>
+        <v>8.213486658700352E-3</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -12381,127 +12401,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.4896992216329783E-3</v>
+        <v>5.1796769294389453E-3</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.5598283485511804E-3</v>
+        <v>5.2179548782228056E-3</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.6304757315623778E-3</v>
+        <v>5.2565157020552566E-3</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.7016452005927335E-3</v>
+        <v>5.2953614913903505E-3</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.7733406138716655E-3</v>
+        <v>5.3344943521306479E-3</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.8455658581410067E-3</v>
+        <v>5.373916405741387E-3</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.9183248488657182E-3</v>
+        <v>5.4136297893654884E-3</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>9.9916215304461462E-3</v>
+        <v>5.4536366559394161E-3</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.006545987643186E-2</v>
+        <v>5.4939391743098901E-3</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0139843889737068E-2</v>
+        <v>5.5345395293514652E-3</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0214777602857616E-2</v>
+        <v>5.5754399220849776E-3</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0290265078089601E-2</v>
+        <v>5.616642569796864E-3</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0366310407749596E-2</v>
+        <v>5.6581497061593674E-3</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0442917714396503E-2</v>
+        <v>5.6999635813516263E-3</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0520091151055039E-2</v>
+        <v>5.7420864621816631E-3</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0597834901440886E-2</v>
+        <v>5.7845206322092706E-3</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0676153180187492E-2</v>
+        <v>5.8272683918698092E-3</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.075505023307456E-2</v>
+        <v>5.8703320585989163E-3</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0834530337258213E-2</v>
+        <v>5.9137139669581396E-3</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0914597801502874E-2</v>
+        <v>5.9574164687614985E-3</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0995256966414848E-2</v>
+        <v>6.0014419332029808E-3</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1076512204677633E-2</v>
+        <v>6.0457927469849786E-3</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1158367921288975E-2</v>
+        <v>6.090471314447678E-3</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1240828553799665E-2</v>
+        <v>6.135480057699403E-3</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1323898572554118E-2</v>
+        <v>6.1808214167479204E-3</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1407582480932706E-2</v>
+        <v>6.2264978496327202E-3</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1491884815595904E-2</v>
+        <v>6.2725118325582686E-3</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1576810146730225E-2</v>
+        <v>6.3188658600282464E-3</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1662363078295981E-2</v>
+        <v>6.3655624449807839E-3</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1748548248276872E-2</v>
+        <v>6.4126041189246901E-3</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1835370328931422E-2</v>
+        <v>6.4599934320766902E-3</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -12511,127 +12531,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0093981719611995E-2</v>
+        <v>9.6129605978300132E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0168576510088703E-2</v>
+        <v>9.6840006295612711E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0243722558029593E-2</v>
+        <v>9.755565648996059E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.031942393724183E-2</v>
+        <v>9.8276595358073177E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.039568475163812E-2</v>
+        <v>9.9002861983388743E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.047250913545919E-2</v>
+        <v>9.9734495738173189E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0549901253497919E-2</v>
+        <v>1.0047153628565449E-2</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0627865301325111E-2</v>
+        <v>1.0121402358217294E-2</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.070640550551695E-2</v>
+        <v>1.019619978793472E-2</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0785526123884129E-2</v>
+        <v>1.027154997262565E-2</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0865231445702674E-2</v>
+        <v>1.0347456997163881E-2</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.0945525791946475E-2</v>
+        <v>1.0423924976610533E-2</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1026413515521531E-2</v>
+        <v>1.0500958056437139E-2</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1107899001501931E-2</v>
+        <v>1.0578560412750375E-2</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1189986667367579E-2</v>
+        <v>1.0656736252518454E-2</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1272680963243667E-2</v>
+        <v>1.0735489813799196E-2</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1355986372141936E-2</v>
+        <v>1.0814825365969777E-2</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1439907410203695E-2</v>
+        <v>1.0894747209958188E-2</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1524448626944661E-2</v>
+        <v>1.0975259678476386E-2</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1609614605501591E-2</v>
+        <v>1.1056367136255185E-2</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1695409962880739E-2</v>
+        <v>1.1138073980280876E-2</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1781839350208163E-2</v>
+        <v>1.1220384640033592E-2</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.186890745298186E-2</v>
+        <v>1.1303303577727443E-2</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1956618991325784E-2</v>
+        <v>1.1386835288552416E-2</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2044978720245725E-2</v>
+        <v>1.1470984300918073E-2</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2133991429887097E-2</v>
+        <v>1.155575517669904E-2</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2223661945794608E-2</v>
+        <v>1.1641152511482317E-2</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2313995129173872E-2</v>
+        <v>1.1727180934816414E-2</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2404995877154941E-2</v>
+        <v>1.1813845110462325E-2</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2496669123057783E-2</v>
+        <v>1.190114973664636E-2</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2589019836659736E-2</v>
+        <v>1.1989099546314845E-2</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -12641,127 +12661,127 @@
       </c>
       <c r="B6" s="13">
         <f>B5*Calibration!$E$26</f>
-        <v>2.2382506626107086E-2</v>
+        <v>2.1315885074310131E-2</v>
       </c>
       <c r="C6" s="13">
         <f>B6*(1+CAGR!$C$27)</f>
-        <v>2.2547913938949154E-2</v>
+        <v>2.1473410025822016E-2</v>
       </c>
       <c r="D6" s="13">
         <f>C6*(1+CAGR!$C$27)</f>
-        <v>2.2714543616184926E-2</v>
+        <v>2.1632099090869994E-2</v>
       </c>
       <c r="E6" s="13">
         <f>D6*(1+CAGR!$C$27)</f>
-        <v>2.2882404691119435E-2</v>
+        <v>2.1791960872283727E-2</v>
       </c>
       <c r="F6" s="13">
         <f>E6*(1+CAGR!$C$27)</f>
-        <v>2.3051506263814067E-2</v>
+        <v>2.1953004036468007E-2</v>
       </c>
       <c r="G6" s="13">
         <f>F6*(1+CAGR!$C$27)</f>
-        <v>2.3221857501579912E-2</v>
+        <v>2.2115237313872594E-2</v>
       </c>
       <c r="H6" s="13">
         <f>G6*(1+CAGR!$C$27)</f>
-        <v>2.3393467639474721E-2</v>
+        <v>2.2278669499465494E-2</v>
       </c>
       <c r="I6" s="13">
         <f>H6*(1+CAGR!$C$27)</f>
-        <v>2.3566345980803569E-2</v>
+        <v>2.2443309453209766E-2</v>
       </c>
       <c r="J6" s="13">
         <f>I6*(1+CAGR!$C$27)</f>
-        <v>2.3740501897623202E-2</v>
+        <v>2.260916610054382E-2</v>
       </c>
       <c r="K6" s="13">
         <f>J6*(1+CAGR!$C$27)</f>
-        <v>2.3915944831250105E-2</v>
+        <v>2.2776248432865298E-2</v>
       </c>
       <c r="L6" s="13">
         <f>K6*(1+CAGR!$C$27)</f>
-        <v>2.4092684292772348E-2</v>
+        <v>2.2944565508018502E-2</v>
       </c>
       <c r="M6" s="13">
         <f>L6*(1+CAGR!$C$27)</f>
-        <v>2.4270729863565186E-2</v>
+        <v>2.3114126450785449E-2</v>
       </c>
       <c r="N6" s="13">
         <f>M6*(1+CAGR!$C$27)</f>
-        <v>2.4450091195810496E-2</v>
+        <v>2.3284940453380525E-2</v>
       </c>
       <c r="O6" s="13">
         <f>N6*(1+CAGR!$C$27)</f>
-        <v>2.4630778013020025E-2</v>
+        <v>2.345701677594883E-2</v>
       </c>
       <c r="P6" s="13">
         <f>O6*(1+CAGR!$C$27)</f>
-        <v>2.4812800110562534E-2</v>
+        <v>2.3630364747068176E-2</v>
       </c>
       <c r="Q6" s="13">
         <f>P6*(1+CAGR!$C$27)</f>
-        <v>2.4996167356194813E-2</v>
+        <v>2.3804993764254812E-2</v>
       </c>
       <c r="R6" s="13">
         <f>Q6*(1+CAGR!$C$27)</f>
-        <v>2.5180889690596637E-2</v>
+        <v>2.398091329447288E-2</v>
       </c>
       <c r="S6" s="13">
         <f>R6*(1+CAGR!$C$27)</f>
-        <v>2.5366977127909664E-2</v>
+        <v>2.4158132874647634E-2</v>
       </c>
       <c r="T6" s="13">
         <f>S6*(1+CAGR!$C$27)</f>
-        <v>2.5554439756280321E-2</v>
+        <v>2.433666211218246E-2</v>
       </c>
       <c r="U6" s="13">
         <f>T6*(1+CAGR!$C$27)</f>
-        <v>2.5743287738406707E-2</v>
+        <v>2.4516510685479703E-2</v>
       </c>
       <c r="V6" s="13">
         <f>U6*(1+CAGR!$C$27)</f>
-        <v>2.5933531312089527E-2</v>
+        <v>2.4697688344465358E-2</v>
       </c>
       <c r="W6" s="13">
         <f>V6*(1+CAGR!$C$27)</f>
-        <v>2.6125180790787097E-2</v>
+        <v>2.4880204911117632E-2</v>
       </c>
       <c r="X6" s="13">
         <f>W6*(1+CAGR!$C$27)</f>
-        <v>2.6318246564174468E-2</v>
+        <v>2.5064070279999406E-2</v>
       </c>
       <c r="Y6" s="13">
         <f>X6*(1+CAGR!$C$27)</f>
-        <v>2.6512739098706654E-2</v>
+        <v>2.5249294418794647E-2</v>
       </c>
       <c r="Z6" s="13">
         <f>Y6*(1+CAGR!$C$27)</f>
-        <v>2.6708668938186058E-2</v>
+        <v>2.5435887368848758E-2</v>
       </c>
       <c r="AA6" s="13">
         <f>Z6*(1+CAGR!$C$27)</f>
-        <v>2.6906046704334056E-2</v>
+        <v>2.5623859245712959E-2</v>
       </c>
       <c r="AB6" s="13">
         <f>AA6*(1+CAGR!$C$27)</f>
-        <v>2.7104883097366819E-2</v>
+        <v>2.5813220239692652E-2</v>
       </c>
       <c r="AC6" s="13">
         <f>AB6*(1+CAGR!$C$27)</f>
-        <v>2.7305188896575402E-2</v>
+        <v>2.6003980616399872E-2</v>
       </c>
       <c r="AD6" s="13">
         <f>AC6*(1+CAGR!$C$27)</f>
-        <v>2.7506974960910105E-2</v>
+        <v>2.6196150717309789E-2</v>
       </c>
       <c r="AE6" s="13">
         <f>AD6*(1+CAGR!$C$27)</f>
-        <v>2.7710252229569157E-2</v>
+        <v>2.6389740960321352E-2</v>
       </c>
       <c r="AF6" s="13">
         <f>AE6*(1+CAGR!$C$27)</f>
-        <v>2.7915031722591743E-2</v>
+        <v>2.6584761840322057E-2</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -12771,127 +12791,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A7,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1879757205955988E-2</v>
+        <v>6.1185298450215607E-3</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.1967548924259844E-2</v>
+        <v>6.1637459415524358E-3</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.205598942567173E-2</v>
+        <v>6.2092961862262918E-3</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2145083504715886E-2</v>
+        <v>6.2551830484066972E-3</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.223483599134821E-2</v>
+        <v>6.301409015705881E-3</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2325251751218099E-2</v>
+        <v>6.3479765941195938E-3</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.241633568593223E-2</v>
+        <v>6.3948883081629592E-3</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2508092733320283E-2</v>
+        <v>6.4421467010073339E-3</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2600527867702627E-2</v>
+        <v>6.489754334618179E-3</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2693646100159989E-2</v>
+        <v>6.5377137898939468E-3</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2787452478805115E-2</v>
+        <v>6.5860276668059971E-3</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2881952089056438E-2</v>
+        <v>6.6346985845395466E-3</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.2977150053913767E-2</v>
+        <v>6.6837291816356607E-3</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3073051534236014E-2</v>
+        <v>6.7331221161342908E-3</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3169661729020973E-2</v>
+        <v>6.782880065718375E-3</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3266985875687171E-2</v>
+        <v>6.8330057278589984E-3</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3365029250357792E-2</v>
+        <v>6.8835018199616274E-3</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3463797168146713E-2</v>
+        <v>6.9343710795134279E-3</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.356329498344664E-2</v>
+        <v>6.985616264231667E-3</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3663528090219382E-2</v>
+        <v>7.0372401522132144E-3</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3764501922288268E-2</v>
+        <v>7.0892455420851503E-3</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3866221953632728E-2</v>
+        <v>7.1416352531564814E-3</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.3968693698685038E-2</v>
+        <v>7.1944121255709832E-3</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4071922712629276E-2</v>
+        <v>7.2475790204611671E-3</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4175914591702476E-2</v>
+        <v>7.3011388201033901E-3</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4280674973498015E-2</v>
+        <v>7.3550944280741069E-3</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4386209537271228E-2</v>
+        <v>7.4094487694072782E-3</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4492524004247298E-2</v>
+        <v>7.4642047907529435E-3</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4599624137931415E-2</v>
+        <v>7.5193654605369637E-3</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.470751574442122E-2</v>
+        <v>7.5749337691219431E-3</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.4816204672721572E-2</v>
+        <v>7.6309127289693468E-3</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -12901,127 +12921,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$F$27</f>
-        <v>4.0313858450103462E-2</v>
+        <v>3.8392731787336508E-2</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$29)</f>
-        <v>4.0611778924691831E-2</v>
+        <v>3.8676455085342926E-2</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$29)</f>
-        <v>4.0911901039425581E-2</v>
+        <v>3.8962275105986259E-2</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$29)</f>
-        <v>4.1214241064483306E-2</v>
+        <v>3.9250207344101964E-2</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$29)</f>
-        <v>4.1518815390280663E-2</v>
+        <v>3.9540267409032728E-2</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$29)</f>
-        <v>4.1825640528358889E-2</v>
+        <v>3.98324710254747E-2</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$29)</f>
-        <v>4.2134733112279964E-2</v>
+        <v>4.0126834034329942E-2</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$29)</f>
-        <v>4.2446109898528324E-2</v>
+        <v>4.04233723935652E-2</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$29)</f>
-        <v>4.2759787767419268E-2</v>
+        <v>4.072210217907702E-2</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$29)</f>
-        <v>4.3075783724014056E-2</v>
+        <v>4.1023039585563234E-2</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$29)</f>
-        <v>4.3394114899041811E-2</v>
+        <v>4.1326200927400927E-2</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$29)</f>
-        <v>4.3714798549828196E-2</v>
+        <v>4.1631602639530862E-2</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$29)</f>
-        <v>4.4037852061230953E-2</v>
+        <v>4.193926127834844E-2</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$29)</f>
-        <v>4.4363292946582387E-2</v>
+        <v>4.2249193522601258E-2</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$29)</f>
-        <v>4.4691138848638796E-2</v>
+        <v>4.2561416174293307E-2</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$29)</f>
-        <v>4.5021407540536899E-2</v>
+        <v>4.2875946159595814E-2</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$29)</f>
-        <v>4.5354116926757372E-2</v>
+        <v>4.3192800529764867E-2</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$29)</f>
-        <v>4.5689285044095473E-2</v>
+        <v>4.3511996462065793E-2</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$29)</f>
-        <v>4.6026930062638846E-2</v>
+        <v>4.3833551260704338E-2</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$29)</f>
-        <v>4.6367070286752562E-2</v>
+        <v>4.4157482357764809E-2</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$29)</f>
-        <v>4.6709724156071442E-2</v>
+        <v>4.4483807314155056E-2</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$29)</f>
-        <v>4.7054910246499673E-2</v>
+        <v>4.4812543820558513E-2</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$29)</f>
-        <v>4.7402647271217888E-2</v>
+        <v>4.5143709698393222E-2</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$29)</f>
-        <v>4.7752954081697593E-2</v>
+        <v>4.5477322900777981E-2</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$29)</f>
-        <v>4.810584966872318E-2</v>
+        <v>4.5813401513505596E-2</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$29)</f>
-        <v>4.8461353163421435E-2</v>
+        <v>4.6151963756023366E-2</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$29)</f>
-        <v>4.881948383829867E-2</v>
+        <v>4.6493027982420783E-2</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$29)</f>
-        <v>4.9180261108285529E-2</v>
+        <v>4.6836612682424547E-2</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$29)</f>
-        <v>4.9543704531789502E-2</v>
+        <v>4.7182736482400921E-2</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$29)</f>
-        <v>4.9909833811755226E-2</v>
+        <v>4.7531418146365502E-2</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$29)</f>
-        <v>5.0278668796732616E-2</v>
+        <v>4.788267657700046E-2</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -19217,25 +19237,25 @@
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6">
-        <v>6.5625257131084701E-4</v>
-      </c>
-      <c r="C2" s="6">
-        <v>1.5805524645082474E-4</v>
-      </c>
-      <c r="D2" s="6">
-        <v>1.0481774505583632E-4</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1.0353350047428987E-4</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>1.3305061076069645E-4</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="B2" s="34">
+        <v>7.2592367078105297E-5</v>
+      </c>
+      <c r="C2" s="34">
+        <v>1.7537305636668391E-4</v>
+      </c>
+      <c r="D2" s="34">
+        <v>6.4283975580087249E-5</v>
+      </c>
+      <c r="E2" s="34">
+        <v>1.1078813107746625E-4</v>
+      </c>
+      <c r="F2" s="34">
+        <v>0</v>
+      </c>
+      <c r="G2" s="34">
+        <v>7.6997048982108972E-5</v>
+      </c>
+      <c r="H2" s="34">
         <v>0</v>
       </c>
       <c r="I2" s="1"/>
@@ -19245,25 +19265,25 @@
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6">
-        <v>5.8978131078270858E-2</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
-        <v>9.4200845489772374E-3</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1.0019934142677002E-2</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>1.1792609511407667E-2</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="B3" s="34">
+        <v>5.8062169096135046E-3</v>
+      </c>
+      <c r="C3" s="34">
+        <v>0</v>
+      </c>
+      <c r="D3" s="34">
+        <v>5.1416797805848074E-3</v>
+      </c>
+      <c r="E3" s="34">
+        <v>9.5424417025899051E-3</v>
+      </c>
+      <c r="F3" s="34">
+        <v>0</v>
+      </c>
+      <c r="G3" s="34">
+        <v>6.0736454453848921E-3</v>
+      </c>
+      <c r="H3" s="34">
         <v>0</v>
       </c>
       <c r="I3" s="1"/>
@@ -19273,25 +19293,25 @@
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="B4" s="34">
+        <v>0</v>
+      </c>
+      <c r="C4" s="34">
+        <v>0</v>
+      </c>
+      <c r="D4" s="34">
+        <v>0</v>
+      </c>
+      <c r="E4" s="34">
         <v>2.992789097910166E-2</v>
       </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="F4" s="34">
+        <v>0</v>
+      </c>
+      <c r="G4" s="34">
+        <v>0</v>
+      </c>
+      <c r="H4" s="34">
         <v>0</v>
       </c>
       <c r="I4" s="1"/>
@@ -19301,25 +19321,25 @@
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="34">
         <v>1.0021251453207708E-3</v>
       </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
+      <c r="C5" s="34">
+        <v>0</v>
+      </c>
+      <c r="D5" s="34">
+        <v>0</v>
+      </c>
+      <c r="E5" s="34">
         <v>1.6108650602655154E-2</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="F5" s="34">
+        <v>0</v>
+      </c>
+      <c r="G5" s="34">
+        <v>0</v>
+      </c>
+      <c r="H5" s="34">
         <v>0</v>
       </c>
       <c r="I5" s="1"/>
@@ -19329,25 +19349,25 @@
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="34">
         <v>1.5467626362604087E-2</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="34">
         <v>4.813365E-3</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="34">
         <v>4.813365E-3</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="34">
         <v>4.813365E-3</v>
       </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="F6" s="34">
+        <v>0</v>
+      </c>
+      <c r="G6" s="34">
+        <v>0</v>
+      </c>
+      <c r="H6" s="34">
         <v>1.4440094999999998E-2</v>
       </c>
       <c r="I6" s="1"/>
@@ -19357,25 +19377,25 @@
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>7.0063905313000519E-5</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34">
+        <v>0</v>
+      </c>
+      <c r="D7" s="34">
+        <v>5.983190553484204E-5</v>
+      </c>
+      <c r="E7" s="34">
+        <v>0</v>
+      </c>
+      <c r="F7" s="34">
+        <v>0</v>
+      </c>
+      <c r="G7" s="34">
+        <v>0</v>
+      </c>
+      <c r="H7" s="34">
         <v>0</v>
       </c>
       <c r="I7" s="1"/>
@@ -19807,127 +19827,127 @@
       </c>
       <c r="B4" s="21">
         <f>'SYFAFE psgr'!D7</f>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="C4" s="13">
         <f t="shared" si="1"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="D4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="E4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="F4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="G4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="H4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="I4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="J4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="K4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="L4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="M4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="N4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="O4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="P4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="Q4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="R4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="S4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="T4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="U4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="V4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="W4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="X4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="Y4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="Z4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AA4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AB4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AC4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AD4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AE4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
       <c r="AF4" s="13">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.9831905534842047E-5</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -20822,127 +20842,127 @@
       </c>
       <c r="B4" s="21">
         <f>'SYFAFE frgt'!D7</f>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="C4" s="21">
         <f t="shared" si="1"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="D4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="E4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="F4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="G4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="H4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="I4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="J4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="K4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="L4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="M4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="N4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="O4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="P4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="Q4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="R4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="S4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="T4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="U4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="V4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="W4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="X4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="Y4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="Z4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AA4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AB4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AC4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AD4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AE4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
       <c r="AF4" s="21">
         <f t="shared" si="0"/>
-        <v>7.0063905313000519E-5</v>
+        <v>5.983190553484204E-5</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -26256,6 +26276,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -26399,22 +26434,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7954CBA-CC49-4137-B897-2F07557F3495}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E16404-9CDB-444B-B1EF-816DE1AF2890}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26430,28 +26474,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7954CBA-CC49-4137-B897-2F07557F3495}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
+++ b/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\BNVFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0295E1B5-04B4-495D-BAC3-233A5CC68C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BC1A94-0FBE-4037-A2D4-66A4923CE019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28050" yWindow="1860" windowWidth="27045" windowHeight="14940" activeTab="1" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
+    <workbookView xWindow="-26580" yWindow="750" windowWidth="25050" windowHeight="14940" firstSheet="23" activeTab="27" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -10996,16 +10996,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="34">
-        <v>1.3426499999999999E-2</v>
+        <v>2.8195999999999998E-3</v>
       </c>
       <c r="C6" s="34">
         <v>0</v>
       </c>
       <c r="D6" s="34">
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="E6" s="34">
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="F6" s="34">
         <v>0</v>
@@ -11014,7 +11014,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="34">
-        <v>1.25346E-2</v>
+        <v>2.6323000000000002E-3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -19376,127 +19376,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$43</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$58)</f>
-        <v>1.3426539742619228E-2</v>
+        <v>2.8195026495079485E-3</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -19634,127 +19634,127 @@
       </c>
       <c r="B4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="C4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="D4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="E4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="F4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="G4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="H4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="I4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="J4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="K4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="L4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="M4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="N4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="O4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="P4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="Q4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="R4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="S4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="T4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="U4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="V4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="W4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="X4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="Y4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="Z4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AA4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AB4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AC4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AD4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AE4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AF4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -19763,127 +19763,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>4.1782E-3</v>
+        <v>8.7739999999999997E-4</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -20150,127 +20150,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!D43</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$64)</f>
-        <v>1.2534599999999998E-2</v>
+        <v>2.6321999999999995E-3</v>
       </c>
     </row>
   </sheetData>
@@ -20394,127 +20394,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$44</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$65)</f>
-        <v>1.5613951930355792E-2</v>
+        <v>3.2790295230885696E-3</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -20523,127 +20523,127 @@
       </c>
       <c r="B3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="C3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="D3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="E3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="F3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="G3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="H3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="I3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="J3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="K3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="L3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="M3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="N3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="O3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="P3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="Q3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="R3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="S3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="T3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="U3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="V3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="W3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="X3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="Y3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="Z3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AA3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AB3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AC3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AD3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AE3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AF3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -20652,127 +20652,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -20781,127 +20781,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.8893954176843649E-3</v>
+        <v>1.0268042322758497E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.9200822306433275E-3</v>
+        <v>1.0332486587804753E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.950961640111497E-3</v>
+        <v>1.0397335317808088E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>4.9820348548626683E-3</v>
+        <v>1.0462591051270589E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.0133030912571401E-3</v>
+        <v>1.052825634262649E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.0447675732893287E-3</v>
+        <v>1.0594333762342157E-3</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.0764295326356816E-3</v>
+        <v>1.0660825897016711E-3</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.1082902087028915E-3</v>
+        <v>1.072773534948328E-3</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.1403508486764131E-3</v>
+        <v>1.079506473891089E-3</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.1726127075692827E-3</v>
+        <v>1.0862816700906988E-3</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.205077048271247E-3</v>
+        <v>1.0930993887620615E-3</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.2377451415981996E-3</v>
+        <v>1.0999598967846227E-3</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.2706182663419246E-3</v>
+        <v>1.1068634627128158E-3</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.3036977093201577E-3</v>
+        <v>1.1138103567865751E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.3369847654269565E-3</v>
+        <v>1.1208008509419143E-3</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.3704807376833896E-3</v>
+        <v>1.1278352188215711E-3</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.4041869372885446E-3</v>
+        <v>1.1349137357857194E-3</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.4381046836708535E-3</v>
+        <v>1.142036678922748E-3</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.4722353045397413E-3</v>
+        <v>1.1492043270601071E-3</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.506580135937602E-3</v>
+        <v>1.156416960775223E-3</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.5411405222920941E-3</v>
+        <v>1.1636748624064819E-3</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.5759178164687707E-3</v>
+        <v>1.1709783160642811E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.6109133798240372E-3</v>
+        <v>1.1783276076421515E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.6461285822584405E-3</v>
+        <v>1.1857230248279477E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.6815648022702945E-3</v>
+        <v>1.1931648571151107E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.7172234270096425E-3</v>
+        <v>1.2006533958139993E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.7531058523325532E-3</v>
+        <v>1.2081889340632942E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.7892134828557672E-3</v>
+        <v>1.2157717668414719E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.8255477320116747E-3</v>
+        <v>1.2234021909783522E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>5.8621100221036499E-3</v>
+        <v>1.2310805051667182E-3</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -21168,127 +21168,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$44</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$71)</f>
-        <v>1.4576699999999998E-2</v>
+        <v>3.0611999999999996E-3</v>
       </c>
     </row>
   </sheetData>
@@ -21460,16 +21460,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="34">
-        <v>1.5614100000000001E-2</v>
+        <v>3.2789999999999998E-3</v>
       </c>
       <c r="C6" s="34">
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="D6" s="34">
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="E6" s="34">
-        <v>4.8589000000000002E-3</v>
+        <v>1.0204000000000001E-3</v>
       </c>
       <c r="F6" s="34">
         <v>0</v>
@@ -21478,7 +21478,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="34">
-        <v>1.4576799999999999E-2</v>
+        <v>3.0611000000000002E-3</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>

--- a/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
+++ b/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\BNVFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BC1A94-0FBE-4037-A2D4-66A4923CE019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E181AA3-FE3A-4293-85A2-0C24EFE6BC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26580" yWindow="750" windowWidth="25050" windowHeight="14940" firstSheet="23" activeTab="27" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
+    <workbookView xWindow="-25170" yWindow="1545" windowWidth="25050" windowHeight="14970" firstSheet="18" activeTab="23" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -10944,16 +10944,16 @@
         <v>18</v>
       </c>
       <c r="B4" s="34">
-        <v>1.9247999999999999E-3</v>
+        <v>7.3141853515822292E-4</v>
       </c>
       <c r="C4" s="34">
-        <v>5.9900000000000003E-4</v>
+        <v>2.2760961548490743E-4</v>
       </c>
       <c r="D4" s="34">
-        <v>5.9900000000000003E-4</v>
+        <v>2.2760961548490743E-4</v>
       </c>
       <c r="E4" s="34">
-        <v>5.9900000000000003E-4</v>
+        <v>2.2760961548490743E-4</v>
       </c>
       <c r="F4" s="34">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="34">
-        <v>1.7968999999999999E-3</v>
+        <v>6.8282937766954584E-4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -10996,16 +10996,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="34">
-        <v>2.8195999999999998E-3</v>
+        <v>2.9538323562160623E-3</v>
       </c>
       <c r="C6" s="34">
         <v>0</v>
       </c>
       <c r="D6" s="34">
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="E6" s="34">
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="F6" s="34">
         <v>0</v>
@@ -11014,7 +11014,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="34">
-        <v>2.6323000000000002E-3</v>
+        <v>2.7576049190822485E-3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -15277,127 +15277,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!B32</f>
-        <v>1.9385542819327719E-3</v>
+        <v>7.3661701954480638E-4</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$30)</f>
-        <v>1.9523345198353156E-3</v>
+        <v>7.4185327104779218E-4</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$30)</f>
-        <v>1.9662127147352057E-3</v>
+        <v>7.4712674451154603E-4</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$30)</f>
-        <v>1.9801895629610101E-3</v>
+        <v>7.5243770452885193E-4</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$30)</f>
-        <v>1.9942657657911578E-3</v>
+        <v>7.5778641757335522E-4</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$30)</f>
-        <v>2.0084420294891239E-3</v>
+        <v>7.6317315201293243E-4</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$30)</f>
-        <v>2.0227190653388672E-3</v>
+        <v>7.6859817812315663E-4</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$30)</f>
-        <v>2.0370975896805174E-3</v>
+        <v>7.7406176810085835E-4</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$30)</f>
-        <v>2.0515783239463165E-3</v>
+        <v>7.7956419607778276E-4</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$30)</f>
-        <v>2.0661619946968179E-3</v>
+        <v>7.8510573813434382E-4</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$30)</f>
-        <v>2.0808493336573392E-3</v>
+        <v>7.9068667231347689E-4</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$30)</f>
-        <v>2.0956410777546769E-3</v>
+        <v>7.9630727863458904E-4</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$30)</f>
-        <v>2.1105379691540812E-3</v>
+        <v>8.019678391076087E-4</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$30)</f>
-        <v>2.1255407552964933E-3</v>
+        <v>8.076686377471358E-4</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$30)</f>
-        <v>2.1406501889360482E-3</v>
+        <v>8.1340996058669143E-4</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$30)</f>
-        <v>2.155867028177843E-3</v>
+        <v>8.1919209569306962E-4</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$30)</f>
-        <v>2.1711920365159744E-3</v>
+        <v>8.2501533318079102E-4</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$30)</f>
-        <v>2.1866259828718475E-3</v>
+        <v>8.308799652266591E-4</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$30)</f>
-        <v>2.2021696416327542E-3</v>
+        <v>8.3678628608441967E-4</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$30)</f>
-        <v>2.2178237926907284E-3</v>
+        <v>8.4273459209952516E-4</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$30)</f>
-        <v>2.233589221481677E-3</v>
+        <v>8.4872518172400351E-4</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$30)</f>
-        <v>2.2494667190247879E-3</v>
+        <v>8.5475835553143259E-4</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$30)</f>
-        <v>2.2654570819622189E-3</v>
+        <v>8.608344162320215E-4</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$30)</f>
-        <v>2.2815611125990686E-3</v>
+        <v>8.6695366868779866E-4</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$30)</f>
-        <v>2.2977796189436323E-3</v>
+        <v>8.7311641992790826E-4</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$30)</f>
-        <v>2.3141134147479417E-3</v>
+        <v>8.7932297916401482E-4</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$30)</f>
-        <v>2.3305633195485958E-3</v>
+        <v>8.8557365780581813E-4</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$30)</f>
-        <v>2.34713015870788E-3</v>
+        <v>8.9186876947667778E-4</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$30)</f>
-        <v>2.3638147634551777E-3</v>
+        <v>8.9820863002934906E-4</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$30)</f>
-        <v>2.3806179709286771E-3</v>
+        <v>9.0459355756183045E-4</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$30)</f>
-        <v>2.3975406242173745E-3</v>
+        <v>9.1102387243332432E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -15667,127 +15667,127 @@
       </c>
       <c r="B5" s="14">
         <f>'SYFAFE psgr'!E4*(1+CAGR!$C$33)</f>
-        <v>6.0325799915976247E-4</v>
+        <v>2.2922758134715884E-4</v>
       </c>
       <c r="C5" s="14">
         <f>B5*(1+CAGR!$C$33)</f>
-        <v>6.0754626636100166E-4</v>
+        <v>2.3085704854043193E-4</v>
       </c>
       <c r="D5" s="14">
         <f>C5*(1+CAGR!$C$33)</f>
-        <v>6.1186501676447735E-4</v>
+        <v>2.3249809882208534E-4</v>
       </c>
       <c r="E5" s="14">
         <f>D5*(1+CAGR!$C$33)</f>
-        <v>6.1621446706042258E-4</v>
+        <v>2.3415081453065096E-4</v>
       </c>
       <c r="F5" s="14">
         <f>E5*(1+CAGR!$C$33)</f>
-        <v>6.205948354794155E-4</v>
+        <v>2.3581527858996517E-4</v>
       </c>
       <c r="G5" s="14">
         <f>F5*(1+CAGR!$C$33)</f>
-        <v>6.2500634180332913E-4</v>
+        <v>2.3749157451332948E-4</v>
       </c>
       <c r="H5" s="14">
         <f>G5*(1+CAGR!$C$33)</f>
-        <v>6.2944920737635884E-4</v>
+        <v>2.3917978640770079E-4</v>
       </c>
       <c r="I5" s="14">
         <f>H5*(1+CAGR!$C$33)</f>
-        <v>6.339236551161279E-4</v>
+        <v>2.408799989779114E-4</v>
       </c>
       <c r="J5" s="14">
         <f>I5*(1+CAGR!$C$33)</f>
-        <v>6.3842990952487255E-4</v>
+        <v>2.4259229753091895E-4</v>
       </c>
       <c r="K5" s="14">
         <f>J5*(1+CAGR!$C$33)</f>
-        <v>6.429681967007058E-4</v>
+        <v>2.4431676798008671E-4</v>
       </c>
       <c r="L5" s="14">
         <f>K5*(1+CAGR!$C$33)</f>
-        <v>6.4753874434896215E-4</v>
+        <v>2.460534968494942E-4</v>
       </c>
       <c r="M5" s="14">
         <f>L5*(1+CAGR!$C$33)</f>
-        <v>6.5214178179362242E-4</v>
+        <v>2.4780257127827846E-4</v>
       </c>
       <c r="N5" s="14">
         <f>M5*(1+CAGR!$C$33)</f>
-        <v>6.5677753998881982E-4</v>
+        <v>2.4956407902500613E-4</v>
       </c>
       <c r="O5" s="14">
         <f>N5*(1+CAGR!$C$33)</f>
-        <v>6.6144625153042788E-4</v>
+        <v>2.5133810847207685E-4</v>
       </c>
       <c r="P5" s="14">
         <f>O5*(1+CAGR!$C$33)</f>
-        <v>6.6614815066773098E-4</v>
+        <v>2.5312474863015762E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>P5*(1+CAGR!$C$33)</f>
-        <v>6.7088347331517757E-4</v>
+        <v>2.5492408914264895E-4</v>
       </c>
       <c r="R5" s="14">
         <f>Q5*(1+CAGR!$C$33)</f>
-        <v>6.7565245706421688E-4</v>
+        <v>2.567362202901825E-4</v>
       </c>
       <c r="S5" s="14">
         <f>R5*(1+CAGR!$C$33)</f>
-        <v>6.8045534119522003E-4</v>
+        <v>2.5856123299515109E-4</v>
       </c>
       <c r="T5" s="14">
         <f>S5*(1+CAGR!$C$33)</f>
-        <v>6.8529236668948563E-4</v>
+        <v>2.6039921882627044E-4</v>
       </c>
       <c r="U5" s="14">
         <f>T5*(1+CAGR!$C$33)</f>
-        <v>6.9016377624133113E-4</v>
+        <v>2.6225027000317374E-4</v>
       </c>
       <c r="V5" s="14">
         <f>U5*(1+CAGR!$C$33)</f>
-        <v>6.9506981427026947E-4</v>
+        <v>2.6411447940103848E-4</v>
       </c>
       <c r="W5" s="14">
         <f>V5*(1+CAGR!$C$33)</f>
-        <v>7.0001072693327284E-4</v>
+        <v>2.6599194055524668E-4</v>
       </c>
       <c r="X5" s="14">
         <f>W5*(1+CAGR!$C$33)</f>
-        <v>7.049867621371236E-4</v>
+        <v>2.6788274766607775E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>X5*(1+CAGR!$C$33)</f>
-        <v>7.099981695508524E-4</v>
+        <v>2.6978699560343503E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>Y5*(1+CAGR!$C$33)</f>
-        <v>7.1504520061826547E-4</v>
+        <v>2.7170477991160573E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>Z5*(1+CAGR!$C$33)</f>
-        <v>7.2012810857056053E-4</v>
+        <v>2.7363619681405492E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>AA5*(1+CAGR!$C$33)</f>
-        <v>7.2524714843903259E-4</v>
+        <v>2.755813432182533E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>AB5*(1+CAGR!$C$33)</f>
-        <v>7.3040257706786984E-4</v>
+        <v>2.7754031672053966E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>AC5*(1+CAGR!$C$33)</f>
-        <v>7.3559465312704063E-4</v>
+        <v>2.7951321561101754E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>AD5*(1+CAGR!$C$33)</f>
-        <v>7.4082363712527218E-4</v>
+        <v>2.8150013887848701E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>AE5*(1+CAGR!$C$33)</f>
-        <v>7.4608979142312118E-4</v>
+        <v>2.8350118621541122E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -16057,127 +16057,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!D32</f>
-        <v>1.8097739974792871E-3</v>
+        <v>6.8768274404147644E-4</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$36)</f>
-        <v>1.8226387990830045E-3</v>
+        <v>6.9257114562129574E-4</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$36)</f>
-        <v>1.8355950502934317E-3</v>
+        <v>6.9749429646625595E-4</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$36)</f>
-        <v>1.8486434011812673E-3</v>
+        <v>7.0245244359195278E-4</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$36)</f>
-        <v>1.8617845064382459E-3</v>
+        <v>7.0744583576989536E-4</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$36)</f>
-        <v>1.875019025409987E-3</v>
+        <v>7.1247472353998828E-4</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$36)</f>
-        <v>1.888347622129076E-3</v>
+        <v>7.1753935922310222E-4</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$36)</f>
-        <v>1.9017709653483832E-3</v>
+        <v>7.2263999693373399E-4</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$36)</f>
-        <v>1.915289728574617E-3</v>
+        <v>7.2777689259275662E-4</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$36)</f>
-        <v>1.9289045901021169E-3</v>
+        <v>7.329503039402599E-4</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$36)</f>
-        <v>1.9426162330468861E-3</v>
+        <v>7.3816049054848233E-4</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$36)</f>
-        <v>1.9564253453808671E-3</v>
+        <v>7.4340771383483507E-4</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$36)</f>
-        <v>1.9703326199664592E-3</v>
+        <v>7.4869223707501817E-4</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$36)</f>
-        <v>1.9843387545912835E-3</v>
+        <v>7.5401432541623032E-4</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$36)</f>
-        <v>1.9984444520031929E-3</v>
+        <v>7.5937424589047264E-4</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$36)</f>
-        <v>2.0126504199455327E-3</v>
+        <v>7.6477226742794658E-4</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$36)</f>
-        <v>2.0269573711926506E-3</v>
+        <v>7.7020866087054729E-4</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$36)</f>
-        <v>2.0413660235856601E-3</v>
+        <v>7.7568369898545306E-4</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$36)</f>
-        <v>2.0558771000684572E-3</v>
+        <v>7.8119765647881117E-4</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$36)</f>
-        <v>2.0704913287239936E-3</v>
+        <v>7.8675081000952095E-4</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$36)</f>
-        <v>2.0852094428108086E-3</v>
+        <v>7.9234343820311522E-4</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$36)</f>
-        <v>2.1000321807998191E-3</v>
+        <v>7.9797582166573982E-4</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$36)</f>
-        <v>2.1149602864113711E-3</v>
+        <v>8.0364824299823309E-4</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$36)</f>
-        <v>2.1299945086525572E-3</v>
+        <v>8.0936098681030498E-4</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$36)</f>
-        <v>2.1451356018547963E-3</v>
+        <v>8.1511433973481713E-4</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$36)</f>
-        <v>2.1603843257116816E-3</v>
+        <v>8.2090859044216464E-4</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$36)</f>
-        <v>2.175741445317098E-3</v>
+        <v>8.2674402965475979E-4</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$36)</f>
-        <v>2.19120773120361E-3</v>
+        <v>8.3262095016161893E-4</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$36)</f>
-        <v>2.2067839593811222E-3</v>
+        <v>8.3853964683305263E-4</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$36)</f>
-        <v>2.2224709113758167E-3</v>
+        <v>8.4450041663546103E-4</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$36)</f>
-        <v>2.238269374269364E-3</v>
+        <v>8.5050355864623372E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -16304,127 +16304,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$32</f>
-        <v>8.3820627549346894E-4</v>
+        <v>3.1847200406925024E-4</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$37)</f>
-        <v>8.4416467552144694E-4</v>
+        <v>3.207358663826638E-4</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$37)</f>
-        <v>8.5016543091221732E-4</v>
+        <v>3.2301582139028159E-4</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$37)</f>
-        <v>8.5620884274941811E-4</v>
+        <v>3.2531198348722618E-4</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$37)</f>
-        <v>8.6229521425694434E-4</v>
+        <v>3.2762446788179927E-4</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$37)</f>
-        <v>8.6842485081416176E-4</v>
+        <v>3.2995339060126223E-4</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$37)</f>
-        <v>8.7459805997122946E-4</v>
+        <v>3.3229886849765782E-4</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$37)</f>
-        <v>8.8081515146453055E-4</v>
+        <v>3.3466101925367292E-4</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$37)</f>
-        <v>8.8707643723221342E-4</v>
+        <v>3.3703996138854334E-4</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$37)</f>
-        <v>8.9338223142984249E-4</v>
+        <v>3.3943581426400043E-4</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$37)</f>
-        <v>8.9973285044616129E-4</v>
+        <v>3.4184869809025987E-4</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$37)</f>
-        <v>9.0612861291896663E-4</v>
+        <v>3.4427873393205321E-4</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$37)</f>
-        <v>9.1256983975109636E-4</v>
+        <v>3.4672604371470221E-4</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$37)</f>
-        <v>9.1905685412652994E-4</v>
+        <v>3.4919075023023637E-4</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$37)</f>
-        <v>9.2558998152660456E-4</v>
+        <v>3.5167297714355387E-4</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$37)</f>
-        <v>9.321695497463455E-4</v>
+        <v>3.5417284899862638E-4</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$37)</f>
-        <v>9.3879588891091327E-4</v>
+        <v>3.5669049122474795E-4</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$37)</f>
-        <v>9.4546933149216726E-4</v>
+        <v>3.5922603014282848E-4</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$37)</f>
-        <v>9.521902123253473E-4</v>
+        <v>3.6177959297173162E-4</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$37)</f>
-        <v>9.589588686258738E-4</v>
+        <v>3.6435130783465789E-4</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$37)</f>
-        <v>9.6577564000626737E-4</v>
+        <v>3.6694130376557332E-4</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$37)</f>
-        <v>9.7264086849318848E-4</v>
+        <v>3.695497107156834E-4</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$37)</f>
-        <v>9.7955489854459864E-4</v>
+        <v>3.7217665955995358E-4</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$37)</f>
-        <v>9.8651807706704288E-4</v>
+        <v>3.7482228210367557E-4</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$37)</f>
-        <v>9.9353075343305624E-4</v>
+        <v>3.7748671108908075E-4</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$37)</f>
-        <v>1.0005932794986926E-3</v>
+        <v>3.801700802020003E-4</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$37)</f>
-        <v>1.007706009621179E-3</v>
+        <v>3.8287252407857283E-4</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$37)</f>
-        <v>1.0148693006766958E-3</v>
+        <v>3.8559417831199972E-4</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$37)</f>
-        <v>1.0220835120782819E-3</v>
+        <v>3.8833517945934828E-4</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$37)</f>
-        <v>1.0293490057938686E-3</v>
+        <v>3.9109566504840355E-4</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$37)</f>
-        <v>1.0366661463644406E-3</v>
+        <v>3.9387577358456855E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -16694,127 +16694,127 @@
       </c>
       <c r="B5" s="14">
         <f>'SYFAFE frgt'!E4*(1+CAGR!$C$40)</f>
-        <v>2.6084110481198412E-4</v>
+        <v>9.9105186660890365E-5</v>
       </c>
       <c r="C5" s="14">
         <f>B5*(1+CAGR!$C$40)</f>
-        <v>2.6269529714106747E-4</v>
+        <v>9.9809677147585148E-5</v>
       </c>
       <c r="D5" s="14">
         <f>C5*(1+CAGR!$C$40)</f>
-        <v>2.6456267002003276E-4</v>
+        <v>1.0051917551391333E-4</v>
       </c>
       <c r="E5" s="14">
         <f>D5*(1+CAGR!$C$40)</f>
-        <v>2.6644331714298738E-4</v>
+        <v>1.0123371735845133E-4</v>
       </c>
       <c r="F5" s="14">
         <f>E5*(1+CAGR!$C$40)</f>
-        <v>2.6833733287006447E-4</v>
+        <v>1.0195333853282848E-4</v>
       </c>
       <c r="G5" s="14">
         <f>F5*(1+CAGR!$C$40)</f>
-        <v>2.7024481223215734E-4</v>
+        <v>1.0267807514352592E-4</v>
       </c>
       <c r="H5" s="14">
         <f>G5*(1+CAGR!$C$40)</f>
-        <v>2.7216585093568768E-4</v>
+        <v>1.0340796355368813E-4</v>
       </c>
       <c r="I5" s="14">
         <f>H5*(1+CAGR!$C$40)</f>
-        <v>2.7410054536740753E-4</v>
+        <v>1.0414304038494747E-4</v>
       </c>
       <c r="J5" s="14">
         <f>I5*(1+CAGR!$C$40)</f>
-        <v>2.7604899259923532E-4</v>
+        <v>1.0488334251926168E-4</v>
       </c>
       <c r="K5" s="14">
         <f>J5*(1+CAGR!$C$40)</f>
-        <v>2.7801129039312647E-4</v>
+        <v>1.0562890710076435E-4</v>
       </c>
       <c r="L5" s="14">
         <f>K5*(1+CAGR!$C$40)</f>
-        <v>2.7998753720597858E-4</v>
+        <v>1.0637977153762859E-4</v>
       </c>
       <c r="M5" s="14">
         <f>L5*(1+CAGR!$C$40)</f>
-        <v>2.8197783219457127E-4</v>
+        <v>1.0713597350394403E-4</v>
       </c>
       <c r="N5" s="14">
         <f>M5*(1+CAGR!$C$40)</f>
-        <v>2.839822752205414E-4</v>
+        <v>1.0789755094160701E-4</v>
       </c>
       <c r="O5" s="14">
         <f>N5*(1+CAGR!$C$40)</f>
-        <v>2.8600096685539367E-4</v>
+        <v>1.0866454206222435E-4</v>
       </c>
       <c r="P5" s="14">
         <f>O5*(1+CAGR!$C$40)</f>
-        <v>2.8803400838554644E-4</v>
+        <v>1.0943698534903056E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>P5*(1+CAGR!$C$40)</f>
-        <v>2.9008150181741399E-4</v>
+        <v>1.1021491955881872E-4</v>
       </c>
       <c r="R5" s="14">
         <f>Q5*(1+CAGR!$C$40)</f>
-        <v>2.9214354988252447E-4</v>
+        <v>1.1099838372388506E-4</v>
       </c>
       <c r="S5" s="14">
         <f>R5*(1+CAGR!$C$40)</f>
-        <v>2.9422025604267441E-4</v>
+        <v>1.1178741715398738E-4</v>
       </c>
       <c r="T5" s="14">
         <f>S5*(1+CAGR!$C$40)</f>
-        <v>2.9631172449511982E-4</v>
+        <v>1.1258205943831743E-4</v>
       </c>
       <c r="U5" s="14">
         <f>T5*(1+CAGR!$C$40)</f>
-        <v>2.9841806017780426E-4</v>
+        <v>1.1338235044748718E-4</v>
       </c>
       <c r="V5" s="14">
         <f>U5*(1+CAGR!$C$40)</f>
-        <v>3.0053936877462401E-4</v>
+        <v>1.1418833033552941E-4</v>
       </c>
       <c r="W5" s="14">
         <f>V5*(1+CAGR!$C$40)</f>
-        <v>3.026757567207307E-4</v>
+        <v>1.1500003954191232E-4</v>
       </c>
       <c r="X5" s="14">
         <f>W5*(1+CAGR!$C$40)</f>
-        <v>3.0482733120787149E-4</v>
+        <v>1.158175187935686E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>X5*(1+CAGR!$C$40)</f>
-        <v>3.0699420018976754E-4</v>
+        <v>1.1664080910693887E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>Y5*(1+CAGR!$C$40)</f>
-        <v>3.0917647238753044E-4</v>
+        <v>1.1746995179002963E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>Z5*(1+CAGR!$C$40)</f>
-        <v>3.1137425729511713E-4</v>
+        <v>1.1830498844448586E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>AA5*(1+CAGR!$C$40)</f>
-        <v>3.1358766518482377E-4</v>
+        <v>1.191459609676784E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>AB5*(1+CAGR!$C$40)</f>
-        <v>3.1581680711281849E-4</v>
+        <v>1.1999291155480606E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>AC5*(1+CAGR!$C$40)</f>
-        <v>3.1806179492471374E-4</v>
+        <v>1.2084588270101276E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>AD5*(1+CAGR!$C$40)</f>
-        <v>3.2032274126117782E-4</v>
+        <v>1.2170491720351972E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>AE5*(1+CAGR!$C$40)</f>
-        <v>3.2259975956358669E-4</v>
+        <v>1.2257005816377272E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -17084,127 +17084,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$32</f>
-        <v>7.8252331443595224E-4</v>
+        <v>2.9731555998267105E-4</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$43)</f>
-        <v>7.880858914232024E-4</v>
+        <v>2.9942903144275539E-4</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$43)</f>
-        <v>7.9368801006009834E-4</v>
+        <v>3.0155752654173994E-4</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$43)</f>
-        <v>7.9932995142896219E-4</v>
+        <v>3.0370115207535391E-4</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$43)</f>
-        <v>8.0501199861019335E-4</v>
+        <v>3.0586001559848537E-4</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$43)</f>
-        <v>8.1073443669647197E-4</v>
+        <v>3.0803422543057769E-4</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$43)</f>
-        <v>8.1649755280706305E-4</v>
+        <v>3.1022389066106431E-4</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$43)</f>
-        <v>8.2230163610222265E-4</v>
+        <v>3.1242912115484237E-4</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$43)</f>
-        <v>8.2814697779770607E-4</v>
+        <v>3.1465002755778502E-4</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$43)</f>
-        <v>8.3403387117937959E-4</v>
+        <v>3.1688672130229301E-4</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$43)</f>
-        <v>8.3996261161793585E-4</v>
+        <v>3.1913931461288573E-4</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$43)</f>
-        <v>8.4593349658371392E-4</v>
+        <v>3.2140792051183202E-4</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$43)</f>
-        <v>8.5194682566162438E-4</v>
+        <v>3.2369265282482099E-4</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$43)</f>
-        <v>8.5800290056618116E-4</v>
+        <v>3.2599362618667305E-4</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$43)</f>
-        <v>8.6410202515663952E-4</v>
+        <v>3.2831095604709171E-4</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$43)</f>
-        <v>8.7024450545224218E-4</v>
+        <v>3.3064475867645619E-4</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$43)</f>
-        <v>8.7643064964757367E-4</v>
+        <v>3.3299515117165521E-4</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$43)</f>
-        <v>8.8266076812802349E-4</v>
+        <v>3.3536225146196217E-4</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$43)</f>
-        <v>8.8893517348535974E-4</v>
+        <v>3.3774617831495231E-4</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$43)</f>
-        <v>8.9525418053341304E-4</v>
+        <v>3.4014705134246159E-4</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$43)</f>
-        <v>9.0161810632387231E-4</v>
+        <v>3.4256499100658827E-4</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$43)</f>
-        <v>9.0802727016219226E-4</v>
+        <v>3.4500011862573698E-4</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$43)</f>
-        <v>9.1448199362361468E-4</v>
+        <v>3.4745255638070582E-4</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$43)</f>
-        <v>9.2098260056930293E-4</v>
+        <v>3.499224273208166E-4</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$43)</f>
-        <v>9.2752941716259165E-4</v>
+        <v>3.5240985537008887E-4</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$43)</f>
-        <v>9.3412277188535176E-4</v>
+        <v>3.5491496533345755E-4</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$43)</f>
-        <v>9.4076299555447159E-4</v>
+        <v>3.5743788290303513E-4</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$43)</f>
-        <v>9.4745042133845584E-4</v>
+        <v>3.5997873466441812E-4</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$43)</f>
-        <v>9.5418538477414156E-4</v>
+        <v>3.6253764810303821E-4</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$43)</f>
-        <v>9.6096822378353367E-4</v>
+        <v>3.6511475161055904E-4</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$43)</f>
-        <v>9.6779927869076023E-4</v>
+        <v>3.6771017449131803E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -19376,127 +19376,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$43</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$58)</f>
-        <v>2.8195026495079485E-3</v>
+        <v>2.9538232025526343E-3</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -19634,127 +19634,127 @@
       </c>
       <c r="B4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="C4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="D4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="E4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="F4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="G4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="H4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="I4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="J4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="K4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="L4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="M4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="N4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="O4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="P4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="Q4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="R4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="S4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="T4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="U4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="V4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="W4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="X4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="Y4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="Z4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AA4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AB4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AC4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AD4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AE4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AF4">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A4,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -19763,127 +19763,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$6:$H$6,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$58:$C$64,MATCH($A5,CAGR!$B$58:$B$64,0))),0)</f>
-        <v>8.7739999999999997E-4</v>
+        <v>9.1919916385677981E-4</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -20150,127 +20150,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!D43</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$64)</f>
-        <v>2.6321999999999995E-3</v>
+        <v>2.7575974915703392E-3</v>
       </c>
     </row>
   </sheetData>
@@ -20394,127 +20394,127 @@
       </c>
       <c r="B2" s="13">
         <f>B5*Calibration!$B$44</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="C2" s="13">
         <f>B2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="D2" s="13">
         <f>C2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="E2" s="13">
         <f>D2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="F2" s="13">
         <f>E2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="G2" s="13">
         <f>F2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="H2" s="13">
         <f>G2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="I2" s="13">
         <f>H2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="J2" s="13">
         <f>I2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="K2" s="13">
         <f>J2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="L2" s="13">
         <f>K2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="M2" s="13">
         <f>L2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="N2" s="13">
         <f>M2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="O2" s="13">
         <f>N2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="P2" s="13">
         <f>O2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="Q2" s="13">
         <f>P2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="R2" s="13">
         <f>Q2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="S2" s="13">
         <f>R2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="T2" s="13">
         <f>S2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="U2" s="13">
         <f>T2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="V2" s="13">
         <f>U2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="W2" s="13">
         <f>V2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="X2" s="13">
         <f>W2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="Y2" s="13">
         <f>X2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="Z2" s="13">
         <f>Y2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="AA2" s="13">
         <f>Z2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="AB2" s="13">
         <f>AA2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="AC2" s="13">
         <f>AB2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="AD2" s="13">
         <f>AC2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="AE2" s="13">
         <f>AD2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
       <c r="AF2" s="13">
         <f>AE2*(1+CAGR!$C$65)</f>
-        <v>3.2790295230885696E-3</v>
+        <v>3.4351009391108858E-3</v>
       </c>
     </row>
     <row r="3" spans="1:32">
@@ -20523,127 +20523,127 @@
       </c>
       <c r="B3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="C3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="D3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="E3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="F3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="G3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="H3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="I3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="J3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="K3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="L3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="M3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="N3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="O3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="P3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="Q3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="R3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="S3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="T3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="U3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="V3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="W3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="X3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="Y3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="Z3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AA3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AB3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AC3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AD3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AE3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AF3">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A3,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A3,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
     </row>
     <row r="4" spans="1:32">
@@ -20652,127 +20652,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A4,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
     </row>
     <row r="5" spans="1:32">
@@ -20781,127 +20781,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$6:$H$6,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$65:$C$71,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0268042322758497E-3</v>
+        <v>1.0756768604057887E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0332486587804753E-3</v>
+        <v>1.0824280211935145E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0397335317808088E-3</v>
+        <v>1.089221553601993E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0462591051270589E-3</v>
+        <v>1.096057723563899E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.052825634262649E-3</v>
+        <v>1.1029367986809533E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0594333762342157E-3</v>
+        <v>1.1098590482343977E-3</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0660825897016711E-3</v>
+        <v>1.116824743195537E-3</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.072773534948328E-3</v>
+        <v>1.1238341562363448E-3</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.079506473891089E-3</v>
+        <v>1.1308875617401385E-3</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0862816700906988E-3</v>
+        <v>1.1379852358123191E-3</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0930993887620615E-3</v>
+        <v>1.1451274562911799E-3</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.0999598967846227E-3</v>
+        <v>1.1523145027587823E-3</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1068634627128158E-3</v>
+        <v>1.1595466565519001E-3</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1138103567865751E-3</v>
+        <v>1.1668242007730322E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1208008509419143E-3</v>
+        <v>1.1741474203014848E-3</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1278352188215711E-3</v>
+        <v>1.181516601804523E-3</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1349137357857194E-3</v>
+        <v>1.1889320337485926E-3</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.142036678922748E-3</v>
+        <v>1.1963940064106116E-3</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1492043270601071E-3</v>
+        <v>1.2039028118893335E-3</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.156416960775223E-3</v>
+        <v>1.2114587441167813E-3</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1636748624064819E-3</v>
+        <v>1.2190620988697535E-3</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1709783160642811E-3</v>
+        <v>1.2267131737814024E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1783276076421515E-3</v>
+        <v>1.2344122683528849E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1857230248279477E-3</v>
+        <v>1.2421596839650862E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.1931648571151107E-3</v>
+        <v>1.2499557238904177E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.2006533958139993E-3</v>
+        <v>1.2578006933046885E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.2081889340632942E-3</v>
+        <v>1.2656948992990514E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.2157717668414719E-3</v>
+        <v>1.273638650892024E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.2234021909783522E-3</v>
+        <v>1.2816322590415851E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$51:$C$57,MATCH($A5,CAGR!$B$65:$B$71,0))),0)</f>
-        <v>1.2310805051667182E-3</v>
+        <v>1.2896760366573475E-3</v>
       </c>
     </row>
     <row r="6" spans="1:32">
@@ -21168,127 +21168,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$44</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$71)</f>
-        <v>3.0611999999999996E-3</v>
+        <v>3.2069034208943316E-3</v>
       </c>
     </row>
   </sheetData>
@@ -21404,16 +21404,16 @@
         <v>18</v>
       </c>
       <c r="B4" s="34">
-        <v>8.3219999999999995E-4</v>
+        <v>3.1622429237254017E-4</v>
       </c>
       <c r="C4" s="34">
-        <v>2.5900000000000001E-4</v>
+        <v>9.8405668706519375E-5</v>
       </c>
       <c r="D4" s="34">
-        <v>2.5900000000000001E-4</v>
+        <v>9.8405668706519375E-5</v>
       </c>
       <c r="E4" s="34">
-        <v>2.5900000000000001E-4</v>
+        <v>9.8405668706519375E-5</v>
       </c>
       <c r="F4" s="34">
         <v>0</v>
@@ -21422,7 +21422,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="34">
-        <v>7.7689999999999996E-4</v>
+        <v>2.9521700611955811E-4</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -21460,16 +21460,16 @@
         <v>20</v>
       </c>
       <c r="B6" s="34">
-        <v>3.2789999999999998E-3</v>
+        <v>3.4351010215682137E-3</v>
       </c>
       <c r="C6" s="34">
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="D6" s="34">
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="E6" s="34">
-        <v>1.0204000000000001E-3</v>
+        <v>1.0689678069647774E-3</v>
       </c>
       <c r="F6" s="34">
         <v>0</v>
@@ -21478,7 +21478,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="34">
-        <v>3.0611000000000002E-3</v>
+        <v>3.2069034208943329E-3</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -28386,21 +28386,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -28544,10 +28529,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E16404-9CDB-444B-B1EF-816DE1AF2890}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -28569,19 +28579,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E16404-9CDB-444B-B1EF-816DE1AF2890}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
+++ b/InputData/trans/BNVFE/BAU New Veh Fuel Economy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\BNVFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E181AA3-FE3A-4293-85A2-0C24EFE6BC69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F188D68-581F-4326-9C9C-DF71807CD9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25170" yWindow="1545" windowWidth="25050" windowHeight="14970" firstSheet="18" activeTab="23" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
+    <workbookView xWindow="-24570" yWindow="2205" windowWidth="24345" windowHeight="13980" firstSheet="14" activeTab="19" xr2:uid="{D850E225-7E57-43A0-BCF6-AD6641E8498D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -10892,25 +10892,25 @@
         <v>16</v>
       </c>
       <c r="B2" s="34">
-        <v>1.2643000000000001E-3</v>
+        <v>9.8940000000000009E-4</v>
       </c>
       <c r="C2" s="34">
-        <v>2.944E-4</v>
+        <v>2.3039999999999999E-4</v>
       </c>
       <c r="D2" s="34">
-        <v>3.8079999999999999E-4</v>
+        <v>2.9799999999999998E-4</v>
       </c>
       <c r="E2" s="34">
-        <v>3.5330000000000002E-4</v>
+        <v>2.765E-4</v>
       </c>
       <c r="F2" s="34">
-        <v>4.347E-4</v>
+        <v>3.4019999999999998E-4</v>
       </c>
       <c r="G2" s="34">
-        <v>3.7209999999999999E-4</v>
+        <v>2.9119999999999998E-4</v>
       </c>
       <c r="H2" s="34">
-        <v>1.9093999999999999E-3</v>
+        <v>1.4943000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -10918,25 +10918,25 @@
         <v>17</v>
       </c>
       <c r="B3" s="34">
-        <v>2.5948999999999998E-3</v>
+        <v>2.0308000000000001E-3</v>
       </c>
       <c r="C3" s="34">
-        <v>2.0125E-3</v>
+        <v>1.575E-3</v>
       </c>
       <c r="D3" s="34">
-        <v>7.3919999999999997E-4</v>
+        <v>5.7850000000000002E-4</v>
       </c>
       <c r="E3" s="34">
-        <v>8.0749999999999995E-4</v>
+        <v>6.3199999999999997E-4</v>
       </c>
       <c r="F3" s="34">
-        <v>1.7906E-3</v>
+        <v>1.4013000000000001E-3</v>
       </c>
       <c r="G3" s="34">
-        <v>1.3548E-3</v>
+        <v>1.0602999999999999E-3</v>
       </c>
       <c r="H3" s="34">
-        <v>2.4225000000000002E-3</v>
+        <v>1.8959000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -11169,127 +11169,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2623958617063904E-3</v>
+        <v>9.8790988339183942E-4</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2604945911994145E-3</v>
+        <v>9.8642201102009069E-4</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2585961841599534E-3</v>
+        <v>9.849363795047519E-4</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2567006362753928E-3</v>
+        <v>9.8345298547091158E-4</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2548079432396135E-3</v>
+        <v>9.8197182554874123E-4</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2529181007529819E-3</v>
+        <v>9.804928963734875E-4</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2510311045223401E-3</v>
+        <v>9.790161945854648E-4</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2491469502609956E-3</v>
+        <v>9.7754171683004732E-4</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2472656336887122E-3</v>
+        <v>9.7606945975766172E-4</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2453871505317003E-3</v>
+        <v>9.7459942002377936E-4</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2435114965226068E-3</v>
+        <v>9.7313159428890857E-4</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2416386674005055E-3</v>
+        <v>9.7166597921858743E-4</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2397686589108877E-3</v>
+        <v>9.702025714833759E-4</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2379014668056521E-3</v>
+        <v>9.687413677588484E-4</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2360370868430956E-3</v>
+        <v>9.6728236472558619E-4</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2341755147879032E-3</v>
+        <v>9.6582555906916966E-4</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2323167464111389E-3</v>
+        <v>9.6437094748017134E-4</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2304607774902357E-3</v>
+        <v>9.629185266541477E-4</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2286076038089859E-3</v>
+        <v>9.6146829329163213E-4</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2267572211575324E-3</v>
+        <v>9.6002024409812725E-4</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2249096253323577E-3</v>
+        <v>9.5857437578409754E-4</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2230648121362756E-3</v>
+        <v>9.5713068506496162E-4</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2212227773784213E-3</v>
+        <v>9.5568916866108512E-4</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2193835168742414E-3</v>
+        <v>9.5424982329777295E-4</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2175470264454849E-3</v>
+        <v>9.5281264570526198E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2157133019201939E-3</v>
+        <v>9.513776326187137E-4</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2138823391326934E-3</v>
+        <v>9.4994478077820661E-4</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2120541339235822E-3</v>
+        <v>9.485140869287291E-4</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2102286821397241E-3</v>
+        <v>9.4708554782017157E-4</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2084059796342373E-3</v>
+        <v>9.4565916020731959E-4</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A2,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.2065860222664855E-3</v>
+        <v>9.442349208498462E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -11299,127 +11299,127 @@
       </c>
       <c r="B3" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9513855523174623E-4</v>
+        <v>2.3097799974658399E-4</v>
       </c>
       <c r="C3" s="14">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.958789632618292E-4</v>
+        <v>2.3155744950925761E-4</v>
       </c>
       <c r="D3" s="14">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9662122873832603E-4</v>
+        <v>2.3213835292564645E-4</v>
       </c>
       <c r="E3" s="14">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9736535632097442E-4</v>
+        <v>2.3272071364250171E-4</v>
       </c>
       <c r="F3" s="14">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9811135068120179E-4</v>
+        <v>2.3330453531572311E-4</v>
       </c>
       <c r="G3" s="14">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.988592165021547E-4</v>
+        <v>2.338898216103819E-4</v>
       </c>
       <c r="H3" s="14">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>2.9960895847872822E-4</v>
+        <v>2.3447657620074378E-4</v>
       </c>
       <c r="I3" s="14">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0036058131759541E-4</v>
+        <v>2.3506480277029202E-4</v>
       </c>
       <c r="J3" s="14">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0111408973723685E-4</v>
+        <v>2.3565450501175056E-4</v>
       </c>
       <c r="K3" s="14">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.018694884679703E-4</v>
+        <v>2.3624568662710719E-4</v>
       </c>
       <c r="L3" s="14">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0262678225198038E-4</v>
+        <v>2.3683835132763683E-4</v>
       </c>
       <c r="M3" s="14">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0338597584334833E-4</v>
+        <v>2.3743250283392479E-4</v>
       </c>
       <c r="N3" s="14">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0414707400808178E-4</v>
+        <v>2.3802814487589011E-4</v>
       </c>
       <c r="O3" s="14">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0491008152414489E-4</v>
+        <v>2.3862528119280904E-4</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0567500318148805E-4</v>
+        <v>2.3922391553333846E-4</v>
       </c>
       <c r="Q3" s="14">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0644184378207813E-4</v>
+        <v>2.3982405165553941E-4</v>
       </c>
       <c r="R3" s="14">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.072106081399287E-4</v>
+        <v>2.4042569332690072E-4</v>
       </c>
       <c r="S3" s="14">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0798130108113006E-4</v>
+        <v>2.4102884432436266E-4</v>
       </c>
       <c r="T3" s="14">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0875392744387961E-4</v>
+        <v>2.4163350843434058E-4</v>
       </c>
       <c r="U3" s="14">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.0952849207851232E-4</v>
+        <v>2.4223968945274877E-4</v>
       </c>
       <c r="V3" s="14">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1030499984753101E-4</v>
+        <v>2.4284739118502426E-4</v>
       </c>
       <c r="W3" s="14">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1108345562563702E-4</v>
+        <v>2.4345661744615068E-4</v>
       </c>
       <c r="X3" s="14">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1186386429976067E-4</v>
+        <v>2.4406737206068225E-4</v>
       </c>
       <c r="Y3" s="14">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1264623076909212E-4</v>
+        <v>2.4467965886276771E-4</v>
       </c>
       <c r="Z3" s="14">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1343055994511199E-4</v>
+        <v>2.4529348169617454E-4</v>
       </c>
       <c r="AA3" s="14">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.142168567516222E-4</v>
+        <v>2.4590884441431297E-4</v>
       </c>
       <c r="AB3" s="14">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1500512612477695E-4</v>
+        <v>2.4652575088026019E-4</v>
       </c>
       <c r="AC3" s="14">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1579537301311368E-4</v>
+        <v>2.4714420496678457E-4</v>
       </c>
       <c r="AD3" s="14">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1658760237758408E-4</v>
+        <v>2.4776421055637006E-4</v>
       </c>
       <c r="AE3" s="14">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1738181919158527E-4</v>
+        <v>2.4838577154124057E-4</v>
       </c>
       <c r="AF3" s="14">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A3,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.1817802844099111E-4</v>
+        <v>2.4900889182338424E-4</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -11429,127 +11429,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8191515243028571E-4</v>
+        <v>2.9887267705941471E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8303357052481187E-4</v>
+        <v>2.9974790970691679E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8415526384690153E-4</v>
+        <v>3.0062570542640924E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8528024198788345E-4</v>
+        <v>3.0150607172371128E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.86408514567174E-4</v>
+        <v>3.0238901612662247E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8754009123235958E-4</v>
+        <v>3.0327454618498724E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8867498165927897E-4</v>
+        <v>3.0416266947075923E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8981319555210617E-4</v>
+        <v>3.050533935780662E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9095474264343329E-4</v>
+        <v>3.0594672612327493E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9209963269435386E-4</v>
+        <v>3.0684267474505626E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9324787549454616E-4</v>
+        <v>3.0774124710445045E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9439948086235718E-4</v>
+        <v>3.0864245088493277E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9555445864488629E-4</v>
+        <v>3.0954629379247918E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9671281871806954E-4</v>
+        <v>3.1045278355563207E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9787457098676426E-4</v>
+        <v>3.1136192792556648E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9903972538483354E-4</v>
+        <v>3.122737346761564E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0020829187523122E-4</v>
+        <v>3.1318821160404114E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0138028045008721E-4</v>
+        <v>3.1410536652869207E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0255570113079277E-4</v>
+        <v>3.1502520729247949E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0373456396808626E-4</v>
+        <v>3.1594774176073965E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0491687904213917E-4</v>
+        <v>3.1687297782184199E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0610265646264215E-4</v>
+        <v>3.178009233872566E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0729190636889162E-4</v>
+        <v>3.1873158639162199E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0848463892987627E-4</v>
+        <v>3.1966497479281271E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.0968086434436425E-4</v>
+        <v>3.2060109657200761E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.1088059284099019E-4</v>
+        <v>3.2153995973375799E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.1208383467834276E-4</v>
+        <v>3.2248157230605596E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.1329060014505233E-4</v>
+        <v>3.2342594234040326E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.14500899559879E-4</v>
+        <v>3.2437307791188E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.1571474327180074E-4</v>
+        <v>3.2532298711921375E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A4,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.1693214166010206E-4</v>
+        <v>3.2627567808484869E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -11559,127 +11559,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5361203080343858E-4</v>
+        <v>2.7674420186003611E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5392433718916497E-4</v>
+        <v>2.7698861939655844E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5423691940057056E-4</v>
+        <v>2.772332528000502E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5454977768126163E-4</v>
+        <v>2.7747810226116281E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5486291227505964E-4</v>
+        <v>2.7772316797071601E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5517632342600144E-4</v>
+        <v>2.7796845011969821E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5549001137833927E-4</v>
+        <v>2.7821394889926632E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5580397637654127E-4</v>
+        <v>2.784596645007462E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5611821866529133E-4</v>
+        <v>2.7870559711563268E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5643273848948956E-4</v>
+        <v>2.7895174693558971E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.567475360942523E-4</v>
+        <v>2.7919811415245044E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5706261172491237E-4</v>
+        <v>2.7944469895821753E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5737796562701935E-4</v>
+        <v>2.7969150154506323E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5769359804633957E-4</v>
+        <v>2.7993852210532938E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5800950922885646E-4</v>
+        <v>2.8018576083152784E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5832569942077075E-4</v>
+        <v>2.8043321791634048E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5864216886850056E-4</v>
+        <v>2.8068089355261927E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5895891781868167E-4</v>
+        <v>2.8092878793338651E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5927594651816765E-4</v>
+        <v>2.8117690125183505E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.595932552140301E-4</v>
+        <v>2.8142523370132833E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.5991084415355886E-4</v>
+        <v>2.8167378547540051E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6022871358426219E-4</v>
+        <v>2.8192255676775678E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6054686375386688E-4</v>
+        <v>2.8217154777227329E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6086529491031853E-4</v>
+        <v>2.8242075868299753E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6118400730178175E-4</v>
+        <v>2.826701896941483E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6150300117664033E-4</v>
+        <v>2.8291984100011603E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6182227678349736E-4</v>
+        <v>2.8316971279546268E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6214183437117557E-4</v>
+        <v>2.8341980527492213E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6246167418871745E-4</v>
+        <v>2.8367011863340028E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6278179648538541E-4</v>
+        <v>2.8392065306597511E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A5,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.6310220151066196E-4</v>
+        <v>2.8417140876789692E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -11689,127 +11689,127 @@
       </c>
       <c r="B6" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A6,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.3612042330321493E-4</v>
+        <v>3.4131163562860293E-4</v>
       </c>
       <c r="C6" s="14">
         <f>IFERROR(B6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.3754548797371836E-4</v>
+        <v>3.4242690363160564E-4</v>
       </c>
       <c r="D6" s="14">
         <f>IFERROR(C6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.3897520917761623E-4</v>
+        <v>3.4354581587813443E-4</v>
       </c>
       <c r="E6" s="14">
         <f>IFERROR(D6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.4040960213057121E-4</v>
+        <v>3.4466838427609918E-4</v>
       </c>
       <c r="F6" s="14">
         <f>IFERROR(E6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.4184868209796454E-4</v>
+        <v>3.4579462077232001E-4</v>
       </c>
       <c r="G6" s="14">
         <f>IFERROR(F6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.4329246439505851E-4</v>
+        <v>3.4692453735265443E-4</v>
       </c>
       <c r="H6" s="14">
         <f>IFERROR(G6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.4474096438715954E-4</v>
+        <v>3.4805814604212478E-4</v>
       </c>
       <c r="I6" s="14">
         <f>IFERROR(H6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.4619419748978154E-4</v>
+        <v>3.4919545890504635E-4</v>
       </c>
       <c r="J6" s="14">
         <f>IFERROR(I6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.476521791688102E-4</v>
+        <v>3.5033648804515575E-4</v>
       </c>
       <c r="K6" s="14">
         <f>IFERROR(J6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.4911492494066738E-4</v>
+        <v>3.5148124560573964E-4</v>
       </c>
       <c r="L6" s="14">
         <f>IFERROR(K6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.5058245037247628E-4</v>
+        <v>3.5262974376976401E-4</v>
       </c>
       <c r="M6" s="14">
         <f>IFERROR(L6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.5205477108222722E-4</v>
+        <v>3.5378199476000392E-4</v>
       </c>
       <c r="N6" s="14">
         <f>IFERROR(M6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.5353190273894378E-4</v>
+        <v>3.5493801083917337E-4</v>
       </c>
       <c r="O6" s="14">
         <f>IFERROR(N6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.5501386106284948E-4</v>
+        <v>3.560978043100561E-4</v>
       </c>
       <c r="P6" s="14">
         <f>IFERROR(O6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.5650066182553517E-4</v>
+        <v>3.5726138751563622E-4</v>
       </c>
       <c r="Q6" s="14">
         <f>IFERROR(P6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.5799232085012691E-4</v>
+        <v>3.5842877283922972E-4</v>
       </c>
       <c r="R6" s="14">
         <f>IFERROR(Q6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.5948885401145425E-4</v>
+        <v>3.5959997270461634E-4</v>
       </c>
       <c r="S6" s="14">
         <f>IFERROR(R6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.6099027723621932E-4</v>
+        <v>3.6077499957617163E-4</v>
       </c>
       <c r="T6" s="14">
         <f>IFERROR(S6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.6249660650316628E-4</v>
+        <v>3.6195386595899964E-4</v>
       </c>
       <c r="U6" s="14">
         <f>IFERROR(T6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.6400785784325119E-4</v>
+        <v>3.631365843990661E-4</v>
       </c>
       <c r="V6" s="14">
         <f>IFERROR(U6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.6552404733981293E-4</v>
+        <v>3.6432316748333178E-4</v>
       </c>
       <c r="W6" s="14">
         <f>IFERROR(V6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.6704519112874415E-4</v>
+        <v>3.6551362783988662E-4</v>
       </c>
       <c r="X6" s="14">
         <f>IFERROR(W6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.6857130539866305E-4</v>
+        <v>3.6670797813808401E-4</v>
       </c>
       <c r="Y6" s="14">
         <f>IFERROR(X6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.7010240639108563E-4</v>
+        <v>3.6790623108867558E-4</v>
       </c>
       <c r="Z6" s="14">
         <f>IFERROR(Y6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.7163851040059866E-4</v>
+        <v>3.6910839944394661E-4</v>
       </c>
       <c r="AA6" s="14">
         <f>IFERROR(Z6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.7317963377503295E-4</v>
+        <v>3.7031449599785168E-4</v>
       </c>
       <c r="AB6" s="14">
         <f>IFERROR(AA6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.747257929156374E-4</v>
+        <v>3.7152453358615083E-4</v>
       </c>
       <c r="AC6" s="14">
         <f>IFERROR(AB6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.7627700427725357E-4</v>
+        <v>3.7273852508654608E-4</v>
       </c>
       <c r="AD6" s="14">
         <f>IFERROR(AC6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.7783328436849077E-4</v>
+        <v>3.7395648341881864E-4</v>
       </c>
       <c r="AE6" s="14">
         <f>IFERROR(AD6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.7939464975190171E-4</v>
+        <v>3.751784215449663E-4</v>
       </c>
       <c r="AF6" s="14">
         <f>IFERROR(AE6*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A6,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>4.8096111704415878E-4</v>
+        <v>3.7640435246934142E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -11819,127 +11819,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.728891997845125E-4</v>
+        <v>2.9181761617105628E-4</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7368007341019642E-4</v>
+        <v>2.9243654226565223E-4</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7447262442715944E-4</v>
+        <v>2.9305678106205009E-4</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7526685639303892E-4</v>
+        <v>2.9367833534440455E-4</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7606277287301762E-4</v>
+        <v>2.9430120790277541E-4</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7686037743983987E-4</v>
+        <v>2.9492540153313993E-4</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7765967367382758E-4</v>
+        <v>2.9555091903740548E-4</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7846066516289623E-4</v>
+        <v>2.9617776322342213E-4</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.7926335550257108E-4</v>
+        <v>2.9680593690499513E-4</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8006774829600328E-4</v>
+        <v>2.9743544290189775E-4</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8087384715398596E-4</v>
+        <v>2.9806628403988367E-4</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8168165569497058E-4</v>
+        <v>2.9869846315069989E-4</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8249117754508301E-4</v>
+        <v>2.9933198307209938E-4</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8330241633814004E-4</v>
+        <v>2.9996684664785375E-4</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8411537571566537E-4</v>
+        <v>3.0060305672776607E-4</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8493005932690631E-4</v>
+        <v>3.012406161676837E-4</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8574647082884983E-4</v>
+        <v>3.0187952782951102E-4</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.865646138862392E-4</v>
+        <v>3.0251979458122233E-4</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8738449217159038E-4</v>
+        <v>3.0316141929687476E-4</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.882061093652085E-4</v>
+        <v>3.0380440485662107E-4</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8902946915520437E-4</v>
+        <v>3.0444875414672263E-4</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.8985457523751102E-4</v>
+        <v>3.0509447005956246E-4</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9068143131590035E-4</v>
+        <v>3.0574155549365802E-4</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9151004110199965E-4</v>
+        <v>3.0639001335367442E-4</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.923404083153084E-4</v>
+        <v>3.0703984655043739E-4</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9317253668321486E-4</v>
+        <v>3.076910580009463E-4</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9400642994101283E-4</v>
+        <v>3.0834365062838725E-4</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9484209183191849E-4</v>
+        <v>3.0899762736214626E-4</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9567952610708706E-4</v>
+        <v>3.0965299113782236E-4</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9651873652562971E-4</v>
+        <v>3.1030974489724088E-4</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A7,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>3.9735972685463054E-4</v>
+        <v>3.1096789158846646E-4</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -11949,127 +11949,127 @@
       </c>
       <c r="B8" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$2:$H$2,,MATCH($A8,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9081742078368943E-3</v>
+        <v>1.4933406927677131E-3</v>
       </c>
       <c r="C8" s="14">
         <f>IFERROR(B8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9069492026049855E-3</v>
+        <v>1.4923820013892481E-3</v>
       </c>
       <c r="D8" s="14">
         <f>IFERROR(C8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9057249837990812E-3</v>
+        <v>1.4914239254692403E-3</v>
       </c>
       <c r="E8" s="14">
         <f>IFERROR(D8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9045015509143136E-3</v>
+        <v>1.4904664646125793E-3</v>
       </c>
       <c r="F8" s="14">
         <f>IFERROR(E8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9032789034461386E-3</v>
+        <v>1.4895096184244082E-3</v>
       </c>
       <c r="G8" s="14">
         <f>IFERROR(F8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9020570408903367E-3</v>
+        <v>1.4885533865101237E-3</v>
       </c>
       <c r="H8" s="14">
         <f>IFERROR(G8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.9008359627430112E-3</v>
+        <v>1.4875977684753754E-3</v>
       </c>
       <c r="I8" s="14">
         <f>IFERROR(H8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8996156685005896E-3</v>
+        <v>1.4866427639260665E-3</v>
       </c>
       <c r="J8" s="14">
         <f>IFERROR(I8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8983961576598226E-3</v>
+        <v>1.485688372468353E-3</v>
       </c>
       <c r="K8" s="14">
         <f>IFERROR(J8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8971774297177836E-3</v>
+        <v>1.4847345937086438E-3</v>
       </c>
       <c r="L8" s="14">
         <f>IFERROR(K8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8959594841718693E-3</v>
+        <v>1.4837814272536005E-3</v>
       </c>
       <c r="M8" s="14">
         <f>IFERROR(L8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8947423205197987E-3</v>
+        <v>1.4828288727101371E-3</v>
       </c>
       <c r="N8" s="14">
         <f>IFERROR(M8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8935259382596135E-3</v>
+        <v>1.48187692968542E-3</v>
       </c>
       <c r="O8" s="14">
         <f>IFERROR(N8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8923103368896775E-3</v>
+        <v>1.4809255977868679E-3</v>
       </c>
       <c r="P8" s="14">
         <f>IFERROR(O8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8910955159086766E-3</v>
+        <v>1.4799748766221514E-3</v>
       </c>
       <c r="Q8" s="14">
         <f>IFERROR(P8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8898814748156186E-3</v>
+        <v>1.4790247657991932E-3</v>
       </c>
       <c r="R8" s="14">
         <f>IFERROR(Q8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8886682131098328E-3</v>
+        <v>1.4780752649261673E-3</v>
       </c>
       <c r="S8" s="14">
         <f>IFERROR(R8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.88745573029097E-3</v>
+        <v>1.4771263736114994E-3</v>
       </c>
       <c r="T8" s="14">
         <f>IFERROR(S8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8862440258590023E-3</v>
+        <v>1.4761780914638669E-3</v>
       </c>
       <c r="U8" s="14">
         <f>IFERROR(T8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8850330993142224E-3</v>
+        <v>1.4752304180921981E-3</v>
       </c>
       <c r="V8" s="14">
         <f>IFERROR(U8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8838229501572442E-3</v>
+        <v>1.4742833531056724E-3</v>
       </c>
       <c r="W8" s="14">
         <f>IFERROR(V8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8826135778890023E-3</v>
+        <v>1.4733368961137199E-3</v>
       </c>
       <c r="X8" s="14">
         <f>IFERROR(W8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8814049820107513E-3</v>
+        <v>1.4723910467260219E-3</v>
       </c>
       <c r="Y8" s="14">
         <f>IFERROR(X8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8801971620240662E-3</v>
+        <v>1.4714458045525099E-3</v>
       </c>
       <c r="Z8" s="14">
         <f>IFERROR(Y8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8789901174308418E-3</v>
+        <v>1.4705011692033663E-3</v>
       </c>
       <c r="AA8" s="14">
         <f>IFERROR(Z8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8777838477332931E-3</v>
+        <v>1.469557140289023E-3</v>
       </c>
       <c r="AB8" s="14">
         <f>IFERROR(AA8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8765783524339543E-3</v>
+        <v>1.4686137174201627E-3</v>
       </c>
       <c r="AC8" s="14">
         <f>IFERROR(AB8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8753736310356788E-3</v>
+        <v>1.4676709002077175E-3</v>
       </c>
       <c r="AD8" s="14">
         <f>IFERROR(AC8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8741696830416397E-3</v>
+        <v>1.4667286882628695E-3</v>
       </c>
       <c r="AE8" s="14">
         <f>IFERROR(AD8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8729665079553286E-3</v>
+        <v>1.4657870811970505E-3</v>
       </c>
       <c r="AF8" s="14">
         <f>IFERROR(AE8*(1+INDEX(CAGR!$C$2:$C$8,MATCH($A8,CAGR!$B$2:$B$8,0))),0)</f>
-        <v>1.8717641052805559E-3</v>
+        <v>1.4648460786219418E-3</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -12196,127 +12196,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.8944789534532561E-4</v>
+        <v>1.4791119101827561E-4</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.9192783449611467E-4</v>
+        <v>1.4984740019482749E-4</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.944402369169781E-4</v>
+        <v>1.5180895502608986E-4</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.9698552756346516E-4</v>
+        <v>1.5379618729553964E-4</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.9956413695394171E-4</v>
+        <v>1.5580943312981546E-4</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.0217650124240949E-4</v>
+        <v>1.5784903305557106E-4</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.0482306229227854E-4</v>
+        <v>1.5991533205707308E-4</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.0750426775110532E-4</v>
+        <v>1.6200867963455282E-4</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.1022057112630923E-4</v>
+        <v>1.6412942986332164E-4</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.1297243186188026E-4</v>
+        <v>1.6627794145366052E-4</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.157603154160908E-4</v>
+        <v>1.6845457781149335E-4</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.1858469334022466E-4</v>
+        <v>1.7065970709985456E-4</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.2144604335833676E-4</v>
+        <v>1.7289370230116132E-4</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.2434484944805678E-4</v>
+        <v>1.7515694128030103E-4</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.2728160192245076E-4</v>
+        <v>1.7744980684854445E-4</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.3025679751295406E-4</v>
+        <v>1.7977268682829568E-4</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.332709394533901E-4</v>
+        <v>1.821259741186896E-4</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.3632453756508896E-4</v>
+        <v>1.8451006676204807E-4</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.3941810834312002E-4</v>
+        <v>1.8692536801120601E-4</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.4255217504365364E-4</v>
+        <v>1.893722863977189E-4</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.4572726777246626E-4</v>
+        <v>1.9185123580096297E-4</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.4894392357460422E-4</v>
+        <v>1.9436263551814021E-4</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.5220268652522115E-4</v>
+        <v>1.9690691033519942E-4</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.555041078216046E-4</v>
+        <v>1.9948449059868596E-4</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.5884874587640719E-4</v>
+        <v>2.020958122885318E-4</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.6223716641209826E-4</v>
+        <v>2.0474131709179863E-4</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.6566994255665204E-4</v>
+        <v>2.0742145247738605E-4</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.6914765494048814E-4</v>
+        <v>2.1013667177171799E-4</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.7267089179468132E-4</v>
+        <v>2.128874342354196E-4</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.7624024905045661E-4</v>
+        <v>2.1567420514099819E-4</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A2,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>2.798563304399871E-4</v>
+        <v>2.1849745585154071E-4</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -12326,127 +12326,127 @@
       </c>
       <c r="B3" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8743154451385681E-5</v>
+        <v>7.7797636840485688E-5</v>
       </c>
       <c r="C3" s="21">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8486975262729385E-5</v>
+        <v>7.7595798691847392E-5</v>
       </c>
       <c r="D3" s="21">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.8231460705227171E-5</v>
+        <v>7.7394484191997163E-5</v>
       </c>
       <c r="E3" s="21">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.797660905456031E-5</v>
+        <v>7.7193691982380851E-5</v>
       </c>
       <c r="F3" s="21">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7722418590883659E-5</v>
+        <v>7.699342070796895E-5</v>
       </c>
       <c r="G3" s="21">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7468887598814037E-5</v>
+        <v>7.6793669017247425E-5</v>
       </c>
       <c r="H3" s="21">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.7216014367418644E-5</v>
+        <v>7.6594435562208634E-5</v>
       </c>
       <c r="I3" s="21">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6963797190203525E-5</v>
+        <v>7.6395718998342177E-5</v>
       </c>
       <c r="J3" s="21">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6712234365102065E-5</v>
+        <v>7.619751798462587E-5</v>
       </c>
       <c r="K3" s="21">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.6461324194463481E-5</v>
+        <v>7.5999831183516683E-5</v>
       </c>
       <c r="L3" s="21">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.621106498504136E-5</v>
+        <v>7.580265726094168E-5</v>
       </c>
       <c r="M3" s="21">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5961455047982271E-5</v>
+        <v>7.5605994886289066E-5</v>
       </c>
       <c r="N3" s="21">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5712492698814332E-5</v>
+        <v>7.5409842732399173E-5</v>
       </c>
       <c r="O3" s="21">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5464176257435845E-5</v>
+        <v>7.5214199475555514E-5</v>
       </c>
       <c r="P3" s="21">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.5216504048103987E-5</v>
+        <v>7.5019063795475868E-5</v>
       </c>
       <c r="Q3" s="21">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.4969474399423463E-5</v>
+        <v>7.4824434375303332E-5</v>
       </c>
       <c r="R3" s="21">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.4723085644335259E-5</v>
+        <v>7.4630309901597475E-5</v>
       </c>
       <c r="S3" s="21">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.4477336120105365E-5</v>
+        <v>7.4436689064325432E-5</v>
       </c>
       <c r="T3" s="21">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.4232224168313579E-5</v>
+        <v>7.4243570556853107E-5</v>
       </c>
       <c r="U3" s="21">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.3987748134842291E-5</v>
+        <v>7.4050953075936339E-5</v>
       </c>
       <c r="V3" s="21">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.3743906369865351E-5</v>
+        <v>7.3858835321712079E-5</v>
       </c>
       <c r="W3" s="21">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.3500697227836903E-5</v>
+        <v>7.3667215997689662E-5</v>
       </c>
       <c r="X3" s="21">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.3258119067480289E-5</v>
+        <v>7.3476093810742024E-5</v>
       </c>
       <c r="Y3" s="21">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.3016170251776996E-5</v>
+        <v>7.3285467471097002E-5</v>
       </c>
       <c r="Z3" s="21">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.2774849147955581E-5</v>
+        <v>7.3095335692328621E-5</v>
       </c>
       <c r="AA3" s="21">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.2534154127480668E-5</v>
+        <v>7.2905697191348389E-5</v>
       </c>
       <c r="AB3" s="21">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.2294083566041939E-5</v>
+        <v>7.2716550688396671E-5</v>
       </c>
       <c r="AC3" s="21">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.2054635843543206E-5</v>
+        <v>7.2527894907034035E-5</v>
       </c>
       <c r="AD3" s="21">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.1815809344091435E-5</v>
+        <v>7.2339728574132638E-5</v>
       </c>
       <c r="AE3" s="21">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.1577602455985877E-5</v>
+        <v>7.2152050419867659E-5</v>
       </c>
       <c r="AF3" s="21">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A3,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>9.1340013571707183E-5</v>
+        <v>7.1964859177708692E-5</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -12456,127 +12456,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4163159527370473E-4</v>
+        <v>1.1071202165761425E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4126414633644014E-4</v>
+        <v>1.1042479044609052E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4089765070850766E-4</v>
+        <v>1.1013830442707289E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4053210591664206E-4</v>
+        <v>1.0985256166723428E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.4016750949399475E-4</v>
+        <v>1.0956756023826349E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.398038589801171E-4</v>
+        <v>1.0928329821685208E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3944115192094392E-4</v>
+        <v>1.0899977368468148E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3907938586877678E-4</v>
+        <v>1.0871698472840999E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3871855838226761E-4</v>
+        <v>1.0843492943965986E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3835866702640215E-4</v>
+        <v>1.0815360591500447E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3799970937248356E-4</v>
+        <v>1.0787301225595542E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3764168299811597E-4</v>
+        <v>1.0759314656894978E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3728458548718821E-4</v>
+        <v>1.0731400696533724E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3692841442985746E-4</v>
+        <v>1.0703559156136742E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3657316742253297E-4</v>
+        <v>1.0675789847817715E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.362188420678599E-4</v>
+        <v>1.0648092584177777E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3586543597470308E-4</v>
+        <v>1.062046717830425E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3551294675813089E-4</v>
+        <v>1.0592913443769383E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3516137203939922E-4</v>
+        <v>1.0565431194629092E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3481070944593537E-4</v>
+        <v>1.0538020245421706E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3446095661132199E-4</v>
+        <v>1.0510680411166715E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3411211117528117E-4</v>
+        <v>1.0483411507363525E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3376417078365857E-4</v>
+        <v>1.0456213349990208E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3341713308840739E-4</v>
+        <v>1.0429085755502263E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3307099574757264E-4</v>
+        <v>1.0402028540831377E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.327257564252753E-4</v>
+        <v>1.037504152338419E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3238141279169651E-4</v>
+        <v>1.034812452104106E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3203796252306196E-4</v>
+        <v>1.0321277352154838E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3169540330162607E-4</v>
+        <v>1.029449983554964E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3135373281565648E-4</v>
+        <v>1.0267791790519623E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A4,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.3101294875941834E-4</v>
+        <v>1.0241153036827769E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -12586,127 +12586,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0971461605709522E-4</v>
+        <v>8.5776881644638074E-5</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0942997251414377E-4</v>
+        <v>8.5554342147421494E-5</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0914606745025242E-4</v>
+        <v>8.5332380006560983E-5</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0886289894951146E-4</v>
+        <v>8.5110993724163506E-5</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0858046510098185E-4</v>
+        <v>8.4890181806222172E-5</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0829876399868227E-4</v>
+        <v>8.466994276260614E-5</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0801779374157627E-4</v>
+        <v>8.445027510705055E-5</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0773755243355947E-4</v>
+        <v>8.4231177357146507E-5</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0745803818344673E-4</v>
+        <v>8.4012648034331093E-5</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0717924910495941E-4</v>
+        <v>8.3794685663877365E-5</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0690118331671261E-4</v>
+        <v>8.3577288774884406E-5</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.066238389422025E-4</v>
+        <v>8.3360455900267422E-5</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0634721410979367E-4</v>
+        <v>8.3144185576747791E-5</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0607130695270647E-4</v>
+        <v>8.2928476344843252E-5</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.057961156090044E-4</v>
+        <v>8.2713326748857998E-5</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0552163822158159E-4</v>
+        <v>8.249873533687289E-5</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0524787293815025E-4</v>
+        <v>8.2284700660735662E-5</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0497481791122814E-4</v>
+        <v>8.2071221276051106E-5</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0470247129812615E-4</v>
+        <v>8.1858295742171368E-5</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0443083126093583E-4</v>
+        <v>8.1645922622186205E-5</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0415989596651701E-4</v>
+        <v>8.1434100482913311E-5</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.038896635864854E-4</v>
+        <v>8.1222827894888593E-5</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0362013229720028E-4</v>
+        <v>8.1012103432356582E-5</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0335130027975219E-4</v>
+        <v>8.0801925673260795E-5</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0308316571995062E-4</v>
+        <v>8.0592293199234114E-5</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0281572680831183E-4</v>
+        <v>8.0383204595589242E-5</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0254898174004658E-4</v>
+        <v>8.0174658451309138E-5</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0228292871504797E-4</v>
+        <v>7.9966653359037513E-5</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0201756593787933E-4</v>
+        <v>7.9759187915069308E-5</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0175289161776204E-4</v>
+        <v>7.9552260719341244E-5</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A5,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>1.0148890396856348E-4</v>
+        <v>7.9345870375422377E-5</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -12716,127 +12716,127 @@
       </c>
       <c r="B6" s="15">
         <f>B5*Calibration!$C$21</f>
-        <v>1.6842939489187289E-4</v>
+        <v>1.3168116327910061E-4</v>
       </c>
       <c r="C6" s="15">
         <f>B6*(1+CAGR!$C$13)</f>
-        <v>1.6968563035456036E-4</v>
+        <v>1.3266331100447444E-4</v>
       </c>
       <c r="D6" s="15">
         <f>C6*(1+CAGR!$C$13)</f>
-        <v>1.7095123548540301E-4</v>
+        <v>1.3365278410676959E-4</v>
       </c>
       <c r="E6" s="15">
         <f>D6*(1+CAGR!$C$13)</f>
-        <v>1.7222628016833896E-4</v>
+        <v>1.3464963722251949E-4</v>
       </c>
       <c r="F6" s="15">
         <f>E6*(1+CAGR!$C$13)</f>
-        <v>1.7351083480853766E-4</v>
+        <v>1.3565392539576575E-4</v>
       </c>
       <c r="G6" s="15">
         <f>F6*(1+CAGR!$C$13)</f>
-        <v>1.7480497033628756E-4</v>
+        <v>1.366657040810975E-4</v>
       </c>
       <c r="H6" s="15">
         <f>G6*(1+CAGR!$C$13)</f>
-        <v>1.7610875821091272E-4</v>
+        <v>1.3768502914671352E-4</v>
       </c>
       <c r="I6" s="15">
         <f>H6*(1+CAGR!$C$13)</f>
-        <v>1.7742227042471856E-4</v>
+        <v>1.3871195687750718E-4</v>
       </c>
       <c r="J6" s="15">
         <f>I6*(1+CAGR!$C$13)</f>
-        <v>1.7874557950696719E-4</v>
+        <v>1.397465439781743E-4</v>
       </c>
       <c r="K6" s="15">
         <f>J6*(1+CAGR!$C$13)</f>
-        <v>1.8007875852788232E-4</v>
+        <v>1.407888475763443E-4</v>
       </c>
       <c r="L6" s="15">
         <f>K6*(1+CAGR!$C$13)</f>
-        <v>1.8142188110268397E-4</v>
+        <v>1.4183892522573468E-4</v>
       </c>
       <c r="M6" s="15">
         <f>L6*(1+CAGR!$C$13)</f>
-        <v>1.8277502139565346E-4</v>
+        <v>1.4289683490932901E-4</v>
       </c>
       <c r="N6" s="15">
         <f>M6*(1+CAGR!$C$13)</f>
-        <v>1.8413825412422845E-4</v>
+        <v>1.4396263504257853E-4</v>
       </c>
       <c r="O6" s="15">
         <f>N6*(1+CAGR!$C$13)</f>
-        <v>1.8551165456312876E-4</v>
+        <v>1.4503638447662786E-4</v>
       </c>
       <c r="P6" s="15">
         <f>O6*(1+CAGR!$C$13)</f>
-        <v>1.8689529854851289E-4</v>
+        <v>1.4611814250156454E-4</v>
       </c>
       <c r="Q6" s="15">
         <f>P6*(1+CAGR!$C$13)</f>
-        <v>1.8828926248216549E-4</v>
+        <v>1.4720796884969294E-4</v>
       </c>
       <c r="R6" s="15">
         <f>Q6*(1+CAGR!$C$13)</f>
-        <v>1.8969362333571611E-4</v>
+        <v>1.4830592369883251E-4</v>
       </c>
       <c r="S6" s="15">
         <f>R6*(1+CAGR!$C$13)</f>
-        <v>1.9110845865488938E-4</v>
+        <v>1.494120676756407E-4</v>
       </c>
       <c r="T6" s="15">
         <f>S6*(1+CAGR!$C$13)</f>
-        <v>1.9253384656378698E-4</v>
+        <v>1.5052646185896064E-4</v>
       </c>
       <c r="U6" s="15">
         <f>T6*(1+CAGR!$C$13)</f>
-        <v>1.9396986576920139E-4</v>
+        <v>1.5164916778319371E-4</v>
       </c>
       <c r="V6" s="15">
         <f>U6*(1+CAGR!$C$13)</f>
-        <v>1.9541659556496197E-4</v>
+        <v>1.5278024744169743E-4</v>
       </c>
       <c r="W6" s="15">
         <f>V6*(1+CAGR!$C$13)</f>
-        <v>1.968741158363134E-4</v>
+        <v>1.5391976329020855E-4</v>
       </c>
       <c r="X6" s="15">
         <f>W6*(1+CAGR!$C$13)</f>
-        <v>1.983425070643267E-4</v>
+        <v>1.5506777825029168E-4</v>
       </c>
       <c r="Y6" s="15">
         <f>X6*(1+CAGR!$C$13)</f>
-        <v>1.9982185033034331E-4</v>
+        <v>1.5622435571281378E-4</v>
       </c>
       <c r="Z6" s="15">
         <f>Y6*(1+CAGR!$C$13)</f>
-        <v>2.0131222732045216E-4</v>
+        <v>1.5738955954144434E-4</v>
       </c>
       <c r="AA6" s="15">
         <f>Z6*(1+CAGR!$C$13)</f>
-        <v>2.0281372033000019E-4</v>
+        <v>1.5856345407618189E-4</v>
       </c>
       <c r="AB6" s="15">
         <f>AA6*(1+CAGR!$C$13)</f>
-        <v>2.0432641226813658E-4</v>
+        <v>1.597461041369067E-4</v>
       </c>
       <c r="AC6" s="15">
         <f>AB6*(1+CAGR!$C$13)</f>
-        <v>2.0585038666239071E-4</v>
+        <v>1.6093757502695993E-4</v>
       </c>
       <c r="AD6" s="15">
         <f>AC6*(1+CAGR!$C$13)</f>
-        <v>2.0738572766328448E-4</v>
+        <v>1.6213793253674961E-4</v>
       </c>
       <c r="AE6" s="15">
         <f>AD6*(1+CAGR!$C$13)</f>
-        <v>2.0893252004897887E-4</v>
+        <v>1.633472429473834E-4</v>
       </c>
       <c r="AF6" s="15">
         <f>AE6*(1+CAGR!$C$13)</f>
-        <v>2.1049084922995518E-4</v>
+        <v>1.6456557303432852E-4</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -12846,127 +12846,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$2:$H$2,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.7797636840485688E-5</v>
+        <v>6.0841741631661887E-5</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.7595798691847392E-5</v>
+        <v>6.0683893848752449E-5</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.7394484191997163E-5</v>
+        <v>6.052645558604906E-5</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.7193691982380851E-5</v>
+        <v>6.0369425781092713E-5</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.699342070796895E-5</v>
+        <v>6.0212803374180838E-5</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.6793669017247425E-5</v>
+        <v>6.0056587308360164E-5</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.6594435562208634E-5</v>
+        <v>5.9900776529419568E-5</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.6395718998342177E-5</v>
+        <v>5.974536998588298E-5</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.619751798462587E-5</v>
+        <v>5.9590366629002281E-5</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.5999831183516683E-5</v>
+        <v>5.9435765412750219E-5</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.580265726094168E-5</v>
+        <v>5.9281565293813357E-5</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.5605994886289066E-5</v>
+        <v>5.9127765231585026E-5</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.5409842732399173E-5</v>
+        <v>5.897436418815831E-5</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.5214199475555514E-5</v>
+        <v>5.8821361128319039E-5</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.5019063795475868E-5</v>
+        <v>5.86687550195388E-5</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.4824434375303332E-5</v>
+        <v>5.8516544831967973E-5</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.4630309901597475E-5</v>
+        <v>5.8364729538428771E-5</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.4436689064325432E-5</v>
+        <v>5.8213308114408329E-5</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.4243570556853107E-5</v>
+        <v>5.8062279538051771E-5</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.4050953075936339E-5</v>
+        <v>5.791164279015532E-5</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3858835321712079E-5</v>
+        <v>5.7761396854159423E-5</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3667215997689662E-5</v>
+        <v>5.7611540716141893E-5</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3476093810742024E-5</v>
+        <v>5.7462073364811052E-5</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3285467471097002E-5</v>
+        <v>5.7312993791498925E-5</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.3095335692328621E-5</v>
+        <v>5.7164300990154421E-5</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.2905697191348389E-5</v>
+        <v>5.7015993957336544E-5</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.2716550688396671E-5</v>
+        <v>5.6868071692207629E-5</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.2527894907034035E-5</v>
+        <v>5.6720533196526589E-5</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.2339728574132638E-5</v>
+        <v>5.6573377474642162E-5</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.2152050419867659E-5</v>
+        <v>5.6426603533486213E-5</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$9:$C$15,MATCH($A7,CAGR!$B$9:$B$15,0))),0)</f>
-        <v>7.1964859177708692E-5</v>
+        <v>5.6280210382567016E-5</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -12976,127 +12976,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$D$21</f>
-        <v>3.291438481712856E-4</v>
+        <v>2.5733064493391417E-4</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$15)</f>
-        <v>3.2828991754243125E-4</v>
+        <v>2.5666302644226441E-4</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$15)</f>
-        <v>3.2743820235075718E-4</v>
+        <v>2.5599714001968286E-4</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$15)</f>
-        <v>3.2658869684853433E-4</v>
+        <v>2.5533298117249041E-4</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$15)</f>
-        <v>3.2574139530294549E-4</v>
+        <v>2.5467054541866642E-4</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$15)</f>
-        <v>3.2489629199604673E-4</v>
+        <v>2.540098282878183E-4</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$15)</f>
-        <v>3.2405338122472874E-4</v>
+        <v>2.5335082532115149E-4</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$15)</f>
-        <v>3.2321265730067837E-4</v>
+        <v>2.5269353207143939E-4</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$15)</f>
-        <v>3.2237411455034019E-4</v>
+        <v>2.5203794410299314E-4</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$15)</f>
-        <v>3.2153774731487821E-4</v>
+        <v>2.5138405699163196E-4</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$15)</f>
-        <v>3.2070354995013782E-4</v>
+        <v>2.507318663246531E-4</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$15)</f>
-        <v>3.198715168266075E-4</v>
+        <v>2.5008136770080213E-4</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$15)</f>
-        <v>3.1904164232938103E-4</v>
+        <v>2.4943255673024324E-4</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$15)</f>
-        <v>3.1821392085811944E-4</v>
+        <v>2.4878542903452959E-4</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$15)</f>
-        <v>3.1738834682701323E-4</v>
+        <v>2.4813998024657383E-4</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$15)</f>
-        <v>3.165649146647448E-4</v>
+        <v>2.4749620601061855E-4</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$15)</f>
-        <v>3.1574361881445075E-4</v>
+        <v>2.4685410198220688E-4</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$15)</f>
-        <v>3.1492445373368442E-4</v>
+        <v>2.4621366382815321E-4</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$15)</f>
-        <v>3.1410741389437845E-4</v>
+        <v>2.4557488722651402E-4</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$15)</f>
-        <v>3.1329249378280751E-4</v>
+        <v>2.4493776786655856E-4</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$15)</f>
-        <v>3.1247968789955102E-4</v>
+        <v>2.4430230144873989E-4</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$15)</f>
-        <v>3.1166899075945616E-4</v>
+        <v>2.4366848368466575E-4</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$15)</f>
-        <v>3.1086039689160079E-4</v>
+        <v>2.4303631029706975E-4</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$15)</f>
-        <v>3.1005390083925651E-4</v>
+        <v>2.4240577701978237E-4</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$15)</f>
-        <v>3.092494971598518E-4</v>
+        <v>2.4177687959770232E-4</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$15)</f>
-        <v>3.0844718042493541E-4</v>
+        <v>2.4114961378676769E-4</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$15)</f>
-        <v>3.0764694522013964E-4</v>
+        <v>2.4052397535392737E-4</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$15)</f>
-        <v>3.0684878614514386E-4</v>
+        <v>2.3989996007711247E-4</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$15)</f>
-        <v>3.0605269781363794E-4</v>
+        <v>2.3927756374520786E-4</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$15)</f>
-        <v>3.0525867485328608E-4</v>
+        <v>2.3865678215802367E-4</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$15)</f>
-        <v>3.0446671190569041E-4</v>
+        <v>2.3803761112626708E-4</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -13223,127 +13223,127 @@
       </c>
       <c r="B2" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A2,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6363466800619893E-3</v>
+        <v>2.063236671112524E-3</v>
       </c>
       <c r="C2" s="14">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.6784553614682158E-3</v>
+        <v>2.0961914324519842E-3</v>
       </c>
       <c r="D2" s="14">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7212366179432605E-3</v>
+        <v>2.1296725591426163E-3</v>
       </c>
       <c r="E2" s="14">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.7647011920990524E-3</v>
+        <v>2.1636884584819291E-3</v>
       </c>
       <c r="F2" s="14">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8088599981323987E-3</v>
+        <v>2.1982476720518239E-3</v>
       </c>
       <c r="G2" s="14">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8537241245655998E-3</v>
+        <v>2.2333588778634334E-3</v>
       </c>
       <c r="H2" s="14">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.8993048370308397E-3</v>
+        <v>2.2690308925362181E-3</v>
       </c>
       <c r="I2" s="14">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9456135810990488E-3</v>
+        <v>2.3052726735118701E-3</v>
       </c>
       <c r="J2" s="14">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.9926619851539499E-3</v>
+        <v>2.3420933213035744E-3</v>
       </c>
       <c r="K2" s="14">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0404618633120117E-3</v>
+        <v>2.3795020817812002E-3</v>
       </c>
       <c r="L2" s="14">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.0890252183890369E-3</v>
+        <v>2.4175083484929902E-3</v>
       </c>
       <c r="M2" s="14">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1383642449141391E-3</v>
+        <v>2.4561216650243315E-3</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.1884913321918546E-3</v>
+        <v>2.495351727394205E-3</v>
       </c>
       <c r="O2" s="14">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2394190674131665E-3</v>
+        <v>2.5352083864899084E-3</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.2911602388162194E-3</v>
+        <v>2.5757016505406692E-3</v>
       </c>
       <c r="Q2" s="14">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.343727838897516E-3</v>
+        <v>2.6168416876307678E-3</v>
       </c>
       <c r="R2" s="14">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.3971350676744064E-3</v>
+        <v>2.6586388282527993E-3</v>
       </c>
       <c r="S2" s="14">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.451395335999685E-3</v>
+        <v>2.7011035679017168E-3</v>
       </c>
       <c r="T2" s="14">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.5065222689291318E-3</v>
+        <v>2.7442465697103107E-3</v>
       </c>
       <c r="U2" s="14">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.5625297091428382E-3</v>
+        <v>2.7880786671267799E-3</v>
       </c>
       <c r="V2" s="14">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.6194317204211826E-3</v>
+        <v>2.8326108666350699E-3</v>
       </c>
       <c r="W2" s="14">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.6772425911763226E-3</v>
+        <v>2.877854350518664E-3</v>
       </c>
       <c r="X2" s="14">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.7359768380400963E-3</v>
+        <v>2.9238204796685164E-3</v>
       </c>
       <c r="Y2" s="14">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.7956492095092284E-3</v>
+        <v>2.9705207964358343E-3</v>
       </c>
       <c r="Z2" s="14">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.8562746896487607E-3</v>
+        <v>3.0179670275304283E-3</v>
       </c>
       <c r="AA2" s="14">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.9178685018546339E-3</v>
+        <v>3.0661710869653532E-3</v>
       </c>
       <c r="AB2" s="14">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>3.9804461126763668E-3</v>
+        <v>3.1151450790485838E-3</v>
       </c>
       <c r="AC2" s="14">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>4.0440232357007947E-3</v>
+        <v>3.1649013014224741E-3</v>
       </c>
       <c r="AD2" s="14">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>4.1086158354978362E-3</v>
+        <v>3.2154522481517627E-3</v>
       </c>
       <c r="AE2" s="14">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>4.1742401316292874E-3</v>
+        <v>3.2668106128609042E-3</v>
       </c>
       <c r="AF2" s="14">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A2,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>4.2409126027216438E-3</v>
+        <v>3.3189892919215066E-3</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -13353,127 +13353,127 @@
       </c>
       <c r="B3" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A3,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0273724279481005E-3</v>
+        <v>1.5866392914376439E-3</v>
       </c>
       <c r="C3" s="14">
         <f>IFERROR(B3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0423547635300254E-3</v>
+        <v>1.5983645975452372E-3</v>
       </c>
       <c r="D3" s="14">
         <f>IFERROR(C3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0574478189660803E-3</v>
+        <v>1.610176553973454E-3</v>
       </c>
       <c r="E3" s="14">
         <f>IFERROR(D3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0726524124788999E-3</v>
+        <v>1.6220758010704432E-3</v>
       </c>
       <c r="F3" s="14">
         <f>IFERROR(E3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0879693683378063E-3</v>
+        <v>1.6340629839165439E-3</v>
       </c>
       <c r="G3" s="14">
         <f>IFERROR(F3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1033995169034933E-3</v>
+        <v>1.6461387523592553E-3</v>
       </c>
       <c r="H3" s="14">
         <f>IFERROR(G3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.118943694673042E-3</v>
+        <v>1.6583037610484674E-3</v>
       </c>
       <c r="I3" s="14">
         <f>IFERROR(H3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1346027443252692E-3</v>
+        <v>1.6705586694719494E-3</v>
       </c>
       <c r="J3" s="14">
         <f>IFERROR(I3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1503775147664098E-3</v>
+        <v>1.6829041419911027E-3</v>
       </c>
       <c r="K3" s="14">
         <f>IFERROR(J3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1662688611761385E-3</v>
+        <v>1.6953408478769772E-3</v>
       </c>
       <c r="L3" s="14">
         <f>IFERROR(K3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1822776450539302E-3</v>
+        <v>1.7078694613465533E-3</v>
       </c>
       <c r="M3" s="14">
         <f>IFERROR(L3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1984047342657638E-3</v>
+        <v>1.7204906615992926E-3</v>
       </c>
       <c r="N3" s="14">
         <f>IFERROR(M3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2146510030911703E-3</v>
+        <v>1.7332051328539586E-3</v>
       </c>
       <c r="O3" s="14">
         <f>IFERROR(N3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2310173322706295E-3</v>
+        <v>1.7460135643857094E-3</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(O3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2475046090533169E-3</v>
+        <v>1.7589166505634648E-3</v>
       </c>
       <c r="Q3" s="14">
         <f>IFERROR(P3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2641137272452023E-3</v>
+        <v>1.771915090887549E-3</v>
       </c>
       <c r="R3" s="14">
         <f>IFERROR(Q3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2808455872575053E-3</v>
+        <v>1.7850095900276122E-3</v>
       </c>
       <c r="S3" s="14">
         <f>IFERROR(R3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2977010961555081E-3</v>
+        <v>1.7982008578608316E-3</v>
       </c>
       <c r="T3" s="14">
         <f>IFERROR(S3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.3146811677077291E-3</v>
+        <v>1.8114896095103958E-3</v>
       </c>
       <c r="U3" s="14">
         <f>IFERROR(T3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.3317867224354597E-3</v>
+        <v>1.8248765653842722E-3</v>
       </c>
       <c r="V3" s="14">
         <f>IFERROR(U3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.349018687662669E-3</v>
+        <v>1.8383624512142622E-3</v>
       </c>
       <c r="W3" s="14">
         <f>IFERROR(V3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.3663779975662737E-3</v>
+        <v>1.8519479980953443E-3</v>
       </c>
       <c r="X3" s="14">
         <f>IFERROR(W3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.383865593226783E-3</v>
+        <v>1.865633942525308E-3</v>
       </c>
       <c r="Y3" s="14">
         <f>IFERROR(X3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4014824226793151E-3</v>
+        <v>1.8794210264446811E-3</v>
       </c>
       <c r="Z3" s="14">
         <f>IFERROR(Y3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4192294409649934E-3</v>
+        <v>1.8933099972769513E-3</v>
       </c>
       <c r="AA3" s="14">
         <f>IFERROR(Z3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4371076101827203E-3</v>
+        <v>1.9073016079690854E-3</v>
       </c>
       <c r="AB3" s="14">
         <f>IFERROR(AA3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4551178995413339E-3</v>
+        <v>1.9213966170323483E-3</v>
       </c>
       <c r="AC3" s="14">
         <f>IFERROR(AB3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4732612854121514E-3</v>
+        <v>1.935595788583423E-3</v>
       </c>
       <c r="AD3" s="14">
         <f>IFERROR(AC3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.4915387513819E-3</v>
+        <v>1.9498998923858349E-3</v>
       </c>
       <c r="AE3" s="14">
         <f>IFERROR(AD3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5099512883060377E-3</v>
+        <v>1.9643097038916819E-3</v>
       </c>
       <c r="AF3" s="14">
         <f>IFERROR(AE3*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A3,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.5284998943624717E-3</v>
+        <v>1.978826004283674E-3</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -13483,127 +13483,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A4,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.4466270744806746E-4</v>
+        <v>5.8277513022011237E-4</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.5016578444789793E-4</v>
+        <v>5.8708185376502844E-4</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.5570952933154097E-4</v>
+        <v>5.9142040411024966E-4</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.6129424263572795E-4</v>
+        <v>5.9579101645666765E-4</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.6692022711816448E-4</v>
+        <v>6.0019392774331474E-4</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.7258778777394377E-4</v>
+        <v>6.0462937666020907E-4</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.7829723185208056E-4</v>
+        <v>6.090976036612942E-4</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.8404886887216809E-4</v>
+        <v>6.1359885097747471E-4</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.8984301064115737E-4</v>
+        <v>6.1813336262974794E-4</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>7.9567997127026114E-4</v>
+        <v>6.2270138444243267E-4</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.0156006719198222E-4</v>
+        <v>6.2730316405649599E-4</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.0748361717726785E-4</v>
+        <v>6.319389509429783E-4</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.1345094235279103E-4</v>
+        <v>6.3660899641651753E-4</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.1946236621835943E-4</v>
+        <v>6.4131355364897326E-4</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.2551821466445257E-4</v>
+        <v>6.46052877683152E-4</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.3161881598988938E-4</v>
+        <v>6.5082722544663313E-4</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.3776450091962572E-4</v>
+        <v>6.5563685576569759E-4</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.4395560262268338E-4</v>
+        <v>6.604820293793594E-4</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.5019245673021218E-4</v>
+        <v>6.653630089535009E-4</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.5647540135368476E-4</v>
+        <v>6.7028005909511193E-4</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.6280477710322671E-4</v>
+        <v>6.7523344636663519E-4</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.6918092710608125E-4</v>
+        <v>6.8022343930041677E-4</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.7560419702521091E-4</v>
+        <v>6.8525030841326377E-4</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.8207493507803665E-4</v>
+        <v>6.9031432622110973E-4</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.8859349205531546E-4</v>
+        <v>6.9541576725378796E-4</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.9516022134015702E-4</v>
+        <v>7.0055490806991466E-4</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.0177547892718172E-4</v>
+        <v>7.0573202727188141E-4</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.0843962344181936E-4</v>
+        <v>7.1094740552095869E-4</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.1515301615975131E-4</v>
+        <v>7.1620132555251124E-4</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.2191602102649549E-4</v>
+        <v>7.2149407219132555E-4</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A4,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.2872900467713703E-4</v>
+        <v>7.2682593236705082E-4</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -13613,127 +13613,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A5,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.1346744624501415E-4</v>
+        <v>6.366704966276768E-4</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.1947899207478029E-4</v>
+        <v>6.4137550834831105E-4</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.2553496338638982E-4</v>
+        <v>6.4611529022934788E-4</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.3163568848532241E-4</v>
+        <v>6.5089009922318739E-4</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.3778149810324388E-4</v>
+        <v>6.5570019418111482E-4</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.4397272541593567E-4</v>
+        <v>6.6054583586733304E-4</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.5020970606135705E-4</v>
+        <v>6.6542728697309937E-4</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.5649277815784061E-4</v>
+        <v>6.7034481213096644E-4</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.6282228232242245E-4</v>
+        <v>6.7529867792912826E-4</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.6919856168930732E-4</v>
+        <v>6.8028915292587286E-4</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.7562196192847094E-4</v>
+        <v>6.8531650766414092E-4</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.8209283126439923E-4</v>
+        <v>6.9038101468619248E-4</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.8861152049496612E-4</v>
+        <v>6.9548294854838229E-4</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>8.951783830104511E-4</v>
+        <v>7.0062258583604355E-4</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.0179377481269709E-4</v>
+        <v>7.0580020517848252E-4</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.0845805453441009E-4</v>
+        <v>7.110160872640833E-4</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.151715834586012E-4</v>
+        <v>7.162705148555245E-4</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.2193472553817241E-4</v>
+        <v>7.2156377280510847E-4</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.2874784741564737E-4</v>
+        <v>7.2689614807020344E-4</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.3561131844304747E-4</v>
+        <v>7.3226792972880012E-4</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.4252551070191527E-4</v>
+        <v>7.3767940899518341E-4</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.4949079902348593E-4</v>
+        <v>7.4313087923571922E-4</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.5650756100900704E-4</v>
+        <v>7.4862263598475867E-4</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.6357617705020941E-4</v>
+        <v>7.5415497696065944E-4</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.7069703034992881E-4</v>
+        <v>7.5972820208192594E-4</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.7787050694288008E-4</v>
+        <v>7.6534261348346804E-4</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.8509699571658468E-4</v>
+        <v>7.7099851553298052E-4</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.9237688843245315E-4</v>
+        <v>7.7669621484744344E-4</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>9.9971057974702297E-4</v>
+        <v>7.8243602030974452E-4</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.0070984672333541E-3</v>
+        <v>7.8821824308542411E-4</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A5,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.0145409514025817E-3</v>
+        <v>7.9404319663954408E-4</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -13743,127 +13743,127 @@
       </c>
       <c r="B6" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A6,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8038325811099969E-3</v>
+        <v>1.4116556438676638E-3</v>
       </c>
       <c r="C6" s="14">
         <f>IFERROR(B6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8171629513425408E-3</v>
+        <v>1.4220878162159625E-3</v>
       </c>
       <c r="D6" s="14">
         <f>IFERROR(C6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.83059183336182E-3</v>
+        <v>1.4325970825923816E-3</v>
       </c>
       <c r="E6" s="14">
         <f>IFERROR(D6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8441199551725304E-3</v>
+        <v>1.4431840127238171E-3</v>
       </c>
       <c r="F6" s="14">
         <f>IFERROR(E6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8577480501593417E-3</v>
+        <v>1.4538491805474621E-3</v>
       </c>
       <c r="G6" s="14">
         <f>IFERROR(F6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8714768571266556E-3</v>
+        <v>1.4645931642419203E-3</v>
       </c>
       <c r="H6" s="14">
         <f>IFERROR(G6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.8853071203386576E-3</v>
+        <v>1.4754165462585506E-3</v>
       </c>
       <c r="I6" s="14">
         <f>IFERROR(H6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.899239589559665E-3</v>
+        <v>1.4863199133530428E-3</v>
       </c>
       <c r="J6" s="14">
         <f>IFERROR(I6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.9132750200947736E-3</v>
+        <v>1.4973038566172268E-3</v>
       </c>
       <c r="K6" s="14">
         <f>IFERROR(J6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.9274141728308034E-3</v>
+        <v>1.5083689715111163E-3</v>
       </c>
       <c r="L6" s="14">
         <f>IFERROR(K6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.9416578142775482E-3</v>
+        <v>1.5195158578951906E-3</v>
       </c>
       <c r="M6" s="14">
         <f>IFERROR(L6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.9560067166093293E-3</v>
+        <v>1.5307451200629134E-3</v>
       </c>
       <c r="N6" s="14">
         <f>IFERROR(M6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.9704616577068562E-3</v>
+        <v>1.5420573667734934E-3</v>
       </c>
       <c r="O6" s="14">
         <f>IFERROR(N6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.9850234211993977E-3</v>
+        <v>1.5534532112848854E-3</v>
       </c>
       <c r="P6" s="14">
         <f>IFERROR(O6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.9996927965072633E-3</v>
+        <v>1.5649332713870369E-3</v>
       </c>
       <c r="Q6" s="14">
         <f>IFERROR(P6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0144705788846E-3</v>
+        <v>1.5764981694353791E-3</v>
       </c>
       <c r="R6" s="14">
         <f>IFERROR(Q6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0293575694625026E-3</v>
+        <v>1.5881485323845667E-3</v>
       </c>
       <c r="S6" s="14">
         <f>IFERROR(R6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0443545752924473E-3</v>
+        <v>1.5998849918224653E-3</v>
       </c>
       <c r="T6" s="14">
         <f>IFERROR(S6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0594624093900407E-3</v>
+        <v>1.6117081840043917E-3</v>
       </c>
       <c r="U6" s="14">
         <f>IFERROR(T6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0746818907790964E-3</v>
+        <v>1.6236187498876063E-3</v>
       </c>
       <c r="V6" s="14">
         <f>IFERROR(U6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.0900138445360361E-3</v>
+        <v>1.6356173351660601E-3</v>
       </c>
       <c r="W6" s="14">
         <f>IFERROR(V6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1054591018346172E-3</v>
+        <v>1.6477045903053999E-3</v>
       </c>
       <c r="X6" s="14">
         <f>IFERROR(W6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1210184999909936E-3</v>
+        <v>1.6598811705782306E-3</v>
       </c>
       <c r="Y6" s="14">
         <f>IFERROR(X6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1366928825091074E-3</v>
+        <v>1.6721477360996384E-3</v>
       </c>
       <c r="Z6" s="14">
         <f>IFERROR(Y6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1524830991264173E-3</v>
+        <v>1.6845049518629781E-3</v>
       </c>
       <c r="AA6" s="14">
         <f>IFERROR(Z6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1683900058599636E-3</v>
+        <v>1.6969534877759225E-3</v>
       </c>
       <c r="AB6" s="14">
         <f>IFERROR(AA6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.1844144650527753E-3</v>
+        <v>1.7094940186967798E-3</v>
       </c>
       <c r="AC6" s="14">
         <f>IFERROR(AB6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2005573454206193E-3</v>
+        <v>1.7221272244710788E-3</v>
       </c>
       <c r="AD6" s="14">
         <f>IFERROR(AC6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2168195220990945E-3</v>
+        <v>1.7348537899684246E-3</v>
       </c>
       <c r="AE6" s="14">
         <f>IFERROR(AD6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2332018766910754E-3</v>
+        <v>1.7476744051196269E-3</v>
       </c>
       <c r="AF6" s="14">
         <f>IFERROR(AE6*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A6,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>2.2497052973145045E-3</v>
+        <v>1.7605897649541019E-3</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -13873,127 +13873,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE psgr'!$B$3:$H$3,,MATCH($A7,'SYFAFE psgr'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3648120076442665E-3</v>
+        <v>1.0681356448960849E-3</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3748980042884364E-3</v>
+        <v>1.0760291954141047E-3</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3850585367131654E-3</v>
+        <v>1.0839810794781289E-3</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.3952941557398328E-3</v>
+        <v>1.0919917281745973E-3</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4056054162604023E-3</v>
+        <v>1.1000615757756898E-3</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4159928772675043E-3</v>
+        <v>1.1081910597628688E-3</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4264571018847388E-3</v>
+        <v>1.1163806208505968E-3</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4369986573972045E-3</v>
+        <v>1.1246307030102272E-3</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4476181152822515E-3</v>
+        <v>1.1329417534940737E-3</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4583160512404629E-3</v>
+        <v>1.1413142228596566E-3</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.469093045226864E-3</v>
+        <v>1.1497485649941274E-3</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4799496814823631E-3</v>
+        <v>1.1582452371388763E-3</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.4908865485654243E-3</v>
+        <v>1.166804699914319E-3</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5019042393839741E-3</v>
+        <v>1.1754274173448685E-3</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5130033512275442E-3</v>
+        <v>1.18411385688409E-3</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5241844857996516E-3</v>
+        <v>1.1928644894400433E-3</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5354482492504183E-3</v>
+        <v>1.2016797894008108E-3</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5467952522094314E-3</v>
+        <v>1.2105602346602156E-3</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.558226109818847E-3</v>
+        <v>1.2195063066437284E-3</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5697414417667375E-3</v>
+        <v>1.2285184903345671E-3</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5813418723206868E-3</v>
+        <v>1.2375972742999881E-3</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.5930280303616327E-3</v>
+        <v>1.2467431507177729E-3</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6048005494179597E-3</v>
+        <v>1.2559566154029098E-3</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6166600676998434E-3</v>
+        <v>1.2652381678344724E-3</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6286072281338495E-3</v>
+        <v>1.2745883111826984E-3</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6406426783977881E-3</v>
+        <v>1.2840075523362666E-3</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6527670709558253E-3</v>
+        <v>1.2934964019297762E-3</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6649810630938544E-3</v>
+        <v>1.3030553743714299E-3</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.677285316955129E-3</v>
+        <v>1.3126849878709202E-3</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.6896804995761585E-3</v>
+        <v>1.3223857644675231E-3</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$16:$C$22,MATCH($A7,CAGR!$B$16:$B$22,0))),0)</f>
-        <v>1.7021672829228699E-3</v>
+        <v>1.3321582300583987E-3</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -14003,127 +14003,127 @@
       </c>
       <c r="B8" s="18">
         <f>'SYFAFE psgr'!H3</f>
-        <v>2.4225000000000002E-3</v>
+        <v>1.8959000000000001E-3</v>
       </c>
       <c r="C8" s="18">
         <f>B8*(1+CAGR!$D$22)</f>
-        <v>2.4481585172899736E-3</v>
+        <v>1.9159809011063201E-3</v>
       </c>
       <c r="D8" s="18">
         <f>C8*(1+CAGR!$D$22)</f>
-        <v>2.4740888032113279E-3</v>
+        <v>1.9362744941210962E-3</v>
       </c>
       <c r="E8" s="18">
         <f>D8*(1+CAGR!$D$22)</f>
-        <v>2.500293736269791E-3</v>
+        <v>1.9567830318241056E-3</v>
       </c>
       <c r="F8" s="18">
         <f>E8*(1+CAGR!$D$22)</f>
-        <v>2.5267762254595084E-3</v>
+        <v>1.9775087908560085E-3</v>
       </c>
       <c r="G8" s="18">
         <f>F8*(1+CAGR!$D$22)</f>
-        <v>2.5535392105859671E-3</v>
+        <v>1.9984540719710769E-3</v>
       </c>
       <c r="H8" s="18">
         <f>G8*(1+CAGR!$D$22)</f>
-        <v>2.5805856625923428E-3</v>
+        <v>2.019621200292599E-3</v>
       </c>
       <c r="I8" s="18">
         <f>H8*(1+CAGR!$D$22)</f>
-        <v>2.6079185838893018E-3</v>
+        <v>2.0410125255709908E-3</v>
       </c>
       <c r="J8" s="18">
         <f>I8*(1+CAGR!$D$22)</f>
-        <v>2.6355410086882974E-3</v>
+        <v>2.0626304224446402E-3</v>
       </c>
       <c r="K8" s="18">
         <f>J8*(1+CAGR!$D$22)</f>
-        <v>2.6634560033383953E-3</v>
+        <v>2.0844772907035137E-3</v>
       </c>
       <c r="L8" s="18">
         <f>K8*(1+CAGR!$D$22)</f>
-        <v>2.6916666666666686E-3</v>
+        <v>2.1065555555555564E-3</v>
       </c>
       <c r="M8" s="18">
         <f>L8*(1+CAGR!$D$22)</f>
-        <v>2.7201761303221944E-3</v>
+        <v>2.1288676678959122E-3</v>
       </c>
       <c r="N8" s="18">
         <f>M8*(1+CAGR!$D$22)</f>
-        <v>2.7489875591236988E-3</v>
+        <v>2.1514161045789967E-3</v>
       </c>
       <c r="O8" s="18">
         <f>N8*(1+CAGR!$D$22)</f>
-        <v>2.7781041514108804E-3</v>
+        <v>2.1742033686934516E-3</v>
       </c>
       <c r="P8" s="18">
         <f>O8*(1+CAGR!$D$22)</f>
-        <v>2.8075291393994551E-3</v>
+        <v>2.1972319898400107E-3</v>
       </c>
       <c r="Q8" s="18">
         <f>P8*(1+CAGR!$D$22)</f>
-        <v>2.8372657895399649E-3</v>
+        <v>2.220504524412309E-3</v>
       </c>
       <c r="R8" s="18">
         <f>Q8*(1+CAGR!$D$22)</f>
-        <v>2.8673174028803821E-3</v>
+        <v>2.244023555880667E-3</v>
       </c>
       <c r="S8" s="18">
         <f>R8*(1+CAGR!$D$22)</f>
-        <v>2.8976873154325589E-3</v>
+        <v>2.2677916950788802E-3</v>
       </c>
       <c r="T8" s="18">
         <f>S8*(1+CAGR!$D$22)</f>
-        <v>2.9283788985425539E-3</v>
+        <v>2.291811580494046E-3</v>
       </c>
       <c r="U8" s="18">
         <f>T8*(1+CAGR!$D$22)</f>
-        <v>2.9593955592648849E-3</v>
+        <v>2.3160858785594607E-3</v>
       </c>
       <c r="V8" s="18">
         <f>U8*(1+CAGR!$D$22)</f>
-        <v>2.9907407407407439E-3</v>
+        <v>2.3406172839506192E-3</v>
       </c>
       <c r="W8" s="18">
         <f>V8*(1+CAGR!$D$22)</f>
-        <v>3.022417922580217E-3</v>
+        <v>2.3654085198843476E-3</v>
       </c>
       <c r="X8" s="18">
         <f>W8*(1+CAGR!$D$22)</f>
-        <v>3.0544306212485555E-3</v>
+        <v>2.3904623384211083E-3</v>
       </c>
       <c r="Y8" s="18">
         <f>X8*(1+CAGR!$D$22)</f>
-        <v>3.0867823904565349E-3</v>
+        <v>2.4157815207705028E-3</v>
       </c>
       <c r="Z8" s="18">
         <f>Y8*(1+CAGR!$D$22)</f>
-        <v>3.1194768215549516E-3</v>
+        <v>2.4413688776000128E-3</v>
       </c>
       <c r="AA8" s="18">
         <f>Z8*(1+CAGR!$D$22)</f>
-        <v>3.1525175439332956E-3</v>
+        <v>2.4672272493470107E-3</v>
       </c>
       <c r="AB8" s="18">
         <f>AA8*(1+CAGR!$D$22)</f>
-        <v>3.1859082254226483E-3</v>
+        <v>2.4933595065340752E-3</v>
       </c>
       <c r="AC8" s="18">
         <f>AB8*(1+CAGR!$D$22)</f>
-        <v>3.2196525727028447E-3</v>
+        <v>2.5197685500876455E-3</v>
       </c>
       <c r="AD8" s="18">
         <f>AC8*(1+CAGR!$D$22)</f>
-        <v>3.2537543317139503E-3</v>
+        <v>2.5464573116600522E-3</v>
       </c>
       <c r="AE8" s="18">
         <f>AD8*(1+CAGR!$D$22)</f>
-        <v>3.2882172880720961E-3</v>
+        <v>2.5734287539549575E-3</v>
       </c>
       <c r="AF8" s="18">
         <f>AE8*(1+CAGR!$D$22)</f>
-        <v>3.3230452674897172E-3</v>
+        <v>2.6006858710562446E-3</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -14250,127 +14250,127 @@
       </c>
       <c r="B2" s="21">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A2,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.8650420585667308E-3</v>
+        <v>2.242251001154885E-3</v>
       </c>
       <c r="C2" s="21">
         <f>IFERROR(B2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9108035451618055E-3</v>
+        <v>2.2780650440326613E-3</v>
       </c>
       <c r="D2" s="21">
         <f>IFERROR(C2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.9572959507495455E-3</v>
+        <v>2.3144511217390944E-3</v>
       </c>
       <c r="E2" s="21">
         <f>IFERROR(D2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0045309498321049E-3</v>
+        <v>2.3514183710210833E-3</v>
       </c>
       <c r="F2" s="21">
         <f>IFERROR(E2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.0525204033810035E-3</v>
+        <v>2.3889760745609482E-3</v>
       </c>
       <c r="G2" s="21">
         <f>IFERROR(F2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1012763618154817E-3</v>
+        <v>2.4271336633073645E-3</v>
       </c>
       <c r="H2" s="21">
         <f>IFERROR(G2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.1508110680284291E-3</v>
+        <v>2.4659007188435255E-3</v>
       </c>
       <c r="I2" s="21">
         <f>IFERROR(H2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2011369604606423E-3</v>
+        <v>2.5052869757931336E-3</v>
       </c>
       <c r="J2" s="21">
         <f>IFERROR(I2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.2522666762241866E-3</v>
+        <v>2.5453023242648152E-3</v>
       </c>
       <c r="K2" s="21">
         <f>IFERROR(J2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3042130542756468E-3</v>
+        <v>2.5859568123355854E-3</v>
       </c>
       <c r="L2" s="21">
         <f>IFERROR(K2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.3569891386400585E-3</v>
+        <v>2.6272606485739742E-3</v>
       </c>
       <c r="M2" s="21">
         <f>IFERROR(L2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4106081816863369E-3</v>
+        <v>2.6692242046034553E-3</v>
       </c>
       <c r="N2" s="21">
         <f>IFERROR(M2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.4650836474550205E-3</v>
+        <v>2.7118580177068188E-3</v>
       </c>
       <c r="O2" s="21">
         <f>IFERROR(N2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.520429215039166E-3</v>
+        <v>2.7551727934721415E-3</v>
       </c>
       <c r="P2" s="21">
         <f>IFERROR(O2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.5766587820192457E-3</v>
+        <v>2.7991794084810196E-3</v>
       </c>
       <c r="Q2" s="21">
         <f>IFERROR(P2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.6337864679529064E-3</v>
+        <v>2.8438889130397394E-3</v>
       </c>
       <c r="R2" s="21">
         <f>IFERROR(Q2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.69182661792047E-3</v>
+        <v>2.8893125339540704E-3</v>
       </c>
       <c r="S2" s="21">
         <f>IFERROR(R2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.7507938061270623E-3</v>
+        <v>2.9354616773483787E-3</v>
       </c>
       <c r="T2" s="21">
         <f>IFERROR(S2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.8107028395622778E-3</v>
+        <v>2.9823479315297689E-3</v>
       </c>
       <c r="U2" s="21">
         <f>IFERROR(T2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.8715687617182962E-3</v>
+        <v>3.0299830698979719E-3</v>
       </c>
       <c r="V2" s="21">
         <f>IFERROR(U2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.9334068563673889E-3</v>
+        <v>3.0783790539017121E-3</v>
       </c>
       <c r="W2" s="21">
         <f>IFERROR(V2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>3.9962326513997577E-3</v>
+        <v>3.1275480360422932E-3</v>
       </c>
       <c r="X2" s="21">
         <f>IFERROR(W2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.0600619227226763E-3</v>
+        <v>3.1775023629251591E-3</v>
       </c>
       <c r="Y2" s="21">
         <f>IFERROR(X2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.1249106982219064E-3</v>
+        <v>3.2282545783601951E-3</v>
       </c>
       <c r="Z2" s="21">
         <f>IFERROR(Y2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.1907952617863909E-3</v>
+        <v>3.2798174265115487E-3</v>
       </c>
       <c r="AA2" s="21">
         <f>IFERROR(Z2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.2577321573972282E-3</v>
+        <v>3.332203855097761E-3</v>
       </c>
       <c r="AB2" s="21">
         <f>IFERROR(AA2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.325738193281959E-3</v>
+        <v>3.3854270186430093E-3</v>
       </c>
       <c r="AC2" s="21">
         <f>IFERROR(AB2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.394830446135204E-3</v>
+        <v>3.439500281780283E-3</v>
       </c>
       <c r="AD2" s="21">
         <f>IFERROR(AC2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.4650262654067196E-3</v>
+        <v>3.4944372226073167E-3</v>
       </c>
       <c r="AE2" s="21">
         <f>IFERROR(AD2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.53634327765794E-3</v>
+        <v>3.5502516360961267E-3</v>
       </c>
       <c r="AF2" s="21">
         <f>IFERROR(AE2*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A2,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>4.608799390988105E-3</v>
+        <v>3.6069575375570042E-3</v>
       </c>
       <c r="AG2" s="14"/>
     </row>
@@ -14380,127 +14380,127 @@
       </c>
       <c r="B3" s="13">
         <f>B5*Calibration!$C$27</f>
-        <v>1.0276218605288386E-3</v>
+        <v>8.0401576058837933E-4</v>
       </c>
       <c r="C3" s="13">
         <f>B3*(1+CAGR!$C$24)</f>
-        <v>1.0352160131144824E-3</v>
+        <v>8.0995745821247267E-4</v>
       </c>
       <c r="D3" s="13">
         <f>C3*(1+CAGR!$C$24)</f>
-        <v>1.0428662866875335E-3</v>
+        <v>8.1594306513833187E-4</v>
       </c>
       <c r="E3" s="13">
         <f>D3*(1+CAGR!$C$24)</f>
-        <v>1.050573095983565E-3</v>
+        <v>8.2197290585685223E-4</v>
       </c>
       <c r="F3" s="13">
         <f>E3*(1+CAGR!$C$24)</f>
-        <v>1.0583368588030573E-3</v>
+        <v>8.2804730725692514E-4</v>
       </c>
       <c r="G3" s="13">
         <f>F3*(1+CAGR!$C$24)</f>
-        <v>1.0661579960340474E-3</v>
+        <v>8.3416659864315979E-4</v>
       </c>
       <c r="H3" s="13">
         <f>G3*(1+CAGR!$C$24)</f>
-        <v>1.0740369316749455E-3</v>
+        <v>8.4033111175373489E-4</v>
       </c>
       <c r="I3" s="13">
         <f>H3*(1+CAGR!$C$24)</f>
-        <v>1.0819740928575217E-3</v>
+        <v>8.4654118077838317E-4</v>
       </c>
       <c r="J3" s="13">
         <f>I3*(1+CAGR!$C$24)</f>
-        <v>1.0899699098700607E-3</v>
+        <v>8.5279714237650813E-4</v>
       </c>
       <c r="K3" s="13">
         <f>J3*(1+CAGR!$C$24)</f>
-        <v>1.0980248161806894E-3</v>
+        <v>8.590993356954351E-4</v>
       </c>
       <c r="L3" s="13">
         <f>K3*(1+CAGR!$C$24)</f>
-        <v>1.106139248460875E-3</v>
+        <v>8.6544810238879731E-4</v>
       </c>
       <c r="M3" s="13">
         <f>L3*(1+CAGR!$C$24)</f>
-        <v>1.1143136466090988E-3</v>
+        <v>8.7184378663505708E-4</v>
       </c>
       <c r="N3" s="13">
         <f>M3*(1+CAGR!$C$24)</f>
-        <v>1.1225484537747033E-3</v>
+        <v>8.7828673515616461E-4</v>
       </c>
       <c r="O3" s="13">
         <f>N3*(1+CAGR!$C$24)</f>
-        <v>1.1308441163819162E-3</v>
+        <v>8.8477729723635467E-4</v>
       </c>
       <c r="P3" s="13">
         <f>O3*(1+CAGR!$C$24)</f>
-        <v>1.1392010841540521E-3</v>
+        <v>8.9131582474108158E-4</v>
       </c>
       <c r="Q3" s="13">
         <f>P3*(1+CAGR!$C$24)</f>
-        <v>1.1476198101378926E-3</v>
+        <v>8.9790267213609451E-4</v>
       </c>
       <c r="R3" s="13">
         <f>Q3*(1+CAGR!$C$24)</f>
-        <v>1.1561007507282473E-3</v>
+        <v>9.0453819650665403E-4</v>
       </c>
       <c r="S3" s="13">
         <f>R3*(1+CAGR!$C$24)</f>
-        <v>1.1646443656926949E-3</v>
+        <v>9.1122275757689005E-4</v>
       </c>
       <c r="T3" s="13">
         <f>S3*(1+CAGR!$C$24)</f>
-        <v>1.1732511181965089E-3</v>
+        <v>9.1795671772930334E-4</v>
       </c>
       <c r="U3" s="13">
         <f>T3*(1+CAGR!$C$24)</f>
-        <v>1.1819214748277666E-3</v>
+        <v>9.2474044202441085E-4</v>
       </c>
       <c r="V3" s="13">
         <f>U3*(1+CAGR!$C$24)</f>
-        <v>1.1906559056226429E-3</v>
+        <v>9.3157429822053638E-4</v>
       </c>
       <c r="W3" s="13">
         <f>V3*(1+CAGR!$C$24)</f>
-        <v>1.1994548840908929E-3</v>
+        <v>9.3845865679374741E-4</v>
       </c>
       <c r="X3" s="13">
         <f>W3*(1+CAGR!$C$24)</f>
-        <v>1.208318887241521E-3</v>
+        <v>9.4539389095793925E-4</v>
       </c>
       <c r="Y3" s="13">
         <f>X3*(1+CAGR!$C$24)</f>
-        <v>1.2172483956086409E-3</v>
+        <v>9.5238037668506786E-4</v>
       </c>
       <c r="Z3" s="13">
         <f>Y3*(1+CAGR!$C$24)</f>
-        <v>1.2262438932775256E-3</v>
+        <v>9.5941849272553168E-4</v>
       </c>
       <c r="AA3" s="13">
         <f>Z3*(1+CAGR!$C$24)</f>
-        <v>1.2353058679108514E-3</v>
+        <v>9.6650862062870472E-4</v>
       </c>
       <c r="AB3" s="13">
         <f>AA3*(1+CAGR!$C$24)</f>
-        <v>1.2444348107751345E-3</v>
+        <v>9.7365114476362065E-4</v>
       </c>
       <c r="AC3" s="13">
         <f>AB3*(1+CAGR!$C$24)</f>
-        <v>1.2536312167673637E-3</v>
+        <v>9.8084645233981064E-4</v>
       </c>
       <c r="AD3" s="13">
         <f>AC3*(1+CAGR!$C$24)</f>
-        <v>1.2628955844418293E-3</v>
+        <v>9.8809493342829464E-4</v>
       </c>
       <c r="AE3" s="13">
         <f>AD3*(1+CAGR!$C$24)</f>
-        <v>1.2722284160371514E-3</v>
+        <v>9.9539698098272708E-4</v>
       </c>
       <c r="AF3" s="13">
         <f>AE3*(1+CAGR!$C$24)</f>
-        <v>1.2816302175035058E-3</v>
+        <v>1.002752990860701E-3</v>
       </c>
       <c r="AG3" s="14"/>
     </row>
@@ -14510,127 +14510,127 @@
       </c>
       <c r="B4" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A4,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5090702594118034E-3</v>
+        <v>1.180661110834869E-3</v>
       </c>
       <c r="C4" s="14">
         <f>IFERROR(B4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5202223283319145E-3</v>
+        <v>1.1893862275066782E-3</v>
       </c>
       <c r="D4" s="14">
         <f>IFERROR(C4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5314568113347518E-3</v>
+        <v>1.1981758230202465E-3</v>
       </c>
       <c r="E4" s="14">
         <f>IFERROR(D4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.542774317462555E-3</v>
+        <v>1.2070303738759109E-3</v>
       </c>
       <c r="F4" s="14">
         <f>IFERROR(E4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5541754602584018E-3</v>
+        <v>1.2159503600953584E-3</v>
       </c>
       <c r="G4" s="14">
         <f>IFERROR(F4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5656608577994697E-3</v>
+        <v>1.2249362652476492E-3</v>
       </c>
       <c r="H4" s="14">
         <f>IFERROR(G4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5772311327305424E-3</v>
+        <v>1.2339885764754311E-3</v>
       </c>
       <c r="I4" s="14">
         <f>IFERROR(H4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5888869122977652E-3</v>
+        <v>1.2431077845213492E-3</v>
       </c>
       <c r="J4" s="14">
         <f>IFERROR(I4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6006288283826489E-3</v>
+        <v>1.2522943837546493E-3</v>
       </c>
       <c r="K4" s="14">
         <f>IFERROR(J4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6124575175363253E-3</v>
+        <v>1.2615488721979796E-3</v>
       </c>
       <c r="L4" s="14">
         <f>IFERROR(K4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6243736210140554E-3</v>
+        <v>1.270871751554388E-3</v>
       </c>
       <c r="M4" s="14">
         <f>IFERROR(L4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6363777848099942E-3</v>
+        <v>1.2802635272345217E-3</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(M4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6484706596922099E-3</v>
+        <v>1.2897247083840256E-3</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(N4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6606529012379639E-3</v>
+        <v>1.2992558079111443E-3</v>
       </c>
       <c r="P4" s="14">
         <f>IFERROR(O4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6729251698692513E-3</v>
+        <v>1.3088573425145279E-3</v>
       </c>
       <c r="Q4" s="14">
         <f>IFERROR(P4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6852881308886025E-3</v>
+        <v>1.3185298327112432E-3</v>
       </c>
       <c r="R4" s="14">
         <f>IFERROR(Q4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6977424545151516E-3</v>
+        <v>1.3282738028649918E-3</v>
       </c>
       <c r="S4" s="14">
         <f>IFERROR(R4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7102888159209692E-3</v>
+        <v>1.3380897812145366E-3</v>
       </c>
       <c r="T4" s="14">
         <f>IFERROR(S4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7229278952676657E-3</v>
+        <v>1.3479782999023392E-3</v>
       </c>
       <c r="U4" s="14">
         <f>IFERROR(T4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7356603777432637E-3</v>
+        <v>1.3579398950034078E-3</v>
       </c>
       <c r="V4" s="14">
         <f>IFERROR(U4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.748486953599343E-3</v>
+        <v>1.3679751065543591E-3</v>
       </c>
       <c r="W4" s="14">
         <f>IFERROR(V4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7614083181884609E-3</v>
+        <v>1.3780844785826944E-3</v>
       </c>
       <c r="X4" s="14">
         <f>IFERROR(W4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7744251720018486E-3</v>
+        <v>1.3882685591362928E-3</v>
       </c>
       <c r="Y4" s="14">
         <f>IFERROR(X4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7875382207073857E-3</v>
+        <v>1.3985279003131215E-3</v>
       </c>
       <c r="Z4" s="14">
         <f>IFERROR(Y4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.800748175187856E-3</v>
+        <v>1.4088630582911664E-3</v>
       </c>
       <c r="AA4" s="14">
         <f>IFERROR(Z4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8140557515794857E-3</v>
+        <v>1.4192745933585831E-3</v>
       </c>
       <c r="AB4" s="14">
         <f>IFERROR(AA4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8274616713107668E-3</v>
+        <v>1.4297630699440713E-3</v>
       </c>
       <c r="AC4" s="14">
         <f>IFERROR(AB4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8409666611415667E-3</v>
+        <v>1.4403290566474742E-3</v>
       </c>
       <c r="AD4" s="14">
         <f>IFERROR(AC4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8545714532025273E-3</v>
+        <v>1.4509731262706022E-3</v>
       </c>
       <c r="AE4" s="14">
         <f>IFERROR(AD4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8682767850347552E-3</v>
+        <v>1.4616958558482866E-3</v>
       </c>
       <c r="AF4" s="14">
         <f>IFERROR(AE4*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A4,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8820833996298053E-3</v>
+        <v>1.4724978266796608E-3</v>
       </c>
       <c r="AG4" s="14"/>
     </row>
@@ -14640,127 +14640,127 @@
       </c>
       <c r="B5" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A5,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5000037491750171E-3</v>
+        <v>1.1736093806507017E-3</v>
       </c>
       <c r="C5" s="14">
         <f>IFERROR(B5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5110888163459419E-3</v>
+        <v>1.1822823848509215E-3</v>
       </c>
       <c r="D5" s="14">
         <f>IFERROR(C5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5222558024549037E-3</v>
+        <v>1.1910194827803645E-3</v>
       </c>
       <c r="E5" s="14">
         <f>IFERROR(D5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5335053128850097E-3</v>
+        <v>1.1998211480933757E-3</v>
       </c>
       <c r="F5" s="14">
         <f>IFERROR(E5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5448379574931645E-3</v>
+        <v>1.2086878579446183E-3</v>
       </c>
       <c r="G5" s="14">
         <f>IFERROR(F5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.556254350643131E-3</v>
+        <v>1.2176200930149414E-3</v>
       </c>
       <c r="H5" s="14">
         <f>IFERROR(G5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5677551112388368E-3</v>
+        <v>1.226618337537438E-3</v>
       </c>
       <c r="I5" s="14">
         <f>IFERROR(H5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5793408627579255E-3</v>
+        <v>1.2356830793236961E-3</v>
       </c>
       <c r="J5" s="14">
         <f>IFERROR(I5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.5910122332855568E-3</v>
+        <v>1.2448148097902445E-3</v>
       </c>
       <c r="K5" s="14">
         <f>IFERROR(J5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6027698555484567E-3</v>
+        <v>1.2540140239851931E-3</v>
       </c>
       <c r="L5" s="14">
         <f>IFERROR(K5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6146143669492179E-3</v>
+        <v>1.26328122061507E-3</v>
       </c>
       <c r="M5" s="14">
         <f>IFERROR(L5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6265464096008552E-3</v>
+        <v>1.2726169020718583E-3</v>
       </c>
       <c r="N5" s="14">
         <f>IFERROR(M5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6385666303616155E-3</v>
+        <v>1.2820215744602302E-3</v>
       </c>
       <c r="O5" s="14">
         <f>IFERROR(N5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6506756808700453E-3</v>
+        <v>1.2914957476249855E-3</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(O5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.662874217580317E-3</v>
+        <v>1.3010399351786903E-3</v>
       </c>
       <c r="Q5" s="14">
         <f>IFERROR(P5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6751629017978163E-3</v>
+        <v>1.3106546545295207E-3</v>
       </c>
       <c r="R5" s="14">
         <f>IFERROR(Q5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6875423997149935E-3</v>
+        <v>1.3203404269093134E-3</v>
       </c>
       <c r="S5" s="14">
         <f>IFERROR(R5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7000133824474784E-3</v>
+        <v>1.3300977774018217E-3</v>
       </c>
       <c r="T5" s="14">
         <f>IFERROR(S5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7125765260704632E-3</v>
+        <v>1.3399272349711817E-3</v>
       </c>
       <c r="U5" s="14">
         <f>IFERROR(T5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7252325116553532E-3</v>
+        <v>1.3498293324905885E-3</v>
       </c>
       <c r="V5" s="14">
         <f>IFERROR(U5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7379820253066898E-3</v>
+        <v>1.3598046067711843E-3</v>
       </c>
       <c r="W5" s="14">
         <f>IFERROR(V5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7508257581993446E-3</v>
+        <v>1.3698535985911594E-3</v>
       </c>
       <c r="X5" s="14">
         <f>IFERROR(W5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7637644066159897E-3</v>
+        <v>1.3799768527250689E-3</v>
       </c>
       <c r="Y5" s="14">
         <f>IFERROR(X5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7767986719848447E-3</v>
+        <v>1.3901749179733671E-3</v>
       </c>
       <c r="Z5" s="14">
         <f>IFERROR(Y5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7899292609177019E-3</v>
+        <v>1.4004483471921575E-3</v>
       </c>
       <c r="AA5" s="14">
         <f>IFERROR(Z5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8031568852482339E-3</v>
+        <v>1.4107976973231646E-3</v>
       </c>
       <c r="AB5" s="14">
         <f>IFERROR(AA5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8164822620705819E-3</v>
+        <v>1.4212235294239273E-3</v>
       </c>
       <c r="AC5" s="14">
         <f>IFERROR(AB5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8299061137782328E-3</v>
+        <v>1.4317264086982143E-3</v>
       </c>
       <c r="AD5" s="14">
         <f>IFERROR(AC5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8434291681031795E-3</v>
+        <v>1.4423069045266649E-3</v>
       </c>
       <c r="AE5" s="14">
         <f>IFERROR(AD5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8570521581553741E-3</v>
+        <v>1.4529655904976565E-3</v>
       </c>
       <c r="AF5" s="14">
         <f>IFERROR(AE5*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A5,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.87077582246247E-3</v>
+        <v>1.4637030444383998E-3</v>
       </c>
       <c r="AG5" s="14"/>
     </row>
@@ -14770,127 +14770,127 @@
       </c>
       <c r="B6" s="13">
         <f>B5*Calibration!$E$26</f>
-        <v>3.3261248918118554E-3</v>
+        <v>2.602374411659376E-3</v>
       </c>
       <c r="C6" s="13">
         <f>B6*(1+CAGR!$C$27)</f>
-        <v>3.350705042271411E-3</v>
+        <v>2.6216060270290082E-3</v>
       </c>
       <c r="D6" s="13">
         <f>C6*(1+CAGR!$C$27)</f>
-        <v>3.3754668406895567E-3</v>
+        <v>2.6409797645421981E-3</v>
       </c>
       <c r="E6" s="13">
         <f>D6*(1+CAGR!$C$27)</f>
-        <v>3.4004116294494863E-3</v>
+        <v>2.6604966744853261E-3</v>
       </c>
       <c r="F6" s="13">
         <f>E6*(1+CAGR!$C$27)</f>
-        <v>3.4255407608546392E-3</v>
+        <v>2.6801578149064165E-3</v>
       </c>
       <c r="G6" s="13">
         <f>F6*(1+CAGR!$C$27)</f>
-        <v>3.450855597202014E-3</v>
+        <v>2.6999642516724958E-3</v>
       </c>
       <c r="H6" s="13">
         <f>G6*(1+CAGR!$C$27)</f>
-        <v>3.4763575108560196E-3</v>
+        <v>2.7199170585273757E-3</v>
       </c>
       <c r="I6" s="13">
         <f>H6*(1+CAGR!$C$27)</f>
-        <v>3.5020478843228739E-3</v>
+        <v>2.7400173171498641E-3</v>
       </c>
       <c r="J6" s="13">
         <f>I6*(1+CAGR!$C$27)</f>
-        <v>3.5279281103255521E-3</v>
+        <v>2.7602661172124029E-3</v>
       </c>
       <c r="K6" s="13">
         <f>J6*(1+CAGR!$C$27)</f>
-        <v>3.553999591879289E-3</v>
+        <v>2.7806645564401418E-3</v>
       </c>
       <c r="L6" s="13">
         <f>K6*(1+CAGR!$C$27)</f>
-        <v>3.5802637423676385E-3</v>
+        <v>2.8012137406704489E-3</v>
       </c>
       <c r="M6" s="13">
         <f>L6*(1+CAGR!$C$27)</f>
-        <v>3.6067219856190966E-3</v>
+        <v>2.8219147839128591E-3</v>
       </c>
       <c r="N6" s="13">
         <f>M6*(1+CAGR!$C$27)</f>
-        <v>3.6333757559842889E-3</v>
+        <v>2.8427688084094673E-3</v>
       </c>
       <c r="O6" s="13">
         <f>N6*(1+CAGR!$C$27)</f>
-        <v>3.6602264984137308E-3</v>
+        <v>2.8637769446957667E-3</v>
       </c>
       <c r="P6" s="13">
         <f>O6*(1+CAGR!$C$27)</f>
-        <v>3.687275668536159E-3</v>
+        <v>2.8849403316619378E-3</v>
       </c>
       <c r="Q6" s="13">
         <f>P6*(1+CAGR!$C$27)</f>
-        <v>3.7145247327374452E-3</v>
+        <v>2.9062601166145894E-3</v>
       </c>
       <c r="R6" s="13">
         <f>Q6*(1+CAGR!$C$27)</f>
-        <v>3.7419751682400914E-3</v>
+        <v>2.9277374553389563E-3</v>
       </c>
       <c r="S6" s="13">
         <f>R6*(1+CAGR!$C$27)</f>
-        <v>3.7696284631833121E-3</v>
+        <v>2.949373512161557E-3</v>
       </c>
       <c r="T6" s="13">
         <f>S6*(1+CAGR!$C$27)</f>
-        <v>3.797486116703711E-3</v>
+        <v>2.9711694600133131E-3</v>
       </c>
       <c r="U6" s="13">
         <f>T6*(1+CAGR!$C$27)</f>
-        <v>3.8255496390165499E-3</v>
+        <v>2.9931264804931366E-3</v>
       </c>
       <c r="V6" s="13">
         <f>U6*(1+CAGR!$C$27)</f>
-        <v>3.853820551497621E-3</v>
+        <v>3.0152457639319868E-3</v>
       </c>
       <c r="W6" s="13">
         <f>V6*(1+CAGR!$C$27)</f>
-        <v>3.882300386765724E-3</v>
+        <v>3.0375285094573997E-3</v>
       </c>
       <c r="X6" s="13">
         <f>W6*(1+CAGR!$C$27)</f>
-        <v>3.9109906887657515E-3</v>
+        <v>3.0599759250584959E-3</v>
       </c>
       <c r="Y6" s="13">
         <f>X6*(1+CAGR!$C$27)</f>
-        <v>3.93989301285239E-3</v>
+        <v>3.0825892276514673E-3</v>
       </c>
       <c r="Z6" s="13">
         <f>Y6*(1+CAGR!$C$27)</f>
-        <v>3.9690089258744383E-3</v>
+        <v>3.1053696431455479E-3</v>
       </c>
       <c r="AA6" s="13">
         <f>Z6*(1+CAGR!$C$27)</f>
-        <v>3.9983400062597475E-3</v>
+        <v>3.1283184065094738E-3</v>
       </c>
       <c r="AB6" s="13">
         <f>AA6*(1+CAGR!$C$27)</f>
-        <v>4.0278878441007936E-3</v>
+        <v>3.1514367618384323E-3</v>
       </c>
       <c r="AC6" s="13">
         <f>AB6*(1+CAGR!$C$27)</f>
-        <v>4.0576540412408778E-3</v>
+        <v>3.1747259624215068E-3</v>
       </c>
       <c r="AD6" s="13">
         <f>AC6*(1+CAGR!$C$27)</f>
-        <v>4.0876402113609643E-3</v>
+        <v>3.1981872708096203E-3</v>
       </c>
       <c r="AE6" s="13">
         <f>AD6*(1+CAGR!$C$27)</f>
-        <v>4.1178479800671628E-3</v>
+        <v>3.2218219588839797E-3</v>
       </c>
       <c r="AF6" s="13">
         <f>AE6*(1+CAGR!$C$27)</f>
-        <v>4.1482789849788546E-3</v>
+        <v>3.245631307925028E-3</v>
       </c>
       <c r="AG6" s="14"/>
     </row>
@@ -14900,127 +14900,127 @@
       </c>
       <c r="B7" s="14">
         <f>IFERROR(INDEX('SYFAFE frgt'!$B$3:$H$3,,MATCH($A7,'SYFAFE frgt'!$B$1:$H$1,0))*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6057797019375264E-3</v>
+        <v>1.2562153628080902E-3</v>
       </c>
       <c r="C7" s="14">
         <f>IFERROR(B7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6176464561822907E-3</v>
+        <v>1.2654988273897848E-3</v>
       </c>
       <c r="D7" s="14">
         <f>IFERROR(C7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6296009060531335E-3</v>
+        <v>1.2748508970189824E-3</v>
       </c>
       <c r="E7" s="14">
         <f>IFERROR(D7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6416436996230389E-3</v>
+        <v>1.2842720786887891E-3</v>
       </c>
       <c r="F7" s="14">
         <f>IFERROR(E7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6537754897542672E-3</v>
+        <v>1.2937628831390035E-3</v>
       </c>
       <c r="G7" s="14">
         <f>IFERROR(F7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6659969341337479E-3</v>
+        <v>1.3033238248838044E-3</v>
       </c>
       <c r="H7" s="14">
         <f>IFERROR(G7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6783086953087345E-3</v>
+        <v>1.3129554222396441E-3</v>
       </c>
       <c r="I7" s="14">
         <f>IFERROR(H7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.6907114407227219E-3</v>
+        <v>1.322658197353347E-3</v>
       </c>
       <c r="J7" s="14">
         <f>IFERROR(I7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7032058427516302E-3</v>
+        <v>1.3324326762304164E-3</v>
       </c>
       <c r="K7" s="14">
         <f>IFERROR(J7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.715792578740255E-3</v>
+        <v>1.34227938876355E-3</v>
       </c>
       <c r="L7" s="14">
         <f>IFERROR(K7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7284723310389879E-3</v>
+        <v>1.3521988687613669E-3</v>
       </c>
       <c r="M7" s="14">
         <f>IFERROR(L7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7412457870408079E-3</v>
+        <v>1.3621916539773452E-3</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(M7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.754113639218546E-3</v>
+        <v>1.3722582861389759E-3</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(N7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7670765851624259E-3</v>
+        <v>1.3823993109771304E-3</v>
       </c>
       <c r="P7" s="14">
         <f>IFERROR(O7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7801353276178811E-3</v>
+        <v>1.3926152782556453E-3</v>
       </c>
       <c r="Q7" s="14">
         <f>IFERROR(P7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.7932905745236527E-3</v>
+        <v>1.4029067418011266E-3</v>
       </c>
       <c r="R7" s="14">
         <f>IFERROR(Q7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8065430390501675E-3</v>
+        <v>1.4132742595329734E-3</v>
       </c>
       <c r="S7" s="14">
         <f>IFERROR(R7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8198934396382004E-3</v>
+        <v>1.423718393493624E-3</v>
       </c>
       <c r="T7" s="14">
         <f>IFERROR(S7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8333425000378227E-3</v>
+        <v>1.4342397098790248E-3</v>
       </c>
       <c r="U7" s="14">
         <f>IFERROR(T7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8468909493476379E-3</v>
+        <v>1.4448387790693257E-3</v>
       </c>
       <c r="V7" s="14">
         <f>IFERROR(U7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8605395220543071E-3</v>
+        <v>1.4555161756598003E-3</v>
       </c>
       <c r="W7" s="14">
         <f>IFERROR(V7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8742889580723673E-3</v>
+        <v>1.4662724784919967E-3</v>
       </c>
       <c r="X7" s="14">
         <f>IFERROR(W7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.8881400027843432E-3</v>
+        <v>1.4771082706851171E-3</v>
       </c>
       <c r="Y7" s="14">
         <f>IFERROR(X7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.9020934070811564E-3</v>
+        <v>1.4880241396676302E-3</v>
       </c>
       <c r="Z7" s="14">
         <f>IFERROR(Y7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.9161499274028316E-3</v>
+        <v>1.4990206772091165E-3</v>
       </c>
       <c r="AA7" s="14">
         <f>IFERROR(Z7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.9303103257795058E-3</v>
+        <v>1.510098479452349E-3</v>
       </c>
       <c r="AB7" s="14">
         <f>IFERROR(AA7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.9445753698727382E-3</v>
+        <v>1.5212581469456117E-3</v>
       </c>
       <c r="AC7" s="14">
         <f>IFERROR(AB7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.9589458330171272E-3</v>
+        <v>1.532500284675256E-3</v>
       </c>
       <c r="AD7" s="14">
         <f>IFERROR(AC7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.9734224942622347E-3</v>
+        <v>1.5438255020984988E-3</v>
       </c>
       <c r="AE7" s="14">
         <f>IFERROR(AD7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>1.9880061384148192E-3</v>
+        <v>1.5552344131764615E-3</v>
       </c>
       <c r="AF7" s="14">
         <f>IFERROR(AE7*(1+INDEX(CAGR!$C$23:$C$29,MATCH($A7,CAGR!$B$23:$B$29,0))),0)</f>
-        <v>2.0026975560813809E-3</v>
+        <v>1.5667276364074545E-3</v>
       </c>
       <c r="AG7" s="14"/>
     </row>
@@ -15030,127 +15030,127 @@
       </c>
       <c r="B8" s="13">
         <f>B5*Calibration!$F$27</f>
-        <v>5.9907913941804319E-3</v>
+        <v>4.687220936346677E-3</v>
       </c>
       <c r="C8" s="13">
         <f>B8*(1+CAGR!$C$29)</f>
-        <v>6.0350635001988418E-3</v>
+        <v>4.721859622385258E-3</v>
       </c>
       <c r="D8" s="13">
         <f>C8*(1+CAGR!$C$29)</f>
-        <v>6.0796627782455093E-3</v>
+        <v>4.7567542892249948E-3</v>
       </c>
       <c r="E8" s="13">
         <f>D8*(1+CAGR!$C$29)</f>
-        <v>6.1245916461303319E-3</v>
+        <v>4.7919068285707427E-3</v>
       </c>
       <c r="F8" s="13">
         <f>E8*(1+CAGR!$C$29)</f>
-        <v>6.1698525395308844E-3</v>
+        <v>4.8273191461071048E-3</v>
       </c>
       <c r="G8" s="13">
         <f>F8*(1+CAGR!$C$29)</f>
-        <v>6.2154479121244634E-3</v>
+        <v>4.8629931616017454E-3</v>
       </c>
       <c r="H8" s="13">
         <f>G8*(1+CAGR!$C$29)</f>
-        <v>6.2613802357211062E-3</v>
+        <v>4.8989308090094611E-3</v>
       </c>
       <c r="I8" s="13">
         <f>H8*(1+CAGR!$C$29)</f>
-        <v>6.3076520003975895E-3</v>
+        <v>4.9351340365770251E-3</v>
       </c>
       <c r="J8" s="13">
         <f>I8*(1+CAGR!$C$29)</f>
-        <v>6.354265714632424E-3</v>
+        <v>4.9716048069488065E-3</v>
       </c>
       <c r="K8" s="13">
         <f>J8*(1+CAGR!$C$29)</f>
-        <v>6.4012239054418432E-3</v>
+        <v>5.0083450972731678E-3</v>
       </c>
       <c r="L8" s="13">
         <f>K8*(1+CAGR!$C$29)</f>
-        <v>6.4485291185167959E-3</v>
+        <v>5.0453568993096484E-3</v>
       </c>
       <c r="M8" s="13">
         <f>L8*(1+CAGR!$C$29)</f>
-        <v>6.4961839183609541E-3</v>
+        <v>5.0826422195369451E-3</v>
       </c>
       <c r="N8" s="13">
         <f>M8*(1+CAGR!$C$29)</f>
-        <v>6.5441908884297404E-3</v>
+        <v>5.1202030792616843E-3</v>
       </c>
       <c r="O8" s="13">
         <f>N8*(1+CAGR!$C$29)</f>
-        <v>6.5925526312703804E-3</v>
+        <v>5.158041514728001E-3</v>
       </c>
       <c r="P8" s="13">
         <f>O8*(1+CAGR!$C$29)</f>
-        <v>6.6412717686629916E-3</v>
+        <v>5.1961595772279283E-3</v>
       </c>
       <c r="Q8" s="13">
         <f>P8*(1+CAGR!$C$29)</f>
-        <v>6.6903509417627158E-3</v>
+        <v>5.2345593332126013E-3</v>
       </c>
       <c r="R8" s="13">
         <f>Q8*(1+CAGR!$C$29)</f>
-        <v>6.7397928112429006E-3</v>
+        <v>5.2732428644042843E-3</v>
       </c>
       <c r="S8" s="13">
         <f>R8*(1+CAGR!$C$29)</f>
-        <v>6.7896000574393404E-3</v>
+        <v>5.3122122679092228E-3</v>
       </c>
       <c r="T8" s="13">
         <f>S8*(1+CAGR!$C$29)</f>
-        <v>6.8397753804955814E-3</v>
+        <v>5.3514696563313324E-3</v>
       </c>
       <c r="U8" s="13">
         <f>T8*(1+CAGR!$C$29)</f>
-        <v>6.890321500509302E-3</v>
+        <v>5.3910171578867277E-3</v>
       </c>
       <c r="V8" s="13">
         <f>U8*(1+CAGR!$C$29)</f>
-        <v>6.9412411576797728E-3</v>
+        <v>5.4308569165190971E-3</v>
       </c>
       <c r="W8" s="13">
         <f>V8*(1+CAGR!$C$29)</f>
-        <v>6.9925371124564097E-3</v>
+        <v>5.4709910920159284E-3</v>
       </c>
       <c r="X8" s="13">
         <f>W8*(1+CAGR!$C$29)</f>
-        <v>7.0442121456884233E-3</v>
+        <v>5.5114218601255965E-3</v>
       </c>
       <c r="Y8" s="13">
         <f>X8*(1+CAGR!$C$29)</f>
-        <v>7.0962690587755718E-3</v>
+        <v>5.5521514126753132E-3</v>
       </c>
       <c r="Z8" s="13">
         <f>Y8*(1+CAGR!$C$29)</f>
-        <v>7.148710673820031E-3</v>
+        <v>5.5931819576899508E-3</v>
       </c>
       <c r="AA8" s="13">
         <f>Z8*(1+CAGR!$C$29)</f>
-        <v>7.2015398337793874E-3</v>
+        <v>5.6345157195117441E-3</v>
       </c>
       <c r="AB8" s="13">
         <f>AA8*(1+CAGR!$C$29)</f>
-        <v>7.2547594026207583E-3</v>
+        <v>5.676154938920876E-3</v>
       </c>
       <c r="AC8" s="13">
         <f>AB8*(1+CAGR!$C$29)</f>
-        <v>7.3083722654760539E-3</v>
+        <v>5.7181018732569535E-3</v>
       </c>
       <c r="AD8" s="13">
         <f>AC8*(1+CAGR!$C$29)</f>
-        <v>7.3623813287983838E-3</v>
+        <v>5.7603587965413825E-3</v>
       </c>
       <c r="AE8" s="13">
         <f>AD8*(1+CAGR!$C$29)</f>
-        <v>7.4167895205196231E-3</v>
+        <v>5.8029279996006464E-3</v>
       </c>
       <c r="AF8" s="13">
         <f>AE8*(1+CAGR!$C$29)</f>
-        <v>7.471599790209141E-3</v>
+        <v>5.8458117901904975E-3</v>
       </c>
       <c r="AG8" s="14"/>
     </row>
@@ -21348,25 +21348,25 @@
         <v>16</v>
       </c>
       <c r="B2" s="34">
-        <v>1.8699999999999999E-4</v>
+        <v>1.46E-4</v>
       </c>
       <c r="C2" s="34">
-        <v>9.8999999999999994E-5</v>
+        <v>7.7999999999999999E-5</v>
       </c>
       <c r="D2" s="34">
-        <v>1.4200000000000001E-4</v>
+        <v>1.11E-4</v>
       </c>
       <c r="E2" s="34">
-        <v>1.1E-4</v>
+        <v>8.6000000000000003E-5</v>
       </c>
       <c r="F2" s="34">
-        <v>2.4800000000000001E-4</v>
+        <v>1.94E-4</v>
       </c>
       <c r="G2" s="34">
-        <v>7.7999999999999999E-5</v>
+        <v>6.0999999999999999E-5</v>
       </c>
       <c r="H2" s="34">
-        <v>1.1900000000000001E-4</v>
+        <v>9.2999999999999997E-5</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -21376,22 +21376,22 @@
         <v>17</v>
       </c>
       <c r="B3" s="34">
-        <v>2.82E-3</v>
+        <v>2.2070000000000002E-3</v>
       </c>
       <c r="C3" s="34">
-        <v>1.5759999999999999E-3</v>
+        <v>1.2340000000000001E-3</v>
       </c>
       <c r="D3" s="34">
-        <v>1.498E-3</v>
+        <v>1.1720000000000001E-3</v>
       </c>
       <c r="E3" s="34">
-        <v>1.4890000000000001E-3</v>
+        <v>1.165E-3</v>
       </c>
       <c r="F3" s="34">
         <v>0</v>
       </c>
       <c r="G3" s="34">
-        <v>1.5939999999999999E-3</v>
+        <v>1.2470000000000001E-3</v>
       </c>
       <c r="H3" s="34">
         <v>0</v>
@@ -28386,6 +28386,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -28529,35 +28544,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E16404-9CDB-444B-B1EF-816DE1AF2890}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -28579,9 +28569,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33097742-8605-4D00-9519-07E7CAC067CD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E16404-9CDB-444B-B1EF-816DE1AF2890}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>